--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="54">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -131,6 +131,12 @@
     <t>一月电费</t>
   </si>
   <si>
+    <t>其他杂项：床+宽带</t>
+  </si>
+  <si>
+    <t>自购食材(非快驴、老家进货)</t>
+  </si>
+  <si>
     <t>成本明细</t>
   </si>
   <si>
@@ -141,6 +147,9 @@
   </si>
   <si>
     <t>2员工工资</t>
+  </si>
+  <si>
+    <t>自购食材</t>
   </si>
   <si>
     <t>营业额明细</t>
@@ -175,12 +184,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -195,6 +204,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -205,11 +220,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -222,7 +236,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,14 +244,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -253,6 +259,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -260,8 +274,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -277,20 +292,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -298,15 +299,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,22 +330,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,13 +359,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -369,7 +413,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,13 +497,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,139 +509,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,8 +556,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -573,18 +581,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,9 +612,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,182 +653,191 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -885,7 +902,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -921,7 +938,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -958,7 +975,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1002,8 +1019,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C34" totalsRowShown="0">
-  <autoFilter ref="A5:C34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C36" totalsRowShown="0">
+  <autoFilter ref="A5:C36"/>
   <tableColumns count="3">
     <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
     <tableColumn id="2" name="分类" dataDxfId="1"/>
@@ -1026,8 +1043,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C12" totalsRowShown="0">
-  <autoFilter ref="A1:C12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C13" totalsRowShown="0">
+  <autoFilter ref="A1:C13"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1327,17 +1344,17 @@
   <dimension ref="A1:F43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="10" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="12" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="8">
+      <c r="C1" s="10">
         <v>100000</v>
       </c>
       <c r="D1" s="1"/>
@@ -1345,44 +1362,44 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:6">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="9">
+      <c r="C2" s="11">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>92744.55</v>
+        <v>94544.55</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:6">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="9">
+      <c r="C3" s="11">
         <f>C1-C2</f>
-        <v>7255.44999999998</v>
+        <v>5455.44999999998</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:6">
-      <c r="A4" s="5"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="12"/>
+      <c r="C4" s="14"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1396,7 +1413,7 @@
       <c r="A6" s="2">
         <v>10000</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1410,7 +1427,7 @@
       <c r="A7" s="2">
         <v>26000</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1424,7 +1441,7 @@
       <c r="A8" s="2">
         <v>6000</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -1438,7 +1455,7 @@
       <c r="A9" s="2">
         <v>3000</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1452,7 +1469,7 @@
       <c r="A10" s="2">
         <v>2100</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1466,7 +1483,7 @@
       <c r="A11" s="2">
         <v>340</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1480,7 +1497,7 @@
       <c r="A12" s="2">
         <v>200</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1494,7 +1511,7 @@
       <c r="A13" s="2">
         <v>11000</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1508,7 +1525,7 @@
       <c r="A14" s="2">
         <v>5000</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1522,7 +1539,7 @@
       <c r="A15" s="2">
         <v>755</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1536,7 +1553,7 @@
       <c r="A16" s="2">
         <v>190</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1550,7 +1567,7 @@
       <c r="A17" s="2">
         <v>405.9</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1564,7 +1581,7 @@
       <c r="A18" s="2">
         <v>228</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1578,7 +1595,7 @@
       <c r="A19" s="2">
         <v>639.5</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1592,7 +1609,7 @@
       <c r="A20" s="2">
         <v>1259.1</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1606,10 +1623,10 @@
       <c r="A21" s="2">
         <v>1000</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="14" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="1"/>
@@ -1620,7 +1637,7 @@
       <c r="A22" s="2">
         <v>13260</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1634,7 +1651,7 @@
       <c r="A23" s="2">
         <v>47.97</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="15" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1648,7 +1665,7 @@
       <c r="A24" s="2">
         <v>276.1</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="15" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -1662,10 +1679,10 @@
       <c r="A25" s="2">
         <v>6000</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="14" t="s">
         <v>30</v>
       </c>
       <c r="D25" s="1"/>
@@ -1676,10 +1693,10 @@
       <c r="A26" s="2">
         <v>640</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D26" s="1"/>
@@ -1690,10 +1707,10 @@
       <c r="A27" s="2">
         <v>500</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D27" s="1"/>
@@ -1704,10 +1721,10 @@
       <c r="A28" s="2">
         <v>600</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="14" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="1"/>
@@ -1718,10 +1735,10 @@
       <c r="A29" s="2">
         <v>938</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D29" s="1"/>
@@ -1732,10 +1749,10 @@
       <c r="A30" s="2">
         <v>1000</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="14" t="s">
         <v>26</v>
       </c>
       <c r="D30" s="1"/>
@@ -1746,10 +1763,10 @@
       <c r="A31" s="2">
         <v>160.41</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="1"/>
@@ -1760,10 +1777,10 @@
       <c r="A32" s="2">
         <v>162.41</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="14" t="s">
         <v>37</v>
       </c>
       <c r="D32" s="1"/>
@@ -1774,10 +1791,10 @@
       <c r="A33" s="2">
         <v>42.16</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="1"/>
@@ -1788,10 +1805,10 @@
       <c r="A34" s="2">
         <v>1000</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="14" t="s">
         <v>26</v>
       </c>
       <c r="D34" s="1"/>
@@ -1799,49 +1816,61 @@
       <c r="F34" s="1"/>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:6">
-      <c r="A35" s="2"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="12"/>
+      <c r="A35" s="4">
+        <v>500</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:6">
-      <c r="A36" s="5"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="12"/>
+      <c r="A36" s="4">
+        <v>1300</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:6">
-      <c r="A37" s="5"/>
+      <c r="A37" s="7"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="12"/>
+      <c r="C37" s="14"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:6">
-      <c r="A38" s="5"/>
+      <c r="A38" s="7"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="12"/>
+      <c r="C38" s="14"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:6">
-      <c r="A39" s="5"/>
+      <c r="A39" s="7"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="12"/>
+      <c r="C39" s="14"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:6">
-      <c r="A40" s="5"/>
+      <c r="A40" s="7"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="12"/>
+      <c r="C40" s="14"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -1854,7 +1883,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B35 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35 B36 B6:B34 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1882,7 +1911,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>4</v>
@@ -1899,7 +1928,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:3">
@@ -1907,10 +1936,10 @@
         <v>12000</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
@@ -2013,25 +2042,31 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="A13" s="4">
+        <v>1300</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="4"/>
+      <c r="A14" s="6"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="4"/>
+      <c r="A15" s="6"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
     <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -2039,75 +2074,75 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="7">
+      <c r="A17" s="9">
         <v>4233.01</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>43</v>
+      <c r="B17" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="7">
+      <c r="A18" s="9">
         <v>0</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>44</v>
+      <c r="B18" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="7">
+      <c r="A19" s="9">
         <v>4623.5</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>45</v>
+      <c r="B19" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="C19" s="3"/>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="7">
+      <c r="A20" s="9">
         <v>2547.16</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>46</v>
+      <c r="B20" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="4">
+      <c r="A23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="6">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>34495.98</v>
-      </c>
-      <c r="C23" s="8"/>
+        <v>35795.98</v>
+      </c>
+      <c r="C23" s="10"/>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="4">
+      <c r="A24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="6">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>11403.67</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="9"/>
+      <c r="A25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" customHeight="1" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 B2:B12">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="55">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>自购食材(非快驴、老家进货)</t>
+  </si>
+  <si>
+    <t>火鸡面补货</t>
   </si>
   <si>
     <t>成本明细</t>
@@ -184,12 +187,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -207,21 +210,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,6 +255,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -242,11 +300,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -259,7 +316,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -274,17 +331,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,58 +352,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -365,25 +368,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,133 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,30 +553,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -595,6 +574,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -610,13 +609,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,192 +653,180 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -902,7 +908,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -938,7 +944,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -975,7 +981,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1019,8 +1025,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C36" totalsRowShown="0">
-  <autoFilter ref="A5:C36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C37" totalsRowShown="0">
+  <autoFilter ref="A5:C37"/>
   <tableColumns count="3">
     <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
     <tableColumn id="2" name="分类" dataDxfId="1"/>
@@ -1043,8 +1049,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C13" totalsRowShown="0">
-  <autoFilter ref="A1:C13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C14" totalsRowShown="0">
+  <autoFilter ref="A1:C14"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1344,17 +1350,17 @@
   <dimension ref="A1:F43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="12" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="13" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:6">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="10">
+      <c r="C1" s="11">
         <v>100000</v>
       </c>
       <c r="D1" s="1"/>
@@ -1362,44 +1368,44 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:6">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>94544.55</v>
+        <v>94798.39</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:6">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="11">
+      <c r="C3" s="12">
         <f>C1-C2</f>
-        <v>5455.44999999998</v>
+        <v>5201.60999999999</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:6">
-      <c r="A4" s="7"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="14"/>
+      <c r="C4" s="15"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:6">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1413,7 +1419,7 @@
       <c r="A6" s="2">
         <v>10000</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1427,7 +1433,7 @@
       <c r="A7" s="2">
         <v>26000</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1441,7 +1447,7 @@
       <c r="A8" s="2">
         <v>6000</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -1455,7 +1461,7 @@
       <c r="A9" s="2">
         <v>3000</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1469,7 +1475,7 @@
       <c r="A10" s="2">
         <v>2100</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1483,7 +1489,7 @@
       <c r="A11" s="2">
         <v>340</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1497,7 +1503,7 @@
       <c r="A12" s="2">
         <v>200</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1511,7 +1517,7 @@
       <c r="A13" s="2">
         <v>11000</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1525,7 +1531,7 @@
       <c r="A14" s="2">
         <v>5000</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1539,7 +1545,7 @@
       <c r="A15" s="2">
         <v>755</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1553,7 +1559,7 @@
       <c r="A16" s="2">
         <v>190</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1567,7 +1573,7 @@
       <c r="A17" s="2">
         <v>405.9</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1581,7 +1587,7 @@
       <c r="A18" s="2">
         <v>228</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1595,7 +1601,7 @@
       <c r="A19" s="2">
         <v>639.5</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1609,7 +1615,7 @@
       <c r="A20" s="2">
         <v>1259.1</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1623,10 +1629,10 @@
       <c r="A21" s="2">
         <v>1000</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="1"/>
@@ -1637,7 +1643,7 @@
       <c r="A22" s="2">
         <v>13260</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1651,7 +1657,7 @@
       <c r="A23" s="2">
         <v>47.97</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1665,7 +1671,7 @@
       <c r="A24" s="2">
         <v>276.1</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -1679,10 +1685,10 @@
       <c r="A25" s="2">
         <v>6000</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>30</v>
       </c>
       <c r="D25" s="1"/>
@@ -1693,10 +1699,10 @@
       <c r="A26" s="2">
         <v>640</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="15" t="s">
         <v>31</v>
       </c>
       <c r="D26" s="1"/>
@@ -1707,10 +1713,10 @@
       <c r="A27" s="2">
         <v>500</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D27" s="1"/>
@@ -1721,10 +1727,10 @@
       <c r="A28" s="2">
         <v>600</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="15" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="1"/>
@@ -1735,10 +1741,10 @@
       <c r="A29" s="2">
         <v>938</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D29" s="1"/>
@@ -1749,10 +1755,10 @@
       <c r="A30" s="2">
         <v>1000</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D30" s="1"/>
@@ -1763,10 +1769,10 @@
       <c r="A31" s="2">
         <v>160.41</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="1"/>
@@ -1777,10 +1783,10 @@
       <c r="A32" s="2">
         <v>162.41</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="15" t="s">
         <v>37</v>
       </c>
       <c r="D32" s="1"/>
@@ -1791,10 +1797,10 @@
       <c r="A33" s="2">
         <v>42.16</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="1"/>
@@ -1805,10 +1811,10 @@
       <c r="A34" s="2">
         <v>1000</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D34" s="1"/>
@@ -1819,10 +1825,10 @@
       <c r="A35" s="4">
         <v>500</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="18" t="s">
         <v>38</v>
       </c>
       <c r="D35" s="1"/>
@@ -1833,10 +1839,10 @@
       <c r="A36" s="4">
         <v>1300</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="1"/>
@@ -1844,33 +1850,39 @@
       <c r="F36" s="1"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:6">
-      <c r="A37" s="7"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="14"/>
+      <c r="A37" s="4">
+        <v>253.84</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>40</v>
+      </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:6">
-      <c r="A38" s="7"/>
+      <c r="A38" s="8"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="14"/>
+      <c r="C38" s="15"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:6">
-      <c r="A39" s="7"/>
+      <c r="A39" s="8"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="14"/>
+      <c r="C39" s="15"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:6">
-      <c r="A40" s="7"/>
+      <c r="A40" s="8"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="14"/>
+      <c r="C40" s="15"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -1883,7 +1895,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35 B36 B6:B34 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35 B36 B37 B6:B34 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1911,7 +1923,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>4</v>
@@ -1928,7 +1940,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:3">
@@ -1936,10 +1948,10 @@
         <v>12000</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
@@ -2049,24 +2061,30 @@
         <v>25</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
+      <c r="A14" s="4">
+        <v>253.84</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="6"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
     <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="A16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -2074,75 +2092,75 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="9">
+      <c r="A17" s="10">
         <v>4233.01</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>46</v>
+      <c r="B17" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="9">
+      <c r="A18" s="10">
         <v>0</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>47</v>
+      <c r="B18" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="9">
+      <c r="A19" s="10">
         <v>4623.5</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>48</v>
+      <c r="B19" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="C19" s="3"/>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="9">
+      <c r="A20" s="10">
         <v>2547.16</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>49</v>
+      <c r="B20" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="6">
+      <c r="A23" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="7">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>35795.98</v>
-      </c>
-      <c r="C23" s="10"/>
+        <v>36049.82</v>
+      </c>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="6">
+      <c r="A24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="7">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>11403.67</v>
       </c>
-      <c r="C24" s="11"/>
+      <c r="C24" s="12"/>
     </row>
     <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="11"/>
+      <c r="A25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="12"/>
     </row>
     <row r="26" customHeight="1" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 B2:B12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 B14 B2:B12">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="55">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -152,7 +152,7 @@
     <t>2员工工资</t>
   </si>
   <si>
-    <t>自购食材</t>
+    <t>老池自购食材</t>
   </si>
   <si>
     <t>营业额明细</t>
@@ -801,7 +801,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -819,7 +819,9 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -829,6 +831,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1025,8 +1028,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C37" totalsRowShown="0">
-  <autoFilter ref="A5:C37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C38" totalsRowShown="0">
+  <autoFilter ref="A5:C38"/>
   <tableColumns count="3">
     <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
     <tableColumn id="2" name="分类" dataDxfId="1"/>
@@ -1037,8 +1040,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A16:C20" totalsRowShown="0">
-  <autoFilter ref="A16:C20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A21:C25" totalsRowShown="0">
+  <autoFilter ref="A21:C25"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1049,8 +1052,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C14" totalsRowShown="0">
-  <autoFilter ref="A1:C14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C15" totalsRowShown="0">
+  <autoFilter ref="A1:C15"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1350,9 +1353,9 @@
   <dimension ref="A1:F43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="13" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="14" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="14" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:6">
@@ -1360,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="11">
+      <c r="C1" s="12">
         <v>100000</v>
       </c>
       <c r="D1" s="1"/>
@@ -1372,9 +1375,9 @@
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>94798.39</v>
+        <v>95798.39</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1385,9 +1388,9 @@
         <v>2</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="12">
+      <c r="C3" s="13">
         <f>C1-C2</f>
-        <v>5201.60999999999</v>
+        <v>4201.60999999999</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1396,7 +1399,7 @@
     <row r="4" ht="15" customHeight="1" spans="1:6">
       <c r="A4" s="8"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="15"/>
+      <c r="C4" s="16"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -1419,7 +1422,7 @@
       <c r="A6" s="2">
         <v>10000</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1433,7 +1436,7 @@
       <c r="A7" s="2">
         <v>26000</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1447,7 +1450,7 @@
       <c r="A8" s="2">
         <v>6000</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -1461,7 +1464,7 @@
       <c r="A9" s="2">
         <v>3000</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1475,7 +1478,7 @@
       <c r="A10" s="2">
         <v>2100</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1489,7 +1492,7 @@
       <c r="A11" s="2">
         <v>340</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1503,7 +1506,7 @@
       <c r="A12" s="2">
         <v>200</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1517,7 +1520,7 @@
       <c r="A13" s="2">
         <v>11000</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1531,7 +1534,7 @@
       <c r="A14" s="2">
         <v>5000</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1545,7 +1548,7 @@
       <c r="A15" s="2">
         <v>755</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1559,7 +1562,7 @@
       <c r="A16" s="2">
         <v>190</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1573,7 +1576,7 @@
       <c r="A17" s="2">
         <v>405.9</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1587,7 +1590,7 @@
       <c r="A18" s="2">
         <v>228</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1601,7 +1604,7 @@
       <c r="A19" s="2">
         <v>639.5</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1615,7 +1618,7 @@
       <c r="A20" s="2">
         <v>1259.1</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1629,10 +1632,10 @@
       <c r="A21" s="2">
         <v>1000</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="1"/>
@@ -1643,7 +1646,7 @@
       <c r="A22" s="2">
         <v>13260</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1657,7 +1660,7 @@
       <c r="A23" s="2">
         <v>47.97</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1671,7 +1674,7 @@
       <c r="A24" s="2">
         <v>276.1</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -1685,10 +1688,10 @@
       <c r="A25" s="2">
         <v>6000</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D25" s="1"/>
@@ -1699,10 +1702,10 @@
       <c r="A26" s="2">
         <v>640</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="16" t="s">
         <v>31</v>
       </c>
       <c r="D26" s="1"/>
@@ -1713,10 +1716,10 @@
       <c r="A27" s="2">
         <v>500</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="16" t="s">
         <v>33</v>
       </c>
       <c r="D27" s="1"/>
@@ -1727,10 +1730,10 @@
       <c r="A28" s="2">
         <v>600</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="1"/>
@@ -1741,10 +1744,10 @@
       <c r="A29" s="2">
         <v>938</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D29" s="1"/>
@@ -1755,10 +1758,10 @@
       <c r="A30" s="2">
         <v>1000</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D30" s="1"/>
@@ -1769,10 +1772,10 @@
       <c r="A31" s="2">
         <v>160.41</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="1"/>
@@ -1783,10 +1786,10 @@
       <c r="A32" s="2">
         <v>162.41</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D32" s="1"/>
@@ -1797,10 +1800,10 @@
       <c r="A33" s="2">
         <v>42.16</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="1"/>
@@ -1811,10 +1814,10 @@
       <c r="A34" s="2">
         <v>1000</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D34" s="1"/>
@@ -1825,10 +1828,10 @@
       <c r="A35" s="4">
         <v>500</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="19" t="s">
         <v>38</v>
       </c>
       <c r="D35" s="1"/>
@@ -1839,10 +1842,10 @@
       <c r="A36" s="4">
         <v>1300</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="1"/>
@@ -1853,10 +1856,10 @@
       <c r="A37" s="4">
         <v>253.84</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="19" t="s">
         <v>40</v>
       </c>
       <c r="D37" s="1"/>
@@ -1864,9 +1867,15 @@
       <c r="F37" s="1"/>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:6">
-      <c r="A38" s="8"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="15"/>
+      <c r="A38" s="4">
+        <v>1000</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>26</v>
+      </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -1874,7 +1883,7 @@
     <row r="39" ht="15" customHeight="1" spans="1:6">
       <c r="A39" s="8"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="15"/>
+      <c r="C39" s="16"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -1882,7 +1891,7 @@
     <row r="40" ht="15" customHeight="1" spans="1:6">
       <c r="A40" s="8"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="15"/>
+      <c r="C40" s="16"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -1895,7 +1904,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35 B36 B37 B6:B34 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35 B36 B37 B38 B6:B34 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1912,7 +1921,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -2076,91 +2085,122 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+      <c r="A15" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B21" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="10">
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="10">
         <v>4233.01</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B22" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="10">
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="10">
         <v>0</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B23" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="10">
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="10">
         <v>4623.5</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B24" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="10">
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="10">
         <v>2547.16</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B25" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="8" t="s">
+      <c r="C25" s="3"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B28" s="11">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>36049.82</v>
-      </c>
-      <c r="C23" s="11"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="8" t="s">
+        <v>37049.82</v>
+      </c>
+      <c r="C28" s="12"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B29" s="11">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>11403.67</v>
       </c>
-      <c r="C24" s="12"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="8" t="s">
+      <c r="C29" s="13"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="12"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:1">
-      <c r="A26" s="1" t="s">
+      <c r="C30" s="13"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:1">
+      <c r="A31" s="1" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 B14 B2:B12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 B14 B15 B2:B12">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DFC61F-F45E-4D03-9038-049A4D823D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5670" yWindow="1260" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28000" windowHeight="15800"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="流水-202602" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="55">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -186,21 +180,21 @@
   </si>
   <si>
     <t>净利润</t>
-  </si>
-  <si>
-    <t>火鸡面补货</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,26 +212,348 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -245,24 +561,272 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -272,7 +836,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -282,135 +846,177 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -418,44 +1024,41 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C39" totalsRowShown="0">
-  <autoFilter ref="A5:C39" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C39" totalsRowShown="0">
+  <autoFilter ref="A5:C39"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="6"/>
+    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
+    <tableColumn id="2" name="分类" dataDxfId="1"/>
+    <tableColumn id="3" name="说明" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表" displayName="营业额明细表" ref="A21:C25" totalsRowShown="0">
-  <autoFilter ref="A21:C25" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A21:C25" totalsRowShown="0">
+  <autoFilter ref="A21:C25"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明" dataDxfId="3"/>
+    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
+    <tableColumn id="2" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" name="说明" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表" displayName="成本明细表" ref="A1:C16" totalsRowShown="0">
-  <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C16" totalsRowShown="0">
+  <autoFilter ref="A1:C16"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="成本明细" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="说明" dataDxfId="0"/>
+    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
+    <tableColumn id="4" name="分类" dataDxfId="7"/>
+    <tableColumn id="1" name="说明" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -740,62 +1343,61 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="7" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="15" customHeight="1" spans="1:3">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9">
+      <c r="C1" s="11">
         <v>100000</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="15" customHeight="1" spans="1:3">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="12">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>96002.890000000014</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="5" t="s">
+        <v>96153.69</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:3">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="12">
         <f>C1-C2</f>
-        <v>3997.109999999986</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="5" t="s">
+        <v>3846.30999999998</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1"/>
+    <row r="5" ht="15" customHeight="1" spans="1:3">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" ht="15" customHeight="1" spans="1:3">
       <c r="A6" s="1">
         <v>10000</v>
       </c>
@@ -806,7 +1408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" ht="15" customHeight="1" spans="1:3">
       <c r="A7" s="1">
         <v>26000</v>
       </c>
@@ -817,7 +1419,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" ht="15" customHeight="1" spans="1:3">
       <c r="A8" s="1">
         <v>6000</v>
       </c>
@@ -828,7 +1430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" ht="15" customHeight="1" spans="1:3">
       <c r="A9" s="1">
         <v>3000</v>
       </c>
@@ -839,7 +1441,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" ht="15" customHeight="1" spans="1:3">
       <c r="A10" s="1">
         <v>2100</v>
       </c>
@@ -850,7 +1452,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" ht="15" customHeight="1" spans="1:3">
       <c r="A11" s="1">
         <v>340</v>
       </c>
@@ -861,7 +1463,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" ht="15" customHeight="1" spans="1:3">
       <c r="A12" s="1">
         <v>200</v>
       </c>
@@ -872,7 +1474,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" ht="15" customHeight="1" spans="1:3">
       <c r="A13" s="1">
         <v>11000</v>
       </c>
@@ -883,7 +1485,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" ht="15" customHeight="1" spans="1:3">
       <c r="A14" s="1">
         <v>5000</v>
       </c>
@@ -894,7 +1496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" ht="15" customHeight="1" spans="1:3">
       <c r="A15" s="1">
         <v>755</v>
       </c>
@@ -905,7 +1507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" ht="15" customHeight="1" spans="1:3">
       <c r="A16" s="1">
         <v>190</v>
       </c>
@@ -916,7 +1518,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" ht="15" customHeight="1" spans="1:3">
       <c r="A17" s="1">
         <v>405.9</v>
       </c>
@@ -927,7 +1529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" ht="15" customHeight="1" spans="1:3">
       <c r="A18" s="1">
         <v>228</v>
       </c>
@@ -938,7 +1540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" ht="15" customHeight="1" spans="1:3">
       <c r="A19" s="1">
         <v>639.5</v>
       </c>
@@ -949,9 +1551,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" ht="15" customHeight="1" spans="1:3">
       <c r="A20" s="1">
-        <v>1259.0999999999999</v>
+        <v>1259.1</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -960,18 +1562,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" ht="15" customHeight="1" spans="1:3">
       <c r="A21" s="1">
         <v>1000</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" ht="15" customHeight="1" spans="1:3">
       <c r="A22" s="1">
         <v>13260</v>
       </c>
@@ -982,7 +1584,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" ht="15" customHeight="1" spans="1:3">
       <c r="A23" s="1">
         <v>47.97</v>
       </c>
@@ -993,9 +1595,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" ht="15" customHeight="1" spans="1:3">
       <c r="A24" s="1">
-        <v>276.10000000000002</v>
+        <v>276.1</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1004,187 +1606,187 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" ht="15" customHeight="1" spans="1:3">
       <c r="A25" s="1">
         <v>6000</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" ht="15" customHeight="1" spans="1:3">
       <c r="A26" s="1">
         <v>640</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" ht="15" customHeight="1" spans="1:3">
       <c r="A27" s="1">
         <v>500</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" ht="15" customHeight="1" spans="1:3">
       <c r="A28" s="1">
         <v>600</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" ht="15" customHeight="1" spans="1:3">
       <c r="A29" s="1">
         <v>938</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" ht="15" customHeight="1" spans="1:3">
       <c r="A30" s="1">
         <v>1000</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" ht="15" customHeight="1" spans="1:3">
       <c r="A31" s="1">
         <v>160.41</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" ht="15" customHeight="1" spans="1:3">
       <c r="A32" s="1">
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" ht="15" customHeight="1" spans="1:3">
       <c r="A33" s="1">
         <v>42.16</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" ht="15" customHeight="1" spans="1:3">
       <c r="A34" s="1">
         <v>1000</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" ht="15" customHeight="1" spans="1:3">
       <c r="A35" s="3">
         <v>500</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" ht="15" customHeight="1" spans="1:3">
       <c r="A36" s="3">
         <v>1300</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="B36" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" ht="15" customHeight="1" spans="1:3">
       <c r="A37" s="3">
         <v>253.84</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="13" t="s">
+      <c r="B37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" ht="15" customHeight="1" spans="1:3">
       <c r="A38" s="3">
         <v>1000</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="B38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="14">
-        <v>204.5</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" ht="15" customHeight="1" spans="1:3">
+      <c r="A39" s="5">
+        <v>355.3</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="43" ht="15" customHeight="1"/>
+    <row r="44" ht="15" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B39 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B39 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1192,19 +1794,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -1215,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" s="1">
         <v>4333</v>
       </c>
@@ -1226,7 +1828,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" s="1">
         <v>12000</v>
       </c>
@@ -1237,7 +1839,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="1">
         <v>1000</v>
       </c>
@@ -1248,7 +1850,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" customHeight="1" spans="1:3">
       <c r="A5" s="1">
         <v>13260</v>
       </c>
@@ -1259,7 +1861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" customHeight="1" spans="1:3">
       <c r="A6" s="1">
         <v>600</v>
       </c>
@@ -1270,7 +1872,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" customHeight="1" spans="1:3">
       <c r="A7" s="1">
         <v>938</v>
       </c>
@@ -1281,7 +1883,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="1">
         <v>1000</v>
       </c>
@@ -1292,7 +1894,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" customHeight="1" spans="1:3">
       <c r="A9" s="1">
         <v>160.41</v>
       </c>
@@ -1303,7 +1905,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" customHeight="1" spans="1:3">
       <c r="A10" s="1">
         <v>162.41</v>
       </c>
@@ -1314,7 +1916,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" customHeight="1" spans="1:3">
       <c r="A11" s="1">
         <v>42.16</v>
       </c>
@@ -1325,7 +1927,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" customHeight="1" spans="1:3">
       <c r="A12" s="1">
         <v>1000</v>
       </c>
@@ -1336,7 +1938,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" customHeight="1" spans="1:3">
       <c r="A13" s="3">
         <v>1300</v>
       </c>
@@ -1347,7 +1949,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" customHeight="1" spans="1:3">
       <c r="A14" s="3">
         <v>253.84</v>
       </c>
@@ -1358,7 +1960,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" customHeight="1" spans="1:3">
       <c r="A15" s="3">
         <v>1000</v>
       </c>
@@ -1369,126 +1971,126 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="14">
-        <v>204.5</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="5">
+        <v>355.3</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="5" t="s">
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="7">
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="9">
         <v>4233.01</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="8" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="7">
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="9">
         <v>0</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="7">
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="9">
         <v>4623.5</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="7">
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="9">
         <v>2547.16</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="10">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>37254.320000000007</v>
-      </c>
-      <c r="C28" s="9"/>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="5" t="s">
+        <v>37405.12</v>
+      </c>
+      <c r="C28" s="11"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="10">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>11403.67</v>
       </c>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="s">
+      <c r="C29" s="12"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C30" s="12"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:1">
       <c r="A31" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16" xr:uid="{3A2AD706-2AEF-4468-8C35-C9CDE77A57E4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15800"/>
+    <workbookView windowWidth="28000" windowHeight="15800" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -187,14 +187,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,20 +207,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -238,17 +224,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -260,40 +239,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -307,22 +261,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -338,7 +279,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,9 +292,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,13 +362,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,169 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,15 +553,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -584,32 +569,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -630,6 +589,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -645,198 +619,212 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -846,8 +834,6 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -912,7 +898,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -948,7 +934,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -985,7 +971,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1354,43 +1340,43 @@
   <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="7" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="9">
         <v>100000</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <f>SUM(成本明细[金额(元)])</f>
         <v>96153.69</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <f>C1-C2</f>
         <v>3846.30999999998</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1569,7 +1555,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1613,7 +1599,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="11" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1624,7 +1610,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="11" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1635,7 +1621,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1646,7 +1632,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="11" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1657,7 +1643,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1668,7 +1654,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1679,7 +1665,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1690,7 +1676,7 @@
       <c r="B32" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="11" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1701,7 +1687,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1712,7 +1698,7 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1720,10 +1706,10 @@
       <c r="A35" s="3">
         <v>500</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1731,10 +1717,10 @@
       <c r="A36" s="3">
         <v>1300</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1742,10 +1728,10 @@
       <c r="A37" s="3">
         <v>253.84</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1753,21 +1739,21 @@
       <c r="A38" s="3">
         <v>1000</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="15" t="s">
+      <c r="B38" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:3">
-      <c r="A39" s="5">
+      <c r="A39" s="3">
         <v>355.3</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="17" t="s">
+      <c r="B39" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1972,41 +1958,41 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="5">
+      <c r="A16" s="3">
         <v>355.3</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2014,66 +2000,66 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="9">
-        <v>4233.01</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="A22" s="7">
+        <v>6596.29</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="2"/>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="9">
+      <c r="A23" s="7">
         <v>0</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C23" s="2"/>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="9">
-        <v>4623.5</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="7">
+        <v>10263.04</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="2"/>
     </row>
     <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="9">
-        <v>2547.16</v>
-      </c>
-      <c r="B25" s="8" t="s">
+      <c r="A25" s="7">
+        <v>7245.93</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="2"/>
     </row>
     <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="8">
         <f>SUM(成本明细表[成本明细])</f>
         <v>37405.12</v>
       </c>
-      <c r="C28" s="11"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="8">
         <f>SUM(营业额明细表[营业额明细])</f>
-        <v>11403.67</v>
-      </c>
-      <c r="C29" s="12"/>
+        <v>24105.26</v>
+      </c>
+      <c r="C29" s="10"/>
     </row>
     <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="12"/>
+      <c r="C30" s="10"/>
     </row>
     <row r="31" customHeight="1" spans="1:1">
       <c r="A31" t="s">

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15800" activeTab="1"/>
+    <workbookView windowHeight="15800" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -125,6 +125,9 @@
     <t>包装盒补货</t>
   </si>
   <si>
+    <t>火鸡面补货</t>
+  </si>
+  <si>
     <t>水电</t>
   </si>
   <si>
@@ -135,9 +138,6 @@
   </si>
   <si>
     <t>自购食材(非快驴、老家进货)</t>
-  </si>
-  <si>
-    <t>火鸡面补货</t>
   </si>
   <si>
     <t>成本明细</t>
@@ -187,12 +187,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -217,37 +217,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,11 +254,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,6 +295,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -300,30 +338,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -337,21 +352,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -362,25 +362,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,30 +530,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -428,121 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -561,6 +561,30 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,15 +645,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -638,163 +653,148 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -803,28 +803,28 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -898,7 +898,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -934,7 +934,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -971,7 +971,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C2" s="10">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>96153.69</v>
+        <v>96053.78</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:3">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C3" s="10">
         <f>C1-C2</f>
-        <v>3846.30999999998</v>
+        <v>3946.21999999999</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
@@ -1660,13 +1660,13 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:3">
       <c r="A31" s="1">
-        <v>160.41</v>
+        <v>60.5</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:3">
@@ -1674,10 +1674,10 @@
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:3">
@@ -1710,7 +1710,7 @@
         <v>9</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:3">
@@ -1721,7 +1721,7 @@
         <v>25</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:3">
@@ -1732,7 +1732,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:3">
@@ -1754,7 +1754,7 @@
         <v>25</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1"/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="9" customHeight="1" spans="1:3">
       <c r="A9" s="1">
-        <v>160.41</v>
+        <v>60.5</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:3">
@@ -1896,10 +1896,10 @@
         <v>162.41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:3">
@@ -1943,7 +1943,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -1965,7 +1965,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B28" s="8">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>37405.12</v>
+        <v>37305.21</v>
       </c>
       <c r="C28" s="9"/>
     </row>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="56">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>自购食材(非快驴、老家进货)</t>
+  </si>
+  <si>
+    <t>主食材补货</t>
   </si>
   <si>
     <t>成本明细</t>
@@ -187,12 +190,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -217,30 +220,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,17 +255,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,21 +297,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,24 +326,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -352,6 +347,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -362,37 +365,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,139 +533,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,15 +568,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -585,45 +579,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,6 +600,54 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -656,175 +659,181 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -832,6 +841,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -898,7 +909,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -934,7 +945,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -971,7 +982,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1015,8 +1026,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C39" totalsRowShown="0">
-  <autoFilter ref="A5:C39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C40" totalsRowShown="0">
+  <autoFilter ref="A5:C40"/>
   <tableColumns count="3">
     <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
     <tableColumn id="2" name="分类" dataDxfId="1"/>
@@ -1027,8 +1038,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A21:C25" totalsRowShown="0">
-  <autoFilter ref="A21:C25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A22:C26" totalsRowShown="0">
+  <autoFilter ref="A22:C26"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1039,8 +1050,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C16" totalsRowShown="0">
-  <autoFilter ref="A1:C16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C17" totalsRowShown="0">
+  <autoFilter ref="A1:C17"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1340,43 +1351,43 @@
   <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="7" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9">
+      <c r="C1" s="11">
         <v>100000</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="12">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>96053.78</v>
+        <v>99053.78</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="12">
         <f>C1-C2</f>
-        <v>3946.21999999999</v>
+        <v>946.219999999987</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1555,7 +1566,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1599,7 +1610,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1610,7 +1621,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1621,7 +1632,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1632,7 +1643,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1643,7 +1654,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1654,7 +1665,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1665,7 +1676,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="13" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1676,7 +1687,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1687,7 +1698,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1698,7 +1709,7 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1706,10 +1717,10 @@
       <c r="A35" s="3">
         <v>500</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1717,10 +1728,10 @@
       <c r="A36" s="3">
         <v>1300</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="B36" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1728,10 +1739,10 @@
       <c r="A37" s="3">
         <v>253.84</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="13" t="s">
+      <c r="B37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1739,10 +1750,10 @@
       <c r="A38" s="3">
         <v>1000</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="B38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1750,14 +1761,24 @@
       <c r="A39" s="3">
         <v>355.3</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="13" t="s">
+      <c r="B39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1"/>
+    <row r="40" ht="15" customHeight="1" spans="1:3">
+      <c r="A40" s="5">
+        <v>3000</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="41" ht="15" customHeight="1"/>
     <row r="42" ht="15" customHeight="1"/>
     <row r="43" ht="15" customHeight="1"/>
@@ -1767,7 +1788,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B39 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B40 B6:B39 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1784,7 +1805,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -1794,7 +1815,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>4</v>
@@ -1811,7 +1832,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:3">
@@ -1819,10 +1840,10 @@
         <v>12000</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
@@ -1932,7 +1953,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
@@ -1969,101 +1990,112 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="5">
+        <v>3000</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="7">
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="9">
         <v>6596.29</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="7">
+      <c r="B23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="9">
         <v>0</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="7">
+      <c r="B24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="9">
         <v>10263.04</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="7">
+      <c r="B25" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="9">
         <v>7245.93</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="5" t="s">
+      <c r="B26" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="8">
+      <c r="C26" s="2"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="10">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>37305.21</v>
-      </c>
-      <c r="C28" s="9"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="8">
+        <v>40305.21</v>
+      </c>
+      <c r="C29" s="11"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="10">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>24105.26</v>
       </c>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:1">
-      <c r="A31" t="s">
+      <c r="C30" s="12"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:3">
+      <c r="A31" s="7" t="s">
         <v>54</v>
+      </c>
+      <c r="C31" s="12"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2071,7 +2103,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16 B17">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FCDF3C-7770-444F-A0B2-582895C47696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15800" activeTab="1"/>
+    <workbookView xWindow="2310" yWindow="1125" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="流水-202602" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -188,16 +194,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,344 +215,28 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -558,251 +244,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -818,19 +262,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -843,177 +281,135 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <name val="宋体"/>
+        <charset val="134"/>
         <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
         <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
         <name val="宋体"/>
+        <charset val="134"/>
         <scheme val="none"/>
-        <charset val="134"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
       </font>
       <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1021,41 +417,44 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C40" totalsRowShown="0">
-  <autoFilter ref="A5:C40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C41" totalsRowShown="0">
+  <autoFilter ref="A5:C41" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
-    <tableColumn id="2" name="分类" dataDxfId="1"/>
-    <tableColumn id="3" name="说明" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A22:C26" totalsRowShown="0">
-  <autoFilter ref="A22:C26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表" displayName="营业额明细表" ref="A22:C26" totalsRowShown="0">
+  <autoFilter ref="A22:C26" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
-    <tableColumn id="2" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" name="说明" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C17" totalsRowShown="0">
-  <autoFilter ref="A1:C17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表" displayName="成本明细表" ref="A1:C18" totalsRowShown="0">
+  <autoFilter ref="A1:C18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
-    <tableColumn id="4" name="分类" dataDxfId="7"/>
-    <tableColumn id="1" name="说明" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="成本明细" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="分类" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1340,61 +739,62 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="7" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="9">
         <v>100000</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99053.78</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="7" t="s">
+        <v>99227.780000000013</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <f>C1-C2</f>
-        <v>946.219999999987</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="7" t="s">
+        <v>772.21999999998661</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>10000</v>
       </c>
@@ -1405,7 +805,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>26000</v>
       </c>
@@ -1416,7 +816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>6000</v>
       </c>
@@ -1427,7 +827,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>3000</v>
       </c>
@@ -1438,7 +838,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>2100</v>
       </c>
@@ -1449,7 +849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>340</v>
       </c>
@@ -1460,7 +860,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>200</v>
       </c>
@@ -1471,7 +871,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>11000</v>
       </c>
@@ -1482,7 +882,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>5000</v>
       </c>
@@ -1493,7 +893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>755</v>
       </c>
@@ -1504,7 +904,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>190</v>
       </c>
@@ -1515,7 +915,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>405.9</v>
       </c>
@@ -1526,7 +926,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>228</v>
       </c>
@@ -1537,7 +937,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>639.5</v>
       </c>
@@ -1548,9 +948,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
-        <v>1259.1</v>
+        <v>1259.0999999999999</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -1559,18 +959,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>1000</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>13260</v>
       </c>
@@ -1581,7 +981,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>47.97</v>
       </c>
@@ -1592,9 +992,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
-        <v>276.1</v>
+        <v>276.10000000000002</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1603,197 +1003,207 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>6000</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>640</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>500</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>600</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>938</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:3">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>1000</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:3">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>60.5</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:3">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:3">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>42.16</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:3">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>1000</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:3">
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3">
         <v>500</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:3">
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3">
         <v>1300</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:3">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3">
         <v>253.84</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:3">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3">
         <v>1000</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="15" t="s">
+      <c r="B38" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:3">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3">
         <v>355.3</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="B39" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:3">
-      <c r="A40" s="5">
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="3">
         <v>3000</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="17" t="s">
+      <c r="B40" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="42" ht="15" customHeight="1"/>
-    <row r="43" ht="15" customHeight="1"/>
-    <row r="44" ht="15" customHeight="1"/>
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="14">
+        <v>174</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B40 B6:B39 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B41 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1801,19 +1211,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1824,7 +1234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>4333</v>
       </c>
@@ -1835,7 +1245,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>12000</v>
       </c>
@@ -1846,7 +1256,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:3">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>1000</v>
       </c>
@@ -1857,7 +1267,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:3">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>13260</v>
       </c>
@@ -1868,7 +1278,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>600</v>
       </c>
@@ -1879,7 +1289,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>938</v>
       </c>
@@ -1890,7 +1300,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>1000</v>
       </c>
@@ -1901,7 +1311,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>60.5</v>
       </c>
@@ -1912,7 +1322,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>162.41</v>
       </c>
@@ -1923,7 +1333,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>42.16</v>
       </c>
@@ -1934,7 +1344,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>1000</v>
       </c>
@@ -1945,7 +1355,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3">
         <v>1300</v>
       </c>
@@ -1956,7 +1366,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3">
         <v>253.84</v>
       </c>
@@ -1967,7 +1377,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3">
         <v>1000</v>
       </c>
@@ -1978,7 +1388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3">
         <v>355.3</v>
       </c>
@@ -1989,126 +1399,132 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="5">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="3">
         <v>3000</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8"/>
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="14">
+        <v>174</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8"/>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="9">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="7">
         <v>6596.29</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="9">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="7">
         <v>0</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="9">
-        <v>10263.04</v>
-      </c>
-      <c r="B25" s="8" t="s">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="7">
+        <v>10263.040000000001</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="9">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="7">
         <v>7245.93</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="8">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>40305.21</v>
-      </c>
-      <c r="C29" s="11"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="7" t="s">
+        <v>40479.210000000006</v>
+      </c>
+      <c r="C29" s="9"/>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="8">
         <f>SUM(营业额明细表[营业额明细])</f>
-        <v>24105.26</v>
-      </c>
-      <c r="C30" s="12"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="7" t="s">
+        <v>24105.260000000002</v>
+      </c>
+      <c r="C30" s="10"/>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="12"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:1">
+      <c r="C31" s="10"/>
+    </row>
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16 B17">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B18" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FCDF3C-7770-444F-A0B2-582895C47696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014E43B8-A63E-4D13-9A7A-769A5A6839BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="1125" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1545" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="57">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -189,6 +189,10 @@
   </si>
   <si>
     <t>净利润</t>
+  </si>
+  <si>
+    <t>硅胶防烫套</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -197,7 +201,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -268,7 +272,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -373,7 +377,7 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -425,8 +429,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C41" totalsRowShown="0">
-  <autoFilter ref="A5:C41" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C42" totalsRowShown="0">
+  <autoFilter ref="A5:C42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
@@ -449,8 +453,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表" displayName="成本明细表" ref="A1:C18" totalsRowShown="0">
-  <autoFilter ref="A1:C18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表" displayName="成本明细表" ref="A1:C19" totalsRowShown="0">
+  <autoFilter ref="A1:C19" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="成本明细" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="分类" dataDxfId="1"/>
@@ -770,7 +774,7 @@
       </c>
       <c r="C2" s="10">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99227.780000000013</v>
+        <v>99261.380000000019</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -779,7 +783,7 @@
       </c>
       <c r="C3" s="10">
         <f>C1-C2</f>
-        <v>772.21999999998661</v>
+        <v>738.61999999998079</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1190,7 +1194,17 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="14">
+        <v>33.6</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
     <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
@@ -1199,7 +1213,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B41 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B42 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1422,9 +1436,15 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="14">
+        <v>33.6</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5"/>
@@ -1489,7 +1509,7 @@
       </c>
       <c r="B29" s="8">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>40479.210000000006</v>
+        <v>40512.810000000005</v>
       </c>
       <c r="C29" s="9"/>
     </row>
@@ -1520,7 +1540,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B18" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014E43B8-A63E-4D13-9A7A-769A5A6839BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1545" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="流水-202602" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -149,6 +143,9 @@
     <t>主食材补货</t>
   </si>
   <si>
+    <t>硅胶防烫套</t>
+  </si>
+  <si>
     <t>成本明细</t>
   </si>
   <si>
@@ -189,21 +186,21 @@
   </si>
   <si>
     <t>净利润</t>
-  </si>
-  <si>
-    <t>硅胶防烫套</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,26 +218,348 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -248,9 +567,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -266,6 +827,12 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -285,135 +852,177 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -421,44 +1030,41 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C42" totalsRowShown="0">
-  <autoFilter ref="A5:C42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C42" totalsRowShown="0">
+  <autoFilter ref="A5:C42"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="6"/>
+    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
+    <tableColumn id="2" name="分类" dataDxfId="1"/>
+    <tableColumn id="3" name="说明" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表" displayName="营业额明细表" ref="A22:C26" totalsRowShown="0">
-  <autoFilter ref="A22:C26" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A22:C26" totalsRowShown="0">
+  <autoFilter ref="A22:C26"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明" dataDxfId="3"/>
+    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
+    <tableColumn id="2" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" name="说明" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表" displayName="成本明细表" ref="A1:C19" totalsRowShown="0">
-  <autoFilter ref="A1:C19" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C19" totalsRowShown="0">
+  <autoFilter ref="A1:C19"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="成本明细" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="说明" dataDxfId="0"/>
+    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
+    <tableColumn id="4" name="分类" dataDxfId="7"/>
+    <tableColumn id="1" name="说明" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -743,62 +1349,61 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="7" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="15" customHeight="1" spans="1:3">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9">
+      <c r="C1" s="11">
         <v>100000</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="15" customHeight="1" spans="1:3">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="12">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99261.380000000019</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="5" t="s">
+        <v>99261.38</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:3">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="12">
         <f>C1-C2</f>
-        <v>738.61999999998079</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="5" t="s">
+        <v>738.619999999981</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1"/>
+    <row r="5" ht="15" customHeight="1" spans="1:3">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" ht="15" customHeight="1" spans="1:3">
       <c r="A6" s="1">
         <v>10000</v>
       </c>
@@ -809,7 +1414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" ht="15" customHeight="1" spans="1:3">
       <c r="A7" s="1">
         <v>26000</v>
       </c>
@@ -820,7 +1425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" ht="15" customHeight="1" spans="1:3">
       <c r="A8" s="1">
         <v>6000</v>
       </c>
@@ -831,7 +1436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" ht="15" customHeight="1" spans="1:3">
       <c r="A9" s="1">
         <v>3000</v>
       </c>
@@ -842,7 +1447,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" ht="15" customHeight="1" spans="1:3">
       <c r="A10" s="1">
         <v>2100</v>
       </c>
@@ -853,7 +1458,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" ht="15" customHeight="1" spans="1:3">
       <c r="A11" s="1">
         <v>340</v>
       </c>
@@ -864,7 +1469,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" ht="15" customHeight="1" spans="1:3">
       <c r="A12" s="1">
         <v>200</v>
       </c>
@@ -875,7 +1480,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" ht="15" customHeight="1" spans="1:3">
       <c r="A13" s="1">
         <v>11000</v>
       </c>
@@ -886,7 +1491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" ht="15" customHeight="1" spans="1:3">
       <c r="A14" s="1">
         <v>5000</v>
       </c>
@@ -897,7 +1502,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" ht="15" customHeight="1" spans="1:3">
       <c r="A15" s="1">
         <v>755</v>
       </c>
@@ -908,7 +1513,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" ht="15" customHeight="1" spans="1:3">
       <c r="A16" s="1">
         <v>190</v>
       </c>
@@ -919,7 +1524,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" ht="15" customHeight="1" spans="1:3">
       <c r="A17" s="1">
         <v>405.9</v>
       </c>
@@ -930,7 +1535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" ht="15" customHeight="1" spans="1:3">
       <c r="A18" s="1">
         <v>228</v>
       </c>
@@ -941,7 +1546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" ht="15" customHeight="1" spans="1:3">
       <c r="A19" s="1">
         <v>639.5</v>
       </c>
@@ -952,9 +1557,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" ht="15" customHeight="1" spans="1:3">
       <c r="A20" s="1">
-        <v>1259.0999999999999</v>
+        <v>1259.1</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -963,18 +1568,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" ht="15" customHeight="1" spans="1:3">
       <c r="A21" s="1">
         <v>1000</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" ht="15" customHeight="1" spans="1:3">
       <c r="A22" s="1">
         <v>13260</v>
       </c>
@@ -985,7 +1590,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" ht="15" customHeight="1" spans="1:3">
       <c r="A23" s="1">
         <v>47.97</v>
       </c>
@@ -996,9 +1601,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" ht="15" customHeight="1" spans="1:3">
       <c r="A24" s="1">
-        <v>276.10000000000002</v>
+        <v>276.1</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1007,217 +1612,217 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" ht="15" customHeight="1" spans="1:3">
       <c r="A25" s="1">
         <v>6000</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" ht="15" customHeight="1" spans="1:3">
       <c r="A26" s="1">
         <v>640</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" ht="15" customHeight="1" spans="1:3">
       <c r="A27" s="1">
         <v>500</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" ht="15" customHeight="1" spans="1:3">
       <c r="A28" s="1">
         <v>600</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" ht="15" customHeight="1" spans="1:3">
       <c r="A29" s="1">
         <v>938</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" ht="15" customHeight="1" spans="1:3">
       <c r="A30" s="1">
         <v>1000</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" ht="15" customHeight="1" spans="1:3">
       <c r="A31" s="1">
         <v>60.5</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" ht="15" customHeight="1" spans="1:3">
       <c r="A32" s="1">
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" ht="15" customHeight="1" spans="1:3">
       <c r="A33" s="1">
         <v>42.16</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" ht="15" customHeight="1" spans="1:3">
       <c r="A34" s="1">
         <v>1000</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" ht="15" customHeight="1" spans="1:3">
       <c r="A35" s="3">
         <v>500</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" ht="15" customHeight="1" spans="1:3">
       <c r="A36" s="3">
         <v>1300</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="B36" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" ht="15" customHeight="1" spans="1:3">
       <c r="A37" s="3">
         <v>253.84</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="13" t="s">
+      <c r="B37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" ht="15" customHeight="1" spans="1:3">
       <c r="A38" s="3">
         <v>1000</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="B38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" ht="15" customHeight="1" spans="1:3">
       <c r="A39" s="3">
         <v>355.3</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="13" t="s">
+      <c r="B39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" ht="15" customHeight="1" spans="1:3">
       <c r="A40" s="3">
         <v>3000</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="13" t="s">
+      <c r="B40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="14">
+    <row r="41" ht="15" customHeight="1" spans="1:3">
+      <c r="A41" s="5">
         <v>174</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="B41" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="14">
+    <row r="42" ht="15" customHeight="1" spans="1:3">
+      <c r="A42" s="5">
         <v>33.6</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="C42" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1"/>
+    <row r="44" ht="15" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B42 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B42 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1225,21 +1830,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>4</v>
@@ -1248,7 +1853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" s="1">
         <v>4333</v>
       </c>
@@ -1256,21 +1861,21 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" s="1">
         <v>12000</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="1">
         <v>1000</v>
       </c>
@@ -1281,7 +1886,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" customHeight="1" spans="1:3">
       <c r="A5" s="1">
         <v>13260</v>
       </c>
@@ -1292,7 +1897,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" customHeight="1" spans="1:3">
       <c r="A6" s="1">
         <v>600</v>
       </c>
@@ -1303,7 +1908,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" customHeight="1" spans="1:3">
       <c r="A7" s="1">
         <v>938</v>
       </c>
@@ -1314,7 +1919,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="1">
         <v>1000</v>
       </c>
@@ -1325,7 +1930,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" customHeight="1" spans="1:3">
       <c r="A9" s="1">
         <v>60.5</v>
       </c>
@@ -1336,7 +1941,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" customHeight="1" spans="1:3">
       <c r="A10" s="1">
         <v>162.41</v>
       </c>
@@ -1347,7 +1952,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" customHeight="1" spans="1:3">
       <c r="A11" s="1">
         <v>42.16</v>
       </c>
@@ -1358,7 +1963,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" customHeight="1" spans="1:3">
       <c r="A12" s="1">
         <v>1000</v>
       </c>
@@ -1369,7 +1974,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" customHeight="1" spans="1:3">
       <c r="A13" s="3">
         <v>1300</v>
       </c>
@@ -1377,10 +1982,10 @@
         <v>25</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:3">
       <c r="A14" s="3">
         <v>253.84</v>
       </c>
@@ -1391,7 +1996,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" customHeight="1" spans="1:3">
       <c r="A15" s="3">
         <v>1000</v>
       </c>
@@ -1402,7 +2007,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" customHeight="1" spans="1:3">
       <c r="A16" s="3">
         <v>355.3</v>
       </c>
@@ -1413,7 +2018,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" customHeight="1" spans="1:3">
       <c r="A17" s="3">
         <v>3000</v>
       </c>
@@ -1424,127 +2029,127 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="14">
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="5">
         <v>174</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="17" t="s">
+      <c r="B18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="14">
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="5">
         <v>33.6</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
+      <c r="C19" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="6" t="s">
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="7">
-        <v>6596.29</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>48</v>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="9">
+        <v>7659.65</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="7">
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="9">
         <v>0</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>49</v>
+      <c r="B24" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="7">
-        <v>10263.040000000001</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>50</v>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="9">
+        <v>14184.78</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="7">
-        <v>7245.93</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>51</v>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="9">
+        <v>10203.28</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="8">
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="10">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>40512.810000000005</v>
-      </c>
-      <c r="C29" s="9"/>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="8">
+        <v>40512.81</v>
+      </c>
+      <c r="C29" s="11"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="10">
         <f>SUM(营业额明细表[营业额明细])</f>
-        <v>24105.260000000002</v>
-      </c>
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="10"/>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>32047.71</v>
+      </c>
+      <c r="C30" s="12"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:3">
+      <c r="A31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="12"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:1">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19">
+      <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15820" activeTab="1"/>
+    <workbookView windowHeight="15860"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="57">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -195,12 +195,12 @@
   <numFmts count="6">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,13 +216,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,14 +246,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,76 +260,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -329,14 +270,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -357,6 +291,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -364,6 +313,51 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -374,25 +368,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,157 +542,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,7 +605,42 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,192 +659,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -827,10 +821,10 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -852,8 +846,8 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1035,8 +1029,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C42" totalsRowShown="0">
-  <autoFilter ref="A5:C42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
+  <autoFilter ref="A5:C43"/>
   <tableColumns count="3">
     <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
     <tableColumn id="2" name="分类" dataDxfId="1"/>
@@ -1059,8 +1053,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C19" totalsRowShown="0">
-  <autoFilter ref="A1:C19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C20" totalsRowShown="0">
+  <autoFilter ref="A1:C20"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1379,7 +1373,7 @@
       </c>
       <c r="C2" s="12">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99261.38</v>
+        <v>99761.38</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:3">
@@ -1388,7 +1382,7 @@
       </c>
       <c r="C3" s="12">
         <f>C1-C2</f>
-        <v>738.619999999981</v>
+        <v>238.619999999981</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
@@ -1789,35 +1783,45 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:3">
-      <c r="A41" s="5">
+      <c r="A41" s="3">
         <v>174</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="17" t="s">
+      <c r="B41" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:3">
-      <c r="A42" s="5">
+      <c r="A42" s="3">
         <v>33.6</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1"/>
+    <row r="43" ht="15" customHeight="1" spans="1:3">
+      <c r="A43" s="5">
+        <v>500</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="44" ht="15" customHeight="1"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B42 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2030,31 +2034,37 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="5">
+      <c r="A18" s="3">
         <v>174</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="B18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="5">
+      <c r="A19" s="3">
         <v>33.6</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="5">
+        <v>500</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
       <c r="A21" s="7"/>
@@ -2114,7 +2124,7 @@
       </c>
       <c r="B29" s="10">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>40512.81</v>
+        <v>41012.81</v>
       </c>
       <c r="C29" s="11"/>
     </row>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15860"/>
+    <workbookView windowWidth="28000" windowHeight="15860" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
-    <sheet name="流水-202602" sheetId="2" r:id="rId2"/>
+    <sheet name="流水-202602 (2)" sheetId="3" r:id="rId2"/>
+    <sheet name="流水-202603" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="59">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -186,6 +187,12 @@
   </si>
   <si>
     <t>净利润</t>
+  </si>
+  <si>
+    <t>3员工工资</t>
+  </si>
+  <si>
+    <t>首批食材</t>
   </si>
 </sst>
 </file>
@@ -193,12 +200,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -216,24 +223,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -244,9 +244,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,9 +285,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -276,8 +299,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,24 +343,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,36 +365,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -368,49 +375,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,133 +543,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,8 +572,58 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -586,61 +643,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,190 +669,182 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -912,7 +911,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -948,7 +947,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -985,7 +984,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1041,8 +1040,32 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A22:C26" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A22:C26" totalsRowShown="0">
   <autoFilter ref="A22:C26"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="营业额明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
+  <autoFilter ref="A1:C20"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="成本明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A6:C10" totalsRowShown="0">
+  <autoFilter ref="A6:C10"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1052,9 +1075,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C20" totalsRowShown="0">
-  <autoFilter ref="A1:C20"/>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C4" totalsRowShown="0">
+  <autoFilter ref="A1:C4"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1354,43 +1377,43 @@
   <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="7" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="7">
         <v>100000</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="8">
         <f>SUM(成本明细[金额(元)])</f>
         <v>99761.38</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="8">
         <f>C1-C2</f>
         <v>238.619999999981</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1569,7 +1592,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1613,7 +1636,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="11" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1624,7 +1647,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="11" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1635,7 +1658,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1646,7 +1669,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="11" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1657,7 +1680,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1668,7 +1691,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1679,7 +1702,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1690,7 +1713,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="11" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1701,7 +1724,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1712,106 +1735,106 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:3">
-      <c r="A35" s="3">
+      <c r="A35" s="9">
         <v>500</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:3">
-      <c r="A36" s="3">
+      <c r="A36" s="9">
         <v>1300</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:3">
-      <c r="A37" s="3">
+      <c r="A37" s="9">
         <v>253.84</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:3">
-      <c r="A38" s="3">
+      <c r="A38" s="9">
         <v>1000</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="15" t="s">
+      <c r="B38" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:3">
-      <c r="A39" s="3">
+      <c r="A39" s="9">
         <v>355.3</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="B39" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:3">
-      <c r="A40" s="3">
+      <c r="A40" s="9">
         <v>3000</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="15" t="s">
+      <c r="B40" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:3">
-      <c r="A41" s="3">
+      <c r="A41" s="9">
         <v>174</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="15" t="s">
+      <c r="B41" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:3">
-      <c r="A42" s="3">
+      <c r="A42" s="9">
         <v>33.6</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:3">
-      <c r="A43" s="5">
+      <c r="A43" s="9">
         <v>500</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="17" t="s">
+      <c r="B43" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1979,32 +2002,32 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="3">
+      <c r="A13" s="9">
         <v>1300</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="3">
+      <c r="A14" s="9">
         <v>253.84</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="3">
+      <c r="A15" s="9">
         <v>1000</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2012,70 +2035,70 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="3">
+      <c r="A16" s="9">
         <v>355.3</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="3">
+      <c r="A17" s="9">
         <v>3000</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="3">
+      <c r="A18" s="9">
         <v>174</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="3">
+      <c r="A19" s="9">
         <v>33.6</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="5">
+      <c r="A20" s="9">
         <v>500</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="B20" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -2083,66 +2106,66 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="9">
+      <c r="A23" s="5">
         <v>7659.65</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="2"/>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="9">
+      <c r="A24" s="5">
         <v>0</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C24" s="2"/>
     </row>
     <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="9">
+      <c r="A25" s="5">
         <v>14184.78</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="2"/>
     </row>
     <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="9">
+      <c r="A26" s="5">
         <v>10203.28</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C26" s="2"/>
     </row>
     <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="10">
-        <f>SUM(成本明细表[成本明细])</f>
+      <c r="B29" s="6">
+        <f>SUM(成本明细表_6[成本明细])</f>
         <v>41012.81</v>
       </c>
-      <c r="C29" s="11"/>
+      <c r="C29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="10">
-        <f>SUM(营业额明细表[营业额明细])</f>
+      <c r="B30" s="6">
+        <f>SUM(营业额明细表_5[营业额明细])</f>
         <v>32047.71</v>
       </c>
-      <c r="C30" s="12"/>
+      <c r="C30" s="8"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="12"/>
+      <c r="C31" s="8"/>
     </row>
     <row r="32" customHeight="1" spans="1:1">
       <c r="A32" t="s">
@@ -2165,4 +2188,159 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="21.125" customWidth="1"/>
+    <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="3" max="3" width="23.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="1">
+        <v>4333</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:3">
+      <c r="A3" s="1">
+        <v>18000</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:3">
+      <c r="A4" s="1">
+        <v>9240</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="5">
+        <v>0</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="5">
+        <v>0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:3">
+      <c r="A9" s="5">
+        <v>0</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:3">
+      <c r="A10" s="5">
+        <v>0</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="6">
+        <f>SUM(成本明细表[成本明细])</f>
+        <v>31573</v>
+      </c>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="6">
+        <f>SUM(营业额明细表[营业额明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:1">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B2:B3">
+      <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15860" activeTab="2"/>
+    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
+    <workbookView windowWidth="28000" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="67">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -162,9 +162,45 @@
     <t>老池自购食材</t>
   </si>
   <si>
+    <t>美团推广费</t>
+  </si>
+  <si>
     <t>营业额明细</t>
   </si>
   <si>
+    <t>微信堂食</t>
+  </si>
+  <si>
+    <t>支付宝堂食</t>
+  </si>
+  <si>
+    <t>京东外卖</t>
+  </si>
+  <si>
+    <t>淘宝外卖</t>
+  </si>
+  <si>
+    <t>美团外卖</t>
+  </si>
+  <si>
+    <t>成本合计</t>
+  </si>
+  <si>
+    <t>营业额合计</t>
+  </si>
+  <si>
+    <t>利润</t>
+  </si>
+  <si>
+    <t>卡内结余</t>
+  </si>
+  <si>
+    <t>3员工工资</t>
+  </si>
+  <si>
+    <t>首批食材</t>
+  </si>
+  <si>
     <t>堂食</t>
   </si>
   <si>
@@ -177,22 +213,10 @@
     <t>美团</t>
   </si>
   <si>
-    <t>成本合计</t>
-  </si>
-  <si>
-    <t>营业额合计</t>
-  </si>
-  <si>
     <t>毛利润</t>
   </si>
   <si>
     <t>净利润</t>
-  </si>
-  <si>
-    <t>3员工工资</t>
-  </si>
-  <si>
-    <t>首批食材</t>
   </si>
 </sst>
 </file>
@@ -200,12 +224,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -238,13 +262,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -252,26 +269,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -292,23 +301,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -322,7 +323,53 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,31 +383,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -387,43 +411,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,127 +573,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,15 +602,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -598,6 +613,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,17 +652,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -639,15 +663,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -666,151 +681,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1040,8 +1064,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A22:C26" totalsRowShown="0">
-  <autoFilter ref="A22:C26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A23:C28" totalsRowShown="0">
+  <autoFilter ref="A23:C28"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细"/>
     <tableColumn id="2" name="分类"/>
@@ -1052,8 +1076,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
-  <autoFilter ref="A1:C20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C21" totalsRowShown="0">
+  <autoFilter ref="A1:C21"/>
   <tableColumns count="3">
     <tableColumn id="1" name="成本明细"/>
     <tableColumn id="2" name="分类"/>
@@ -1374,7 +1398,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="23.75" style="3" customWidth="1"/>
@@ -1838,7 +1862,6 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
@@ -1861,7 +1884,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -2090,33 +2113,35 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="2"/>
+      <c r="A21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="5">
-        <v>7659.65</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="2"/>
     </row>
     <row r="24" customHeight="1" spans="1:3">
       <c r="A24" s="5">
-        <v>0</v>
+        <v>6370.2</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>50</v>
@@ -2125,7 +2150,7 @@
     </row>
     <row r="25" customHeight="1" spans="1:3">
       <c r="A25" s="5">
-        <v>14184.78</v>
+        <v>1789.99</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>51</v>
@@ -2134,42 +2159,60 @@
     </row>
     <row r="26" customHeight="1" spans="1:3">
       <c r="A26" s="5">
-        <v>10203.28</v>
+        <v>0</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="3" t="s">
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="5">
+        <v>16451.39</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="6">
-        <f>SUM(成本明细表_6[成本明细])</f>
-        <v>41012.81</v>
-      </c>
-      <c r="C29" s="7"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="3" t="s">
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="5">
+        <v>11352.59</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="6">
-        <f>SUM(营业额明细表_5[营业额明细])</f>
-        <v>32047.71</v>
-      </c>
-      <c r="C30" s="8"/>
+      <c r="C28" s="2"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
       <c r="A31" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="8"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:1">
-      <c r="A32" t="s">
+      <c r="B31" s="6">
+        <f>SUM(成本明细表_6[成本明细])</f>
+        <v>42012.81</v>
+      </c>
+      <c r="C31" s="7"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="3" t="s">
         <v>56</v>
+      </c>
+      <c r="B32" s="6">
+        <f>SUM(营业额明细表_5[营业额明细])</f>
+        <v>35964.17</v>
+      </c>
+      <c r="C32" s="8"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="8"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2233,7 +2276,7 @@
         <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
@@ -2244,7 +2287,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:3">
@@ -2254,7 +2297,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>4</v>
@@ -2268,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -2277,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2"/>
     </row>
@@ -2286,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2"/>
     </row>
@@ -2295,13 +2338,13 @@
         <v>0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="13" customHeight="1" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="6">
         <f>SUM(成本明细表[成本明细])</f>
@@ -2311,7 +2354,7 @@
     </row>
     <row r="14" customHeight="1" spans="1:3">
       <c r="A14" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" s="6">
         <f>SUM(营业额明细表[营业额明细])</f>
@@ -2321,13 +2364,13 @@
     </row>
     <row r="15" customHeight="1" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C15" s="8"/>
     </row>
     <row r="16" customHeight="1" spans="1:1">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15820" activeTab="1"/>
+    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="68">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -198,7 +198,10 @@
     <t>3员工工资</t>
   </si>
   <si>
-    <t>首批食材</t>
+    <t>芋头小笼120斤*12，肉燕120斤*22.5，菜探长进货</t>
+  </si>
+  <si>
+    <t>肉片300斤*8，高级肉片199斤*9，香菇小笼100斤*11，肉燕100斤*18，鸡翅320，运费455，硕美进货</t>
   </si>
   <si>
     <t>堂食</t>
@@ -224,12 +227,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -247,7 +250,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,6 +278,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -269,10 +302,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -285,22 +318,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -308,15 +325,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -337,23 +372,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -361,30 +380,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -399,13 +402,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,19 +534,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,19 +570,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,121 +582,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,8 +599,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,50 +646,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -684,166 +670,189 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1088,8 +1097,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A6:C10" totalsRowShown="0">
-  <autoFilter ref="A6:C10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A7:C11" totalsRowShown="0">
+  <autoFilter ref="A7:C11"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1100,8 +1109,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C4" totalsRowShown="0">
-  <autoFilter ref="A1:C4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1401,43 +1410,43 @@
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="3" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7">
+      <c r="C1" s="9">
         <v>100000</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="10">
         <f>SUM(成本明细[金额(元)])</f>
         <v>99761.38</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="10">
         <f>C1-C2</f>
         <v>238.619999999981</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1616,7 +1625,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1660,7 +1669,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1671,7 +1680,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1682,7 +1691,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1693,7 +1702,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1704,7 +1713,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1715,7 +1724,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1726,7 +1735,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="13" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1737,7 +1746,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1748,7 +1757,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1759,106 +1768,106 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:3">
-      <c r="A35" s="9">
+      <c r="A35" s="11">
         <v>500</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:3">
-      <c r="A36" s="9">
+      <c r="A36" s="11">
         <v>1300</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="B36" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:3">
-      <c r="A37" s="9">
+      <c r="A37" s="11">
         <v>253.84</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="13" t="s">
+      <c r="B37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:3">
-      <c r="A38" s="9">
+      <c r="A38" s="11">
         <v>1000</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="B38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:3">
-      <c r="A39" s="9">
+      <c r="A39" s="11">
         <v>355.3</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="13" t="s">
+      <c r="B39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:3">
-      <c r="A40" s="9">
+      <c r="A40" s="11">
         <v>3000</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="13" t="s">
+      <c r="B40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:3">
-      <c r="A41" s="9">
+      <c r="A41" s="11">
         <v>174</v>
       </c>
-      <c r="B41" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="13" t="s">
+      <c r="B41" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:3">
-      <c r="A42" s="9">
+      <c r="A42" s="11">
         <v>33.6</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="15" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:3">
-      <c r="A43" s="9">
+      <c r="A43" s="11">
         <v>500</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="13" t="s">
+      <c r="B43" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2025,32 +2034,32 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="9">
+      <c r="A13" s="11">
         <v>1300</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="9">
+      <c r="A14" s="11">
         <v>253.84</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="9">
+      <c r="A15" s="11">
         <v>1000</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="12" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2058,65 +2067,65 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="9">
+      <c r="A16" s="11">
         <v>355.3</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="9">
+      <c r="A17" s="11">
         <v>3000</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="9">
+      <c r="A18" s="11">
         <v>174</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="9">
+      <c r="A19" s="11">
         <v>33.6</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="9">
+      <c r="A20" s="11">
         <v>500</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="B20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="3">
+      <c r="A21" s="5">
         <v>1000</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2124,15 +2133,15 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="4"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
       <c r="C22" s="2"/>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2140,75 +2149,75 @@
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="5">
+      <c r="A24" s="7">
         <v>6370.2</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C24" s="2"/>
     </row>
     <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="5">
+      <c r="A25" s="7">
         <v>1789.99</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="2"/>
     </row>
     <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="5">
+      <c r="A26" s="7">
         <v>0</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C26" s="2"/>
     </row>
     <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="5">
+      <c r="A27" s="7">
         <v>16451.39</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C27" s="2"/>
     </row>
     <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="5">
+      <c r="A28" s="7">
         <v>11352.59</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C28" s="2"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="8">
         <f>SUM(成本明细表_6[成本明细])</f>
         <v>42012.81</v>
       </c>
-      <c r="C31" s="7"/>
+      <c r="C31" s="9"/>
     </row>
     <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="8">
         <f>SUM(营业额明细表_5[营业额明细])</f>
         <v>35964.17</v>
       </c>
-      <c r="C32" s="8"/>
+      <c r="C32" s="10"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="8"/>
+      <c r="C33" s="10"/>
     </row>
     <row r="35" customHeight="1" spans="1:1">
       <c r="A35" t="s">
@@ -2238,12 +2247,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="23.25" customWidth="1"/>
+    <col min="3" max="3" width="95.5096153846154" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
@@ -2281,7 +2290,7 @@
     </row>
     <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="1">
-        <v>9240</v>
+        <v>4140</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>25</v>
@@ -2291,91 +2300,102 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="3">
+        <v>7886</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="5">
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="7">
         <v>0</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="5">
+      <c r="B8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:3">
+      <c r="A9" s="7">
         <v>0</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="5">
+      <c r="B9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:3">
+      <c r="A10" s="7">
         <v>0</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:3">
-      <c r="A10" s="5">
+      <c r="B10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:3">
+      <c r="A11" s="7">
         <v>0</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="3" t="s">
+      <c r="B11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:3">
+      <c r="A14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B14" s="8">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>31573</v>
-      </c>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="3" t="s">
+        <v>34359</v>
+      </c>
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B15" s="8">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>0</v>
       </c>
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="8"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:1">
-      <c r="A16" t="s">
+      <c r="C15" s="10"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="5" t="s">
         <v>66</v>
+      </c>
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:1">
+      <c r="A17" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B2:B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B5 B2:B3">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1058,6 +1058,53 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4381500"/>
+          <a:ext cx="9734550" cy="4010025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2401,9 +2448,10 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06D4F65-277A-43EB-B8BF-B91B85426336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
+    <workbookView xWindow="2580" yWindow="1305" windowWidth="35070" windowHeight="19335" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="流水-202602 (2)" sheetId="3" r:id="rId2"/>
     <sheet name="流水-202603" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="72">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -220,21 +226,33 @@
   </si>
   <si>
     <t>净利润</t>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE食品保鲜袋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>食材</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鸡面补货</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,344 +268,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -595,253 +305,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -871,184 +339,142 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <name val="宋体"/>
+        <charset val="134"/>
         <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
         <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
         <name val="宋体"/>
+        <charset val="134"/>
         <scheme val="none"/>
-        <charset val="134"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
       </font>
       <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1056,34 +482,43 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1108,60 +543,60 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
-  <autoFilter ref="A5:C43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
+  <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
-    <tableColumn id="2" name="分类" dataDxfId="1"/>
-    <tableColumn id="3" name="说明" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A23:C28" totalsRowShown="0">
-  <autoFilter ref="A23:C28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A25:C30" totalsRowShown="0">
+  <autoFilter ref="A25:C30" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="营业额明细"/>
-    <tableColumn id="2" name="分类"/>
-    <tableColumn id="3" name="说明"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C21" totalsRowShown="0">
-  <autoFilter ref="A1:C21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C23" totalsRowShown="0">
+  <autoFilter ref="A1:C23" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="成本明细"/>
-    <tableColumn id="2" name="分类"/>
-    <tableColumn id="3" name="说明"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A7:C11" totalsRowShown="0">
-  <autoFilter ref="A7:C11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A12:C16" totalsRowShown="0">
+  <autoFilter ref="A12:C16" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
-    <tableColumn id="2" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" name="说明" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C5" totalsRowShown="0">
-  <autoFilter ref="A1:C5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C7" totalsRowShown="0">
+  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
-    <tableColumn id="4" name="分类" dataDxfId="7"/>
-    <tableColumn id="1" name="说明" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1446,23 +881,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1470,26 +906,26 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="10">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99761.38</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:3">
+        <v>99761.380000000019</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="10">
         <f>C1-C2</f>
-        <v>238.619999999981</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="5" ht="15" customHeight="1" spans="1:3">
+        <v>238.61999999998079</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1500,7 +936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>10000</v>
       </c>
@@ -1511,7 +947,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>26000</v>
       </c>
@@ -1522,7 +958,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>6000</v>
       </c>
@@ -1533,7 +969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>3000</v>
       </c>
@@ -1544,7 +980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>2100</v>
       </c>
@@ -1555,7 +991,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>340</v>
       </c>
@@ -1566,7 +1002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>200</v>
       </c>
@@ -1577,7 +1013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>11000</v>
       </c>
@@ -1588,7 +1024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>5000</v>
       </c>
@@ -1599,7 +1035,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>755</v>
       </c>
@@ -1610,7 +1046,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>190</v>
       </c>
@@ -1621,7 +1057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>405.9</v>
       </c>
@@ -1632,7 +1068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>228</v>
       </c>
@@ -1643,7 +1079,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>639.5</v>
       </c>
@@ -1654,9 +1090,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
-        <v>1259.1</v>
+        <v>1259.0999999999999</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -1665,18 +1101,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>1000</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>13260</v>
       </c>
@@ -1687,7 +1123,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>47.97</v>
       </c>
@@ -1698,9 +1134,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
-        <v>276.1</v>
+        <v>276.10000000000002</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1709,226 +1145,226 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>6000</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>640</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>500</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>600</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>938</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:3">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>1000</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:3">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>60.5</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:3">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:3">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>42.16</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:3">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>1000</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:3">
-      <c r="A35" s="11">
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="3">
         <v>500</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:3">
-      <c r="A36" s="11">
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="3">
         <v>1300</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:3">
-      <c r="A37" s="11">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="3">
         <v>253.84</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:3">
-      <c r="A38" s="11">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="3">
         <v>1000</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="15" t="s">
+      <c r="B38" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:3">
-      <c r="A39" s="11">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="3">
         <v>355.3</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="B39" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:3">
-      <c r="A40" s="11">
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="3">
         <v>3000</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="15" t="s">
+      <c r="B40" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:3">
-      <c r="A41" s="11">
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="3">
         <v>174</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="15" t="s">
+      <c r="B41" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:3">
-      <c r="A42" s="11">
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="3">
         <v>33.6</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:3">
-      <c r="A43" s="11">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="3">
         <v>500</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="15" t="s">
+      <c r="B43" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1936,19 +1372,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1959,7 +1395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>4333</v>
       </c>
@@ -1970,7 +1406,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>12000</v>
       </c>
@@ -1981,7 +1417,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:3">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>1000</v>
       </c>
@@ -1992,7 +1428,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:3">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>13260</v>
       </c>
@@ -2003,7 +1439,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>600</v>
       </c>
@@ -2014,7 +1450,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>938</v>
       </c>
@@ -2025,7 +1461,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>1000</v>
       </c>
@@ -2036,7 +1472,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>60.5</v>
       </c>
@@ -2047,7 +1483,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>162.41</v>
       </c>
@@ -2058,7 +1494,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>42.16</v>
       </c>
@@ -2069,7 +1505,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>1000</v>
       </c>
@@ -2080,95 +1516,95 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="11">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="3">
         <v>1300</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="12" t="s">
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="11">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="3">
         <v>253.84</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="B14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="11">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="3">
         <v>1000</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="11">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="3">
         <v>355.3</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="11">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="3">
         <v>3000</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="12" t="s">
+      <c r="B17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="11">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="3">
         <v>174</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="12" t="s">
+      <c r="B18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="11">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="3">
         <v>33.6</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="11">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="3">
         <v>500</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="B20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5">
         <v>1000</v>
       </c>
@@ -2179,109 +1615,119 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="5" t="s">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="2"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="15"/>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="2"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="7">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="7">
         <v>6370.2</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="7">
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="7">
         <v>1789.99</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B27" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="7">
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="7">
         <v>0</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B28" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="7">
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="7">
         <v>16451.39</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B29" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="7">
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="7">
         <v>11352.59</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B30" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="5" t="s">
+      <c r="C30" s="2"/>
+    </row>
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B33" s="8">
         <f>SUM(成本明细表_6[成本明细])</f>
-        <v>42012.81</v>
-      </c>
-      <c r="C31" s="9"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="5" t="s">
+        <v>42012.810000000005</v>
+      </c>
+      <c r="C33" s="9"/>
+    </row>
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B34" s="8">
         <f>SUM(营业额明细表_5[营业额明细])</f>
         <v>35964.17</v>
       </c>
-      <c r="C32" s="10"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="5" t="s">
+      <c r="C34" s="10"/>
+    </row>
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="10"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:1">
-      <c r="A35" t="s">
+      <c r="C35" s="10"/>
+    </row>
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
@@ -2290,19 +1736,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="95.5096153846154" customWidth="1"/>
+    <col min="3" max="3" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -2313,7 +1759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>4333</v>
       </c>
@@ -2324,7 +1770,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>18000</v>
       </c>
@@ -2335,7 +1781,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:3">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>4140</v>
       </c>
@@ -2346,7 +1792,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:3">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3">
         <v>7886</v>
       </c>
@@ -2357,97 +1803,134 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="5" t="s">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="16">
+        <v>28.64</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="16">
+        <v>44.48</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="7">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7">
         <v>0</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B13" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="7">
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="7">
         <v>0</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B14" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:3">
-      <c r="A10" s="7">
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7">
         <v>0</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:3">
-      <c r="A11" s="7">
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7">
         <v>0</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="5" t="s">
+      <c r="C16" s="2"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B19" s="8">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>34359</v>
-      </c>
-      <c r="C14" s="9"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="5" t="s">
+        <v>34432.120000000003</v>
+      </c>
+      <c r="C19" s="9"/>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B20" s="8">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>0</v>
       </c>
-      <c r="C15" s="10"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="5" t="s">
+      <c r="C20" s="10"/>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="10"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:1">
-      <c r="A17" t="s">
+      <c r="C21" s="10"/>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B5 B2:B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B10" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
   <tableParts count="2">
     <tablePart r:id="rId2"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06D4F65-277A-43EB-B8BF-B91B85426336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB57DF75-57C0-40BF-9500-38A08C5A8FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="1305" windowWidth="35070" windowHeight="19335" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="35070" windowHeight="19335" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="75">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -241,6 +241,18 @@
   </si>
   <si>
     <t>火鸡面补货</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>食材</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>快驴补货</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>首批调味粉</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -264,6 +276,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -591,8 +604,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C7" totalsRowShown="0">
-  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C9" totalsRowShown="0">
+  <autoFilter ref="A1:C9" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
@@ -1826,14 +1839,26 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="A8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="A9" s="3">
+        <v>23</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
@@ -1898,7 +1923,7 @@
       </c>
       <c r="B19" s="8">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>34432.120000000003</v>
+        <v>37455.120000000003</v>
       </c>
       <c r="C19" s="9"/>
     </row>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB57DF75-57C0-40BF-9500-38A08C5A8FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B41CC5-6A5A-4C50-BA61-B1A8FD4686A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="35070" windowHeight="19335" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,24 @@
     <sheet name="流水-202603" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="81">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -253,6 +266,30 @@
   </si>
   <si>
     <t>首批调味粉</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000圆打包盒1000个</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1250圆打包盒450个</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡翅10斤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>普福店调货补给老李（此处被老李算错账）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>盒子</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鸡面拼多多补货5箱150袋</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -264,7 +301,7 @@
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +338,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -322,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -355,16 +401,11 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -372,6 +413,23 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <alignment horizontal="left"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -400,20 +458,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -508,13 +552,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -580,8 +624,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C23" totalsRowShown="0">
-  <autoFilter ref="A1:C23" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C21" totalsRowShown="0">
+  <autoFilter ref="A1:C21" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
@@ -592,8 +636,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A12:C16" totalsRowShown="0">
-  <autoFilter ref="A12:C16" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A23:C27" totalsRowShown="0">
+  <autoFilter ref="A23:C27" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="4"/>
@@ -604,12 +648,12 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C9" totalsRowShown="0">
-  <autoFilter ref="A1:C9" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C15" totalsRowShown="0">
+  <autoFilter ref="A1:C15" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1629,14 +1673,14 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="2"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="2"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5"/>
@@ -1656,7 +1700,7 @@
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7">
-        <v>6370.2</v>
+        <v>6683.96</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>50</v>
@@ -1665,7 +1709,7 @@
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7">
-        <v>1789.99</v>
+        <v>1861.8</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>51</v>
@@ -1683,7 +1727,7 @@
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7">
-        <v>16451.39</v>
+        <v>19919.099999999999</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>53</v>
@@ -1692,7 +1736,7 @@
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="7">
-        <v>11352.59</v>
+        <v>13970.88</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>54</v>
@@ -1715,7 +1759,7 @@
       </c>
       <c r="B34" s="8">
         <f>SUM(营业额明细表_5[营业额明细])</f>
-        <v>35964.17</v>
+        <v>42435.74</v>
       </c>
       <c r="C34" s="10"/>
     </row>
@@ -1753,7 +1797,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -1762,7 +1806,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1773,7 +1817,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="1">
+      <c r="A2" s="16">
         <v>4333</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1784,7 +1828,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1">
+      <c r="A3" s="16">
         <v>18000</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1795,7 +1839,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1">
+      <c r="A4" s="16">
         <v>4140</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1806,8 +1850,8 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="3">
-        <v>7886</v>
+      <c r="A5" s="16">
+        <v>7866</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>25</v>
@@ -1820,10 +1864,10 @@
       <c r="A6" s="16">
         <v>28.64</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="14" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1831,15 +1875,15 @@
       <c r="A7" s="16">
         <v>44.48</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="3">
+      <c r="A8" s="16">
         <v>3000</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1850,7 +1894,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="3">
+      <c r="A9" s="16">
         <v>23</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -1861,97 +1905,188 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="16">
+        <v>234</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="5" t="s">
+      <c r="A11" s="16">
+        <v>385</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="16">
+        <v>295</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="16">
+        <v>718</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="16">
+        <v>57.6</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="16">
+        <v>302.5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="16"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="16"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="16"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="16"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="16"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="16"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B23" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="7">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="7">
         <v>0</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="7">
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="7">
         <v>0</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B25" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="7">
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="7">
         <v>0</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="7">
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="7">
         <v>0</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B27" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="5" t="s">
+      <c r="C27" s="2"/>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B30" s="8">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>37455.120000000003</v>
-      </c>
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="5" t="s">
+        <v>39427.22</v>
+      </c>
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B31" s="8">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>0</v>
       </c>
-      <c r="C20" s="10"/>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="5" t="s">
+      <c r="C31" s="10"/>
+    </row>
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="10"/>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
+      <c r="C32" s="10"/>
+    </row>
+    <row r="33" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B10" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B21" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B41CC5-6A5A-4C50-BA61-B1A8FD4686A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973372E3-AD87-4924-A2FA-DB1589430361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
-    <sheet name="流水-202602 (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="流水-202603" sheetId="2" r:id="rId3"/>
+    <sheet name="2026-02流水 " sheetId="3" r:id="rId2"/>
+    <sheet name="2026-03流水" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -181,9 +181,6 @@
     <t>老池自购食材</t>
   </si>
   <si>
-    <t>美团推广费</t>
-  </si>
-  <si>
     <t>营业额明细</t>
   </si>
   <si>
@@ -212,9 +209,6 @@
   </si>
   <si>
     <t>卡内结余</t>
-  </si>
-  <si>
-    <t>3员工工资</t>
   </si>
   <si>
     <t>芋头小笼120斤*12，肉燕120斤*22.5，菜探长进货</t>
@@ -261,14 +255,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>快驴补货</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>首批调味粉</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>1000圆打包盒1000个</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -285,11 +271,27 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>盒子</t>
+    <t>美团外卖推广</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>火鸡面拼多多补货5箱150袋</t>
+    <t>快驴充值</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>员工工资</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>食材调味粉</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>外卖盒子临时补货</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鸡面拼多多补货5箱共150袋</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -368,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -408,28 +410,14 @@
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-      <alignment horizontal="left"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -458,6 +446,23 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -552,13 +557,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -612,8 +617,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A25:C30" totalsRowShown="0">
-  <autoFilter ref="A25:C30" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A24:C29" totalsRowShown="0">
+  <autoFilter ref="A24:C29" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类"/>
@@ -624,8 +629,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C21" totalsRowShown="0">
-  <autoFilter ref="A1:C21" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
+  <autoFilter ref="A1:C20" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
@@ -636,8 +641,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A23:C27" totalsRowShown="0">
-  <autoFilter ref="A23:C27" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A20:C24" totalsRowShown="0">
+  <autoFilter ref="A20:C24" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="4"/>
@@ -648,12 +653,12 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C15" totalsRowShown="0">
-  <autoFilter ref="A1:C15" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C16" totalsRowShown="0">
+  <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1433,7 +1438,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -1662,15 +1667,9 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="5">
-        <v>1000</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
@@ -1683,24 +1682,28 @@
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="2"/>
+      <c r="A24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="7">
+        <v>6683.96</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7">
-        <v>6683.96</v>
+        <v>1861.8</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>50</v>
@@ -1709,7 +1712,7 @@
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7">
-        <v>1861.8</v>
+        <v>0</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>51</v>
@@ -1718,7 +1721,7 @@
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="7">
-        <v>0</v>
+        <v>19919.099999999999</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>52</v>
@@ -1727,51 +1730,42 @@
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7">
-        <v>19919.099999999999</v>
+        <v>13970.88</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="7">
-        <v>13970.88</v>
-      </c>
-      <c r="B30" s="6" t="s">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="2"/>
+      <c r="B32" s="8">
+        <f>SUM(成本明细表_6[成本明细])</f>
+        <v>41012.810000000005</v>
+      </c>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B33" s="8">
-        <f>SUM(成本明细表_6[成本明细])</f>
-        <v>42012.810000000005</v>
-      </c>
-      <c r="C33" s="9"/>
+        <f>SUM(营业额明细表_5[营业额明细])</f>
+        <v>42435.74</v>
+      </c>
+      <c r="C33" s="10"/>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="8">
-        <f>SUM(营业额明细表_5[营业额明细])</f>
-        <v>42435.74</v>
-      </c>
       <c r="C34" s="10"/>
     </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="5" t="s">
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" t="s">
         <v>57</v>
-      </c>
-      <c r="C35" s="10"/>
-    </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1797,7 +1791,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -1834,8 +1828,8 @@
       <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>59</v>
+      <c r="C3" s="17" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1846,7 +1840,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1857,7 +1851,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1865,10 +1859,10 @@
         <v>28.64</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1876,10 +1870,10 @@
         <v>44.48</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1887,10 +1881,10 @@
         <v>3000</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1898,10 +1892,10 @@
         <v>23</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1912,7 +1906,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1923,7 +1917,7 @@
         <v>25</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1934,7 +1928,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1945,7 +1939,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1971,9 +1965,15 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="16"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
+      <c r="A16" s="16">
+        <v>1000</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="16"/>
@@ -1986,107 +1986,92 @@
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="16"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="16"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
+      <c r="A20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="16"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
+      <c r="A21" s="7">
+        <v>0</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="7">
+        <v>0</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="5" t="s">
-        <v>49</v>
+      <c r="A23" s="7">
+        <v>0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7">
         <v>0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="7">
-        <v>0</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="7">
-        <v>0</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="2"/>
-    </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="7">
-        <v>0</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="5" t="s">
+      <c r="A27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="8">
+        <f>SUM(成本明细表[成本明细])</f>
+        <v>40427.22</v>
+      </c>
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="8">
-        <f>SUM(成本明细表[成本明细])</f>
-        <v>39427.22</v>
-      </c>
-      <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="B28" s="8">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>0</v>
       </c>
-      <c r="C31" s="10"/>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="10"/>
-    </row>
-    <row r="33" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" t="s">
-        <v>67</v>
+      <c r="C28" s="10"/>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="10"/>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B21" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B18" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973372E3-AD87-4924-A2FA-DB1589430361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC284339-211C-435B-8831-E0A873EF880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,14 +255,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1000圆打包盒1000个</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1250圆打包盒450个</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>鸡翅10斤</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -292,6 +284,14 @@
   </si>
   <si>
     <t>火鸡面拼多多补货5箱共150袋</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000圆打包盒1000个，0.385/个</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1280圆打包盒900个，0.52/个</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -421,6 +421,42 @@
     <dxf>
       <font>
         <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
@@ -502,42 +538,6 @@
       </font>
       <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -608,9 +608,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
   <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -644,9 +644,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A20:C24" totalsRowShown="0">
   <autoFilter ref="A20:C24" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -656,9 +656,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C16" totalsRowShown="0">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1829,7 +1829,7 @@
         <v>45</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1884,7 +1884,7 @@
         <v>70</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1895,18 +1895,18 @@
         <v>70</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="16">
-        <v>234</v>
+        <v>468</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1917,7 +1917,7 @@
         <v>25</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1928,7 +1928,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1939,7 +1939,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1950,7 +1950,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1961,7 +1961,7 @@
         <v>25</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1972,7 +1972,7 @@
         <v>32</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B27" s="8">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>40427.22</v>
+        <v>40661.22</v>
       </c>
       <c r="C27" s="9"/>
     </row>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,41 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC284339-211C-435B-8831-E0A873EF880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="2026-02流水 " sheetId="3" r:id="rId2"/>
     <sheet name="2026-03流水" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="77">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -211,12 +192,45 @@
     <t>卡内结余</t>
   </si>
   <si>
+    <t>员工工资</t>
+  </si>
+  <si>
     <t>芋头小笼120斤*12，肉燕120斤*22.5，菜探长进货</t>
   </si>
   <si>
     <t>肉片300斤*8，高级肉片199斤*9，香菇小笼100斤*11，肉燕100斤*18，鸡翅320，运费455，硕美进货</t>
   </si>
   <si>
+    <t>PE食品保鲜袋</t>
+  </si>
+  <si>
+    <t>食材调味粉</t>
+  </si>
+  <si>
+    <t>1280圆打包盒900个，0.52/个</t>
+  </si>
+  <si>
+    <t>1000圆打包盒1000个，0.385/个</t>
+  </si>
+  <si>
+    <t>鸡翅10斤</t>
+  </si>
+  <si>
+    <t>普福店调货补给老李（此处被老李算错账）</t>
+  </si>
+  <si>
+    <t>外卖盒子临时补货</t>
+  </si>
+  <si>
+    <t>火鸡面拼多多补货5箱共150袋</t>
+  </si>
+  <si>
+    <t>美团外卖推广</t>
+  </si>
+  <si>
+    <t>750圆打包盒600个，0.375/个</t>
+  </si>
+  <si>
     <t>堂食</t>
   </si>
   <si>
@@ -233,77 +247,36 @@
   </si>
   <si>
     <t>净利润</t>
-  </si>
-  <si>
-    <t>其他</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE食品保鲜袋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>食材</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>火鸡面补货</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>食材</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>鸡翅10斤</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>普福店调货补给老李（此处被老李算错账）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>美团外卖推广</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>快驴充值</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>员工工资</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>食材调味粉</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>外卖盒子临时补货</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>火鸡面拼多多补货5箱共150袋</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000圆打包盒1000个，0.385/个</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1280圆打包盒900个，0.52/个</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,50 +288,348 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -366,22 +637,268 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -400,143 +917,181 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
         <name val="宋体"/>
+        <scheme val="none"/>
         <charset val="134"/>
-        <scheme val="none"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
         <name val="宋体"/>
+        <scheme val="none"/>
         <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -544,15 +1099,12 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -568,27 +1120,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="4381500"/>
-          <a:ext cx="9734550" cy="4010025"/>
+          <a:off x="0" y="6858000"/>
+          <a:ext cx="9733915" cy="4010025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -605,60 +1151,60 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
-  <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
+  <autoFilter ref="A5:C43"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="0"/>
+    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
+    <tableColumn id="2" name="分类" dataDxfId="1"/>
+    <tableColumn id="3" name="说明" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A24:C29" totalsRowShown="0">
-  <autoFilter ref="A24:C29" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A24:C29" totalsRowShown="0">
+  <autoFilter ref="A24:C29"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明"/>
+    <tableColumn id="1" name="营业额明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
-  <autoFilter ref="A1:C20" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
+  <autoFilter ref="A1:C20"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="说明"/>
+    <tableColumn id="1" name="成本明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A20:C24" totalsRowShown="0">
-  <autoFilter ref="A20:C24" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A20:C24" totalsRowShown="0">
+  <autoFilter ref="A20:C24"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="6"/>
+    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
+    <tableColumn id="2" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" name="说明" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C16" totalsRowShown="0">
-  <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C17" totalsRowShown="0">
+  <autoFilter ref="A1:C17"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="3"/>
+    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
+    <tableColumn id="4" name="分类" dataDxfId="7"/>
+    <tableColumn id="1" name="说明" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -943,490 +1489,489 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="7" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="11" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="15" customHeight="1" spans="1:3">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9">
+      <c r="C1" s="11">
         <v>100000</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="15" customHeight="1" spans="1:3">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="12">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99761.380000000019</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="5" t="s">
+        <v>99761.38</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:3">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="12">
         <f>C1-C2</f>
-        <v>238.61999999998079</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="5" t="s">
+        <v>238.619999999981</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1"/>
+    <row r="5" ht="15" customHeight="1" spans="1:3">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
+    <row r="6" ht="15" customHeight="1" spans="1:3">
+      <c r="A6" s="13">
         <v>10000</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
+    <row r="7" ht="15" customHeight="1" spans="1:3">
+      <c r="A7" s="13">
         <v>26000</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
+    <row r="8" ht="15" customHeight="1" spans="1:3">
+      <c r="A8" s="13">
         <v>6000</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
+    <row r="9" ht="15" customHeight="1" spans="1:3">
+      <c r="A9" s="13">
         <v>3000</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1">
+    <row r="10" ht="15" customHeight="1" spans="1:3">
+      <c r="A10" s="13">
         <v>2100</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1">
+    <row r="11" ht="15" customHeight="1" spans="1:3">
+      <c r="A11" s="13">
         <v>340</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="1">
+    <row r="12" ht="15" customHeight="1" spans="1:3">
+      <c r="A12" s="13">
         <v>200</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="1">
+    <row r="13" ht="15" customHeight="1" spans="1:3">
+      <c r="A13" s="13">
         <v>11000</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="1">
+    <row r="14" ht="15" customHeight="1" spans="1:3">
+      <c r="A14" s="13">
         <v>5000</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="1">
+    <row r="15" ht="15" customHeight="1" spans="1:3">
+      <c r="A15" s="13">
         <v>755</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="1">
+    <row r="16" ht="15" customHeight="1" spans="1:3">
+      <c r="A16" s="13">
         <v>190</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="1">
+    <row r="17" ht="15" customHeight="1" spans="1:3">
+      <c r="A17" s="13">
         <v>405.9</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="1">
+    <row r="18" ht="15" customHeight="1" spans="1:3">
+      <c r="A18" s="13">
         <v>228</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="1">
+    <row r="19" ht="15" customHeight="1" spans="1:3">
+      <c r="A19" s="13">
         <v>639.5</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="1">
-        <v>1259.0999999999999</v>
+    <row r="20" ht="15" customHeight="1" spans="1:3">
+      <c r="A20" s="13">
+        <v>1259.1</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="1">
+    <row r="21" ht="15" customHeight="1" spans="1:3">
+      <c r="A21" s="13">
         <v>1000</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="1">
+    <row r="22" ht="15" customHeight="1" spans="1:3">
+      <c r="A22" s="13">
         <v>13260</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="1">
+    <row r="23" ht="15" customHeight="1" spans="1:3">
+      <c r="A23" s="13">
         <v>47.97</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="1">
-        <v>276.10000000000002</v>
+    <row r="24" ht="15" customHeight="1" spans="1:3">
+      <c r="A24" s="13">
+        <v>276.1</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="1">
+    <row r="25" ht="15" customHeight="1" spans="1:3">
+      <c r="A25" s="13">
         <v>6000</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="1">
+    <row r="26" ht="15" customHeight="1" spans="1:3">
+      <c r="A26" s="13">
         <v>640</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="1">
+    <row r="27" ht="15" customHeight="1" spans="1:3">
+      <c r="A27" s="13">
         <v>500</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="1">
+    <row r="28" ht="15" customHeight="1" spans="1:3">
+      <c r="A28" s="13">
         <v>600</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="1">
+    <row r="29" ht="15" customHeight="1" spans="1:3">
+      <c r="A29" s="13">
         <v>938</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="1">
+    <row r="30" ht="15" customHeight="1" spans="1:3">
+      <c r="A30" s="13">
         <v>1000</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="1">
+    <row r="31" ht="15" customHeight="1" spans="1:3">
+      <c r="A31" s="13">
         <v>60.5</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="1">
+    <row r="32" ht="15" customHeight="1" spans="1:3">
+      <c r="A32" s="13">
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="1">
+    <row r="33" ht="15" customHeight="1" spans="1:3">
+      <c r="A33" s="13">
         <v>42.16</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="1">
+    <row r="34" ht="15" customHeight="1" spans="1:3">
+      <c r="A34" s="13">
         <v>1000</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="3">
+    <row r="35" ht="15" customHeight="1" spans="1:3">
+      <c r="A35" s="6">
         <v>500</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="3">
+    <row r="36" ht="15" customHeight="1" spans="1:3">
+      <c r="A36" s="6">
         <v>1300</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="B36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="3">
+    <row r="37" ht="15" customHeight="1" spans="1:3">
+      <c r="A37" s="6">
         <v>253.84</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="13" t="s">
+      <c r="B37" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="3">
+    <row r="38" ht="15" customHeight="1" spans="1:3">
+      <c r="A38" s="6">
         <v>1000</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="B38" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="3">
+    <row r="39" ht="15" customHeight="1" spans="1:3">
+      <c r="A39" s="6">
         <v>355.3</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="13" t="s">
+      <c r="B39" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="3">
+    <row r="40" ht="15" customHeight="1" spans="1:3">
+      <c r="A40" s="6">
         <v>3000</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="13" t="s">
+      <c r="B40" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="3">
+    <row r="41" ht="15" customHeight="1" spans="1:3">
+      <c r="A41" s="6">
         <v>174</v>
       </c>
-      <c r="B41" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="13" t="s">
+      <c r="B41" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="3">
+    <row r="42" ht="15" customHeight="1" spans="1:3">
+      <c r="A42" s="6">
         <v>33.6</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="3">
+    <row r="43" ht="15" customHeight="1" spans="1:3">
+      <c r="A43" s="6">
         <v>500</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="13" t="s">
+      <c r="B43" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1434,351 +1979,351 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" customHeight="1" spans="1:3">
+      <c r="A1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="1">
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="13">
         <v>4333</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1">
+    <row r="3" customHeight="1" spans="1:3">
+      <c r="A3" s="13">
         <v>12000</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1">
+    <row r="4" customHeight="1" spans="1:3">
+      <c r="A4" s="13">
         <v>1000</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
+    <row r="5" customHeight="1" spans="1:3">
+      <c r="A5" s="13">
         <v>13260</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
+    <row r="6" customHeight="1" spans="1:3">
+      <c r="A6" s="13">
         <v>600</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="13">
         <v>938</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="13">
         <v>1000</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
+    <row r="9" customHeight="1" spans="1:3">
+      <c r="A9" s="13">
         <v>60.5</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1">
+    <row r="10" customHeight="1" spans="1:3">
+      <c r="A10" s="13">
         <v>162.41</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1">
+    <row r="11" customHeight="1" spans="1:3">
+      <c r="A11" s="13">
         <v>42.16</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="1">
+    <row r="12" customHeight="1" spans="1:3">
+      <c r="A12" s="13">
         <v>1000</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="3">
+    <row r="13" customHeight="1" spans="1:3">
+      <c r="A13" s="6">
         <v>1300</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="3">
+    <row r="14" customHeight="1" spans="1:3">
+      <c r="A14" s="6">
         <v>253.84</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="3">
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="6">
         <v>1000</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="3">
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="6">
         <v>355.3</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="3">
+    <row r="17" customHeight="1" spans="1:3">
+      <c r="A17" s="6">
         <v>3000</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="3">
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="6">
         <v>174</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="3">
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="6">
         <v>33.6</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="3">
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="6">
         <v>500</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="7">
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="9">
         <v>6683.96</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="7">
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="9">
         <v>1861.8</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="7">
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="9">
         <v>0</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="7">
-        <v>19919.099999999999</v>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="9">
+        <v>19919.1</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="7">
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="9">
         <v>13970.88</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="5" t="s">
+      <c r="C29" s="3"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="10">
         <f>SUM(成本明细表_6[成本明细])</f>
-        <v>41012.810000000005</v>
-      </c>
-      <c r="C32" s="9"/>
-    </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="5" t="s">
+        <v>41012.81</v>
+      </c>
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="10">
         <f>SUM(营业额明细表_5[营业额明细])</f>
         <v>42435.74</v>
       </c>
-      <c r="C33" s="10"/>
-    </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="5" t="s">
+      <c r="C33" s="12"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="10"/>
-    </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C34" s="12"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:1">
       <c r="A36" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
@@ -1787,295 +2332,301 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="16" t="s">
+    <row r="1" customHeight="1" spans="1:3">
+      <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16">
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="2">
         <v>4333</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="16">
+    <row r="3" customHeight="1" spans="1:3">
+      <c r="A3" s="2">
         <v>18000</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16">
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:3">
+      <c r="A4" s="2">
         <v>4140</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16">
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:3">
+      <c r="A5" s="2">
         <v>7866</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16">
+      <c r="B5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:3">
+      <c r="A6" s="2">
         <v>28.64</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="2">
+        <v>44.48</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="2">
+        <v>3000</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:3">
+      <c r="A9" s="2">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:3">
+      <c r="A10" s="2">
+        <v>468</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:3">
+      <c r="A11" s="2">
+        <v>385</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A12" s="2">
+        <v>295</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A13" s="2">
+        <v>718</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="14" t="s">
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A14" s="2">
+        <v>57.6</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16">
-        <v>44.48</v>
-      </c>
-      <c r="B7" s="14" t="s">
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="2">
+        <v>302.5</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="14" t="s">
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16">
-        <v>3000</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row r="17" customHeight="1" spans="1:3">
+      <c r="A17" s="6">
+        <v>225</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="9">
+        <v>0</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="9">
+        <v>0</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="9">
+        <v>0</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="9">
+        <v>0</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16">
-        <v>23</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16">
-        <v>468</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="16">
-        <v>385</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="16">
-        <v>295</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="16">
-        <v>718</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="16">
-        <v>57.6</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="16">
-        <v>302.5</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="16">
-        <v>1000</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="16"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="16"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="7">
-        <v>0</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="7">
-        <v>0</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="7">
-        <v>0</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="7">
-        <v>0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="5" t="s">
+      <c r="C24" s="3"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="10">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>40661.22</v>
-      </c>
-      <c r="C27" s="9"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
+        <v>40886.22</v>
+      </c>
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="10">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>0</v>
       </c>
-      <c r="C28" s="10"/>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C28" s="12"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="12"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:1">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B18" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17 B18 B2:B16">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
   <tableParts count="2">
     <tablePart r:id="rId2"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="78">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>750圆打包盒600个，0.375/个</t>
+  </si>
+  <si>
+    <t>一次性餐具(筷子+勺子)，70元/500个，0.14/个</t>
   </si>
   <si>
     <t>堂食</t>
@@ -254,14 +257,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,19 +285,28 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -306,15 +318,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,39 +335,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -391,14 +379,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -407,7 +387,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -420,18 +423,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -462,169 +458,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,6 +631,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -649,6 +654,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -677,15 +697,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -696,21 +707,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -738,167 +734,167 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -907,22 +903,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -987,7 +983,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -1023,7 +1019,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -1060,7 +1056,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1199,8 +1195,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C17" totalsRowShown="0">
-  <autoFilter ref="A1:C17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C18" totalsRowShown="0">
+  <autoFilter ref="A1:C18"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -2532,9 +2528,15 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
+      <c r="A18" s="6">
+        <v>350</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
       <c r="A19" s="7"/>
@@ -2557,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="3"/>
     </row>
@@ -2566,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" s="3"/>
     </row>
@@ -2575,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23" s="3"/>
     </row>
@@ -2584,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C24" s="3"/>
     </row>
@@ -2594,7 +2596,7 @@
       </c>
       <c r="B27" s="10">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>40886.22</v>
+        <v>41236.22</v>
       </c>
       <c r="C27" s="11"/>
     </row>
@@ -2610,13 +2612,13 @@
     </row>
     <row r="29" customHeight="1" spans="1:3">
       <c r="A29" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="12"/>
     </row>
     <row r="30" customHeight="1" spans="1:1">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB35D7F-BA7A-40DB-9F63-84704C9B384E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
+    <workbookView xWindow="1410" yWindow="1545" windowWidth="35070" windowHeight="19335" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="2026-02流水 " sheetId="3" r:id="rId2"/>
     <sheet name="2026-03流水" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="80">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -250,21 +256,25 @@
   </si>
   <si>
     <t>净利润</t>
+  </si>
+  <si>
+    <t>食材</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一次性筷子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,345 +297,29 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -633,262 +327,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -903,7 +352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -913,181 +362,136 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <name val="宋体"/>
+        <charset val="134"/>
         <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
         <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
         <name val="宋体"/>
+        <charset val="134"/>
         <scheme val="none"/>
-        <charset val="134"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
       </font>
       <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1095,34 +499,43 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1147,60 +560,60 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
-  <autoFilter ref="A5:C43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
+  <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
-    <tableColumn id="2" name="分类" dataDxfId="1"/>
-    <tableColumn id="3" name="说明" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A24:C29" totalsRowShown="0">
-  <autoFilter ref="A24:C29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A24:C29" totalsRowShown="0">
+  <autoFilter ref="A24:C29" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="营业额明细"/>
-    <tableColumn id="2" name="分类"/>
-    <tableColumn id="3" name="说明"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
-  <autoFilter ref="A1:C20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
+  <autoFilter ref="A1:C20" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="成本明细"/>
-    <tableColumn id="2" name="分类"/>
-    <tableColumn id="3" name="说明"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A20:C24" totalsRowShown="0">
-  <autoFilter ref="A20:C24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A21:C25" totalsRowShown="0">
+  <autoFilter ref="A21:C25" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
-    <tableColumn id="2" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" name="说明" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C18" totalsRowShown="0">
-  <autoFilter ref="A1:C18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C19" totalsRowShown="0">
+  <autoFilter ref="A1:C19" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
-    <tableColumn id="4" name="分类" dataDxfId="7"/>
-    <tableColumn id="1" name="说明" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1485,62 +898,63 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="7" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="6" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="14" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>100000</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99761.38</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="7" t="s">
+        <v>99761.380000000019</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <f>C1-C2</f>
-        <v>238.619999999981</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="7" t="s">
+        <v>238.61999999998079</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:3">
-      <c r="A6" s="13">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
         <v>10000</v>
       </c>
       <c r="B6" t="s">
@@ -1550,8 +964,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:3">
-      <c r="A7" s="13">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
         <v>26000</v>
       </c>
       <c r="B7" t="s">
@@ -1561,8 +975,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:3">
-      <c r="A8" s="13">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
         <v>6000</v>
       </c>
       <c r="B8" t="s">
@@ -1572,8 +986,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:3">
-      <c r="A9" s="13">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
         <v>3000</v>
       </c>
       <c r="B9" t="s">
@@ -1583,8 +997,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="13">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
         <v>2100</v>
       </c>
       <c r="B10" t="s">
@@ -1594,8 +1008,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:3">
-      <c r="A11" s="13">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
         <v>340</v>
       </c>
       <c r="B11" t="s">
@@ -1605,8 +1019,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:3">
-      <c r="A12" s="13">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
         <v>200</v>
       </c>
       <c r="B12" t="s">
@@ -1616,8 +1030,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:3">
-      <c r="A13" s="13">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
         <v>11000</v>
       </c>
       <c r="B13" t="s">
@@ -1627,8 +1041,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:3">
-      <c r="A14" s="13">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
         <v>5000</v>
       </c>
       <c r="B14" t="s">
@@ -1638,8 +1052,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:3">
-      <c r="A15" s="13">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
         <v>755</v>
       </c>
       <c r="B15" t="s">
@@ -1649,8 +1063,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:3">
-      <c r="A16" s="13">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
         <v>190</v>
       </c>
       <c r="B16" t="s">
@@ -1660,8 +1074,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:3">
-      <c r="A17" s="13">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
         <v>405.9</v>
       </c>
       <c r="B17" t="s">
@@ -1671,8 +1085,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:3">
-      <c r="A18" s="13">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
         <v>228</v>
       </c>
       <c r="B18" t="s">
@@ -1682,8 +1096,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:3">
-      <c r="A19" s="13">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
         <v>639.5</v>
       </c>
       <c r="B19" t="s">
@@ -1693,9 +1107,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:3">
-      <c r="A20" s="13">
-        <v>1259.1</v>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>1259.0999999999999</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -1704,19 +1118,19 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:3">
-      <c r="A21" s="13">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
         <v>1000</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:3">
-      <c r="A22" s="13">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
         <v>13260</v>
       </c>
       <c r="B22" t="s">
@@ -1726,8 +1140,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:3">
-      <c r="A23" s="13">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
         <v>47.97</v>
       </c>
       <c r="B23" t="s">
@@ -1737,9 +1151,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:3">
-      <c r="A24" s="13">
-        <v>276.1</v>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>276.10000000000002</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1748,226 +1162,226 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:3">
-      <c r="A25" s="13">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
         <v>6000</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:3">
-      <c r="A26" s="13">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
         <v>640</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:3">
-      <c r="A27" s="13">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
         <v>500</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:3">
-      <c r="A28" s="13">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
         <v>600</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:3">
-      <c r="A29" s="13">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
         <v>938</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:3">
-      <c r="A30" s="13">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
         <v>1000</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:3">
-      <c r="A31" s="13">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="2">
         <v>60.5</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:3">
-      <c r="A32" s="13">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="2">
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:3">
-      <c r="A33" s="13">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="2">
         <v>42.16</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:3">
-      <c r="A34" s="13">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
         <v>1000</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:3">
-      <c r="A35" s="6">
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="5">
         <v>500</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:3">
-      <c r="A36" s="6">
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="5">
         <v>1300</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="B36" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:3">
-      <c r="A37" s="6">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="5">
         <v>253.84</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="16" t="s">
+      <c r="B37" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:3">
-      <c r="A38" s="6">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="5">
         <v>1000</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="16" t="s">
+      <c r="B38" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:3">
-      <c r="A39" s="6">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="5">
         <v>355.3</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="B39" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:3">
-      <c r="A40" s="6">
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="5">
         <v>3000</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="16" t="s">
+      <c r="B40" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:3">
-      <c r="A41" s="6">
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="5">
         <v>174</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="B41" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:3">
-      <c r="A42" s="6">
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="5">
         <v>33.6</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:3">
-      <c r="A43" s="6">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="5">
         <v>500</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="16" t="s">
+      <c r="B43" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="14" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1975,20 +1389,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -1998,8 +1412,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="13">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
         <v>4333</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -2009,8 +1423,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
-      <c r="A3" s="13">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
         <v>12000</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -2020,8 +1434,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:3">
-      <c r="A4" s="13">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
         <v>1000</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -2031,8 +1445,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="13">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
         <v>13260</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -2042,8 +1456,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="13">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
         <v>600</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -2053,8 +1467,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="13">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
         <v>938</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -2064,8 +1478,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="13">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
         <v>1000</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -2075,8 +1489,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="13">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
         <v>60.5</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -2086,8 +1500,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
-      <c r="A10" s="13">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
         <v>162.41</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2097,8 +1511,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:3">
-      <c r="A11" s="13">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
         <v>42.16</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2108,8 +1522,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:3">
-      <c r="A12" s="13">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
         <v>1000</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2119,207 +1533,207 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="6">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="5">
         <v>1300</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="6">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="5">
         <v>253.84</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="6">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="5">
         <v>1000</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="6">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="5">
         <v>355.3</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="6">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="5">
         <v>3000</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="6">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="5">
         <v>174</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="6">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="5">
         <v>33.6</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="6">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="5">
         <v>500</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="6"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="8"/>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="8"/>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="6"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="9">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="8">
         <v>6683.96</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="9">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="8">
         <v>1861.8</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="9">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="8">
         <v>0</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="9">
-        <v>19919.1</v>
-      </c>
-      <c r="B28" s="8" t="s">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="8">
+        <v>19919.099999999999</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="9">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="8">
         <v>13970.88</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="3"/>
     </row>
-    <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <f>SUM(成本明细表_6[成本明细])</f>
-        <v>41012.81</v>
-      </c>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="7" t="s">
+        <v>41012.810000000005</v>
+      </c>
+      <c r="C32" s="10"/>
+    </row>
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <f>SUM(营业额明细表_5[营业额明细])</f>
         <v>42435.74</v>
       </c>
-      <c r="C33" s="12"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="7" t="s">
+      <c r="C33" s="11"/>
+    </row>
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="12"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:1">
+      <c r="C34" s="11"/>
+    </row>
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
@@ -2328,19 +1742,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -2351,7 +1765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2">
         <v>4333</v>
       </c>
@@ -2362,18 +1776,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
         <v>18000</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:3">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>4140</v>
       </c>
@@ -2384,251 +1798,262 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:3">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>7866</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>28.64</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>44.48</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
         <v>3000</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
         <v>23</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2">
         <v>468</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2">
         <v>385</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
         <v>295</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2">
         <v>718</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
         <v>57.6</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
         <v>302.5</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2">
         <v>1000</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="6">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="5">
         <v>225</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="6">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="5">
         <v>350</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="7" t="s">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="15">
+        <v>112</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="9">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="8">
         <v>0</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="9">
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="8">
         <v>0</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="9">
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="8">
         <v>0</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="9">
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="8">
         <v>0</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="7" t="s">
+      <c r="C25" s="3"/>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B28" s="9">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>41236.22</v>
-      </c>
-      <c r="C27" s="11"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="7" t="s">
+        <v>41348.22</v>
+      </c>
+      <c r="C28" s="10"/>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B29" s="9">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>0</v>
       </c>
-      <c r="C28" s="12"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="7" t="s">
+      <c r="C29" s="11"/>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="12"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:1">
-      <c r="A30" t="s">
+      <c r="C30" s="11"/>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" t="s">
         <v>77</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17 B18 B2:B16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B19" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
   <tableParts count="2">
     <tablePart r:id="rId2"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB35D7F-BA7A-40DB-9F63-84704C9B384E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="1545" windowWidth="35070" windowHeight="19335" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="2026-02流水 " sheetId="3" r:id="rId2"/>
     <sheet name="2026-03流水" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="80">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -240,6 +234,12 @@
     <t>一次性餐具(筷子+勺子)，70元/500个，0.14/个</t>
   </si>
   <si>
+    <t>一次性筷子</t>
+  </si>
+  <si>
+    <t>福州鱼丸20包/198</t>
+  </si>
+  <si>
     <t>堂食</t>
   </si>
   <si>
@@ -256,25 +256,21 @@
   </si>
   <si>
     <t>净利润</t>
-  </si>
-  <si>
-    <t>食材</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>一次性筷子</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,29 +293,351 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -327,35 +645,289 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -365,133 +937,175 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -499,50 +1113,41 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="6858000"/>
+          <a:off x="0" y="7239000"/>
           <a:ext cx="9733915" cy="4010025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -560,60 +1165,60 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
-  <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
+  <autoFilter ref="A5:C43"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="6"/>
+    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
+    <tableColumn id="2" name="分类" dataDxfId="1"/>
+    <tableColumn id="3" name="说明" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A24:C29" totalsRowShown="0">
-  <autoFilter ref="A24:C29" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A24:C29" totalsRowShown="0">
+  <autoFilter ref="A24:C29"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明"/>
+    <tableColumn id="1" name="营业额明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
-  <autoFilter ref="A1:C20" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
+  <autoFilter ref="A1:C20"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="说明"/>
+    <tableColumn id="1" name="成本明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A21:C25" totalsRowShown="0">
-  <autoFilter ref="A21:C25" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A22:C26" totalsRowShown="0">
+  <autoFilter ref="A22:C26"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="3"/>
+    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
+    <tableColumn id="2" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" name="说明" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A1:C19" totalsRowShown="0">
-  <autoFilter ref="A1:C19" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C20" totalsRowShown="0">
+  <autoFilter ref="A1:C20"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="0"/>
+    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
+    <tableColumn id="4" name="分类" dataDxfId="7"/>
+    <tableColumn id="1" name="说明" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -898,62 +1503,61 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="6" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="10" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="12" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="15" customHeight="1" spans="1:3">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10">
+      <c r="C1" s="14">
         <v>100000</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="6" t="s">
+    <row r="2" ht="15" customHeight="1" spans="1:3">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="15">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99761.380000000019</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+        <v>99761.38</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:3">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="15">
         <f>C1-C2</f>
-        <v>238.61999999998079</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="6" t="s">
+        <v>238.619999999981</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1"/>
+    <row r="5" ht="15" customHeight="1" spans="1:3">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" ht="15" customHeight="1" spans="1:3">
       <c r="A6" s="2">
         <v>10000</v>
       </c>
@@ -964,7 +1568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" ht="15" customHeight="1" spans="1:3">
       <c r="A7" s="2">
         <v>26000</v>
       </c>
@@ -975,7 +1579,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" ht="15" customHeight="1" spans="1:3">
       <c r="A8" s="2">
         <v>6000</v>
       </c>
@@ -986,7 +1590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" ht="15" customHeight="1" spans="1:3">
       <c r="A9" s="2">
         <v>3000</v>
       </c>
@@ -997,7 +1601,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" ht="15" customHeight="1" spans="1:3">
       <c r="A10" s="2">
         <v>2100</v>
       </c>
@@ -1008,7 +1612,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" ht="15" customHeight="1" spans="1:3">
       <c r="A11" s="2">
         <v>340</v>
       </c>
@@ -1019,7 +1623,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" ht="15" customHeight="1" spans="1:3">
       <c r="A12" s="2">
         <v>200</v>
       </c>
@@ -1030,7 +1634,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" ht="15" customHeight="1" spans="1:3">
       <c r="A13" s="2">
         <v>11000</v>
       </c>
@@ -1041,7 +1645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" ht="15" customHeight="1" spans="1:3">
       <c r="A14" s="2">
         <v>5000</v>
       </c>
@@ -1052,7 +1656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" ht="15" customHeight="1" spans="1:3">
       <c r="A15" s="2">
         <v>755</v>
       </c>
@@ -1063,7 +1667,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" ht="15" customHeight="1" spans="1:3">
       <c r="A16" s="2">
         <v>190</v>
       </c>
@@ -1074,7 +1678,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" ht="15" customHeight="1" spans="1:3">
       <c r="A17" s="2">
         <v>405.9</v>
       </c>
@@ -1085,7 +1689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" ht="15" customHeight="1" spans="1:3">
       <c r="A18" s="2">
         <v>228</v>
       </c>
@@ -1096,7 +1700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" ht="15" customHeight="1" spans="1:3">
       <c r="A19" s="2">
         <v>639.5</v>
       </c>
@@ -1107,9 +1711,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" ht="15" customHeight="1" spans="1:3">
       <c r="A20" s="2">
-        <v>1259.0999999999999</v>
+        <v>1259.1</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -1118,18 +1722,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" ht="15" customHeight="1" spans="1:3">
       <c r="A21" s="2">
         <v>1000</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" ht="15" customHeight="1" spans="1:3">
       <c r="A22" s="2">
         <v>13260</v>
       </c>
@@ -1140,7 +1744,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" ht="15" customHeight="1" spans="1:3">
       <c r="A23" s="2">
         <v>47.97</v>
       </c>
@@ -1151,9 +1755,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" ht="15" customHeight="1" spans="1:3">
       <c r="A24" s="2">
-        <v>276.10000000000002</v>
+        <v>276.1</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1162,226 +1766,226 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" ht="15" customHeight="1" spans="1:3">
       <c r="A25" s="2">
         <v>6000</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" ht="15" customHeight="1" spans="1:3">
       <c r="A26" s="2">
         <v>640</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" ht="15" customHeight="1" spans="1:3">
       <c r="A27" s="2">
         <v>500</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" ht="15" customHeight="1" spans="1:3">
       <c r="A28" s="2">
         <v>600</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" ht="15" customHeight="1" spans="1:3">
       <c r="A29" s="2">
         <v>938</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" ht="15" customHeight="1" spans="1:3">
       <c r="A30" s="2">
         <v>1000</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" ht="15" customHeight="1" spans="1:3">
       <c r="A31" s="2">
         <v>60.5</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" ht="15" customHeight="1" spans="1:3">
       <c r="A32" s="2">
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" ht="15" customHeight="1" spans="1:3">
       <c r="A33" s="2">
         <v>42.16</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" ht="15" customHeight="1" spans="1:3">
       <c r="A34" s="2">
         <v>1000</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" ht="15" customHeight="1" spans="1:3">
       <c r="A35" s="5">
         <v>500</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="18" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" ht="15" customHeight="1" spans="1:3">
       <c r="A36" s="5">
         <v>1300</v>
       </c>
-      <c r="B36" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="14" t="s">
+      <c r="B36" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" ht="15" customHeight="1" spans="1:3">
       <c r="A37" s="5">
         <v>253.84</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="14" t="s">
+      <c r="B37" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" ht="15" customHeight="1" spans="1:3">
       <c r="A38" s="5">
         <v>1000</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="14" t="s">
+      <c r="B38" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" ht="15" customHeight="1" spans="1:3">
       <c r="A39" s="5">
         <v>355.3</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="B39" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" ht="15" customHeight="1" spans="1:3">
       <c r="A40" s="5">
         <v>3000</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="14" t="s">
+      <c r="B40" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="18" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" ht="15" customHeight="1" spans="1:3">
       <c r="A41" s="5">
         <v>174</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="14" t="s">
+      <c r="B41" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" ht="15" customHeight="1" spans="1:3">
       <c r="A42" s="5">
         <v>33.6</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="18" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" ht="15" customHeight="1" spans="1:3">
       <c r="A43" s="5">
         <v>500</v>
       </c>
-      <c r="B43" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1389,19 +1993,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -1412,7 +2016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" s="2">
         <v>4333</v>
       </c>
@@ -1423,7 +2027,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" s="2">
         <v>12000</v>
       </c>
@@ -1434,7 +2038,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="2">
         <v>1000</v>
       </c>
@@ -1445,7 +2049,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" customHeight="1" spans="1:3">
       <c r="A5" s="2">
         <v>13260</v>
       </c>
@@ -1456,7 +2060,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" customHeight="1" spans="1:3">
       <c r="A6" s="2">
         <v>600</v>
       </c>
@@ -1467,7 +2071,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" customHeight="1" spans="1:3">
       <c r="A7" s="2">
         <v>938</v>
       </c>
@@ -1478,7 +2082,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="2">
         <v>1000</v>
       </c>
@@ -1489,7 +2093,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" customHeight="1" spans="1:3">
       <c r="A9" s="2">
         <v>60.5</v>
       </c>
@@ -1500,7 +2104,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" customHeight="1" spans="1:3">
       <c r="A10" s="2">
         <v>162.41</v>
       </c>
@@ -1511,7 +2115,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" customHeight="1" spans="1:3">
       <c r="A11" s="2">
         <v>42.16</v>
       </c>
@@ -1522,7 +2126,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" customHeight="1" spans="1:3">
       <c r="A12" s="2">
         <v>1000</v>
       </c>
@@ -1533,7 +2137,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" customHeight="1" spans="1:3">
       <c r="A13" s="5">
         <v>1300</v>
       </c>
@@ -1544,7 +2148,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" customHeight="1" spans="1:3">
       <c r="A14" s="5">
         <v>253.84</v>
       </c>
@@ -1555,7 +2159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" customHeight="1" spans="1:3">
       <c r="A15" s="5">
         <v>1000</v>
       </c>
@@ -1566,7 +2170,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" customHeight="1" spans="1:3">
       <c r="A16" s="5">
         <v>355.3</v>
       </c>
@@ -1577,7 +2181,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" customHeight="1" spans="1:3">
       <c r="A17" s="5">
         <v>3000</v>
       </c>
@@ -1588,7 +2192,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" customHeight="1" spans="1:3">
       <c r="A18" s="5">
         <v>174</v>
       </c>
@@ -1599,7 +2203,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" customHeight="1" spans="1:3">
       <c r="A19" s="5">
         <v>33.6</v>
       </c>
@@ -1610,7 +2214,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" customHeight="1" spans="1:3">
       <c r="A20" s="5">
         <v>500</v>
       </c>
@@ -1621,119 +2225,119 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="6" t="s">
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="8">
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="12">
         <v>6683.96</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="11" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="3"/>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="8">
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="12">
         <v>1861.8</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="11" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="8">
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="12">
         <v>0</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="8">
-        <v>19919.099999999999</v>
-      </c>
-      <c r="B28" s="7" t="s">
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="12">
+        <v>19919.1</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="8">
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="12">
         <v>13970.88</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="11" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="3"/>
     </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="6" t="s">
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="13">
         <f>SUM(成本明细表_6[成本明细])</f>
-        <v>41012.810000000005</v>
-      </c>
-      <c r="C32" s="10"/>
-    </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="6" t="s">
+        <v>41012.81</v>
+      </c>
+      <c r="C32" s="14"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="13">
         <f>SUM(营业额明细表_5[营业额明细])</f>
         <v>42435.74</v>
       </c>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="6" t="s">
+      <c r="C33" s="15"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="11"/>
-    </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C34" s="15"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:1">
       <c r="A36" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
@@ -1742,19 +2346,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -1765,7 +2369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" s="2">
         <v>4333</v>
       </c>
@@ -1776,7 +2380,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" s="2">
         <v>18000</v>
       </c>
@@ -1787,7 +2391,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="2">
         <v>4140</v>
       </c>
@@ -1798,7 +2402,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" customHeight="1" spans="1:3">
       <c r="A5" s="2">
         <v>7866</v>
       </c>
@@ -1809,7 +2413,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" customHeight="1" spans="1:3">
       <c r="A6" s="2">
         <v>28.64</v>
       </c>
@@ -1820,7 +2424,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" customHeight="1" spans="1:3">
       <c r="A7" s="2">
         <v>44.48</v>
       </c>
@@ -1831,7 +2435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="2">
         <v>3000</v>
       </c>
@@ -1842,7 +2446,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" customHeight="1" spans="1:3">
       <c r="A9" s="2">
         <v>23</v>
       </c>
@@ -1853,7 +2457,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" customHeight="1" spans="1:3">
       <c r="A10" s="2">
         <v>468</v>
       </c>
@@ -1864,7 +2468,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" customHeight="1" spans="1:3">
       <c r="A11" s="2">
         <v>385</v>
       </c>
@@ -1875,7 +2479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:3">
       <c r="A12" s="2">
         <v>295</v>
       </c>
@@ -1886,7 +2490,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:3">
       <c r="A13" s="2">
         <v>718</v>
       </c>
@@ -1897,7 +2501,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:3">
       <c r="A14" s="2">
         <v>57.6</v>
       </c>
@@ -1908,7 +2512,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" customHeight="1" spans="1:3">
       <c r="A15" s="2">
         <v>302.5</v>
       </c>
@@ -1919,7 +2523,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" customHeight="1" spans="1:3">
       <c r="A16" s="2">
         <v>1000</v>
       </c>
@@ -1930,7 +2534,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" customHeight="1" spans="1:3">
       <c r="A17" s="5">
         <v>225</v>
       </c>
@@ -1941,7 +2545,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" customHeight="1" spans="1:3">
       <c r="A18" s="5">
         <v>350</v>
       </c>
@@ -1952,108 +2556,119 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="15">
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="6">
         <v>112</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="6" t="s">
+      <c r="B19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="8">
+        <v>198</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B22" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="8">
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="12">
         <v>0</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="8">
+      <c r="B23" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="12">
         <v>0</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="8">
+      <c r="B24" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="12">
         <v>0</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="8">
+      <c r="B25" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="12">
         <v>0</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="6" t="s">
+      <c r="B26" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B29" s="13">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>41348.22</v>
-      </c>
-      <c r="C28" s="10"/>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="6" t="s">
+        <v>41546.22</v>
+      </c>
+      <c r="C29" s="14"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B30" s="13">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>0</v>
       </c>
-      <c r="C29" s="11"/>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="11"/>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" t="s">
-        <v>77</v>
+      <c r="C30" s="15"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:3">
+      <c r="A31" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="15"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:1">
+      <c r="A32" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B19" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20 B2:B19">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
   <tableParts count="2">
     <tablePart r:id="rId2"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -156,7 +156,7 @@
     <t>工资</t>
   </si>
   <si>
-    <t>2员工工资</t>
+    <t>员工工资</t>
   </si>
   <si>
     <t>老池自购食材</t>
@@ -192,9 +192,6 @@
     <t>卡内结余</t>
   </si>
   <si>
-    <t>员工工资</t>
-  </si>
-  <si>
     <t>芋头小笼120斤*12，肉燕120斤*22.5，菜探长进货</t>
   </si>
   <si>
@@ -238,6 +235,9 @@
   </si>
   <si>
     <t>福州鱼丸20包/198</t>
+  </si>
+  <si>
+    <t>京东外卖刷单</t>
   </si>
   <si>
     <t>堂食</t>
@@ -264,13 +264,13 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,21 +296,15 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -322,14 +316,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -337,14 +324,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -367,22 +346,23 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -397,9 +377,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -413,18 +422,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -434,14 +436,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -452,13 +446,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,163 +602,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -649,23 +643,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -673,8 +652,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -694,13 +673,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -722,176 +729,163 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -904,18 +898,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1123,13 +1105,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1147,7 +1129,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="7239000"/>
+          <a:off x="0" y="7429500"/>
           <a:ext cx="9733915" cy="4010025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1201,8 +1183,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A22:C26" totalsRowShown="0">
-  <autoFilter ref="A22:C26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A23:C27" totalsRowShown="0">
+  <autoFilter ref="A23:C27"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1213,8 +1195,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C20" totalsRowShown="0">
-  <autoFilter ref="A1:C20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C21" totalsRowShown="0">
+  <autoFilter ref="A1:C21"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1514,43 +1496,43 @@
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="10" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="6" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="16" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14">
+      <c r="C1" s="10">
         <v>100000</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="11">
         <f>SUM(成本明细[金额(元)])</f>
         <v>99761.38</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="11">
         <f>C1-C2</f>
         <v>238.619999999981</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1729,7 +1711,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="12" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1773,7 +1755,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="12" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1784,7 +1766,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1795,7 +1777,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="12" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1806,7 +1788,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="12" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1817,7 +1799,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="12" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1828,7 +1810,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="12" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1839,7 +1821,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="12" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1850,7 +1832,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="12" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1861,7 +1843,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="12" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1872,7 +1854,7 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="12" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1880,10 +1862,10 @@
       <c r="A35" s="5">
         <v>500</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="14" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1891,10 +1873,10 @@
       <c r="A36" s="5">
         <v>1300</v>
       </c>
-      <c r="B36" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="18" t="s">
+      <c r="B36" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1902,10 +1884,10 @@
       <c r="A37" s="5">
         <v>253.84</v>
       </c>
-      <c r="B37" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="18" t="s">
+      <c r="B37" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1913,10 +1895,10 @@
       <c r="A38" s="5">
         <v>1000</v>
       </c>
-      <c r="B38" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="18" t="s">
+      <c r="B38" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1924,10 +1906,10 @@
       <c r="A39" s="5">
         <v>355.3</v>
       </c>
-      <c r="B39" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="18" t="s">
+      <c r="B39" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1935,10 +1917,10 @@
       <c r="A40" s="5">
         <v>3000</v>
       </c>
-      <c r="B40" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="18" t="s">
+      <c r="B40" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="14" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1946,10 +1928,10 @@
       <c r="A41" s="5">
         <v>174</v>
       </c>
-      <c r="B41" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="18" t="s">
+      <c r="B41" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="14" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1957,10 +1939,10 @@
       <c r="A42" s="5">
         <v>33.6</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1968,10 +1950,10 @@
       <c r="A43" s="5">
         <v>500</v>
       </c>
-      <c r="B43" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="18" t="s">
+      <c r="B43" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2029,7 +2011,7 @@
     </row>
     <row r="3" customHeight="1" spans="1:3">
       <c r="A3" s="2">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>45</v>
@@ -2226,25 +2208,25 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="3"/>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
       <c r="C22" s="3"/>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="3"/>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -2252,75 +2234,75 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="12">
+      <c r="A25" s="8">
         <v>6683.96</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="12">
+      <c r="A26" s="8">
         <v>1861.8</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="3"/>
     </row>
     <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="12">
+      <c r="A27" s="8">
         <v>0</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="12">
+      <c r="A28" s="8">
         <v>19919.1</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="3"/>
     </row>
     <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="12">
+      <c r="A29" s="8">
         <v>13970.88</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="3"/>
     </row>
     <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="9">
         <f>SUM(成本明细表_6[成本明细])</f>
-        <v>41012.81</v>
-      </c>
-      <c r="C32" s="14"/>
+        <v>36512.81</v>
+      </c>
+      <c r="C32" s="10"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="9">
         <f>SUM(营业额明细表_5[营业额明细])</f>
         <v>42435.74</v>
       </c>
-      <c r="C33" s="15"/>
+      <c r="C33" s="11"/>
     </row>
     <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="15"/>
+      <c r="C34" s="11"/>
     </row>
     <row r="36" customHeight="1" spans="1:1">
       <c r="A36" t="s">
@@ -2350,7 +2332,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -2388,7 +2370,7 @@
         <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
@@ -2399,7 +2381,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:3">
@@ -2410,7 +2392,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
@@ -2421,7 +2403,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
@@ -2454,7 +2436,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:3">
@@ -2465,7 +2447,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:3">
@@ -2476,7 +2458,7 @@
         <v>25</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:3">
@@ -2487,7 +2469,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:3">
@@ -2498,7 +2480,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:3">
@@ -2509,7 +2491,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -2520,7 +2502,7 @@
         <v>25</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
@@ -2531,7 +2513,7 @@
         <v>32</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -2542,7 +2524,7 @@
         <v>25</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -2553,121 +2535,133 @@
         <v>25</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="5">
+        <v>112</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="6">
-        <v>112</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="7" t="s">
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="5">
+        <v>198</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="8">
-        <v>198</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="9" t="s">
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="5">
+        <v>100</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="3"/>
-    </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B23" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="12">
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="8">
         <v>0</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="12">
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="8">
         <v>0</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B25" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="12">
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="8">
         <v>0</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B26" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="12">
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="8">
         <v>0</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B27" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="10" t="s">
+      <c r="C27" s="3"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B30" s="9">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>41546.22</v>
-      </c>
-      <c r="C29" s="14"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="10" t="s">
+        <v>41646.22</v>
+      </c>
+      <c r="C30" s="10"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:3">
+      <c r="A31" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B31" s="9">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>0</v>
       </c>
-      <c r="C30" s="15"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="10" t="s">
+      <c r="C31" s="11"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="15"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:1">
-      <c r="A32" t="s">
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:1">
+      <c r="A33" t="s">
         <v>79</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20 B2:B19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20 B21 B2:B19">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <tableParts count="2">

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="81">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>京东外卖刷单</t>
+  </si>
+  <si>
+    <t>硕美牛肉丸样品20斤，17一斤+22运费</t>
   </si>
   <si>
     <t>堂食</t>
@@ -263,11 +266,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -294,6 +297,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -302,35 +312,6 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -371,14 +352,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -391,6 +372,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -398,9 +417,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -416,22 +434,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -446,13 +449,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +569,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,157 +629,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -649,30 +652,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -684,30 +663,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -737,179 +692,233 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -983,7 +992,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -1019,7 +1028,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -1056,7 +1065,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1105,13 +1114,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1129,7 +1138,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="7429500"/>
+          <a:off x="0" y="9334500"/>
           <a:ext cx="9733915" cy="4010025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1183,8 +1192,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A23:C27" totalsRowShown="0">
-  <autoFilter ref="A23:C27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A33:C37" totalsRowShown="0">
+  <autoFilter ref="A33:C37"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1195,8 +1204,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C21" totalsRowShown="0">
-  <autoFilter ref="A1:C21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C22" totalsRowShown="0">
+  <autoFilter ref="A1:C22"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1496,43 +1505,43 @@
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="6" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="8" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="12" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10">
+      <c r="C1" s="12">
         <v>100000</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="13">
         <f>SUM(成本明细[金额(元)])</f>
         <v>99761.38</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="13">
         <f>C1-C2</f>
         <v>238.619999999981</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1711,7 +1720,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1755,7 +1764,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1766,7 +1775,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="14" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1777,7 +1786,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="14" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1788,7 +1797,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="14" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1799,7 +1808,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="14" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1810,7 +1819,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1821,7 +1830,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="14" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1832,7 +1841,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1843,7 +1852,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="14" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1854,7 +1863,7 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1862,10 +1871,10 @@
       <c r="A35" s="5">
         <v>500</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="16" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1873,10 +1882,10 @@
       <c r="A36" s="5">
         <v>1300</v>
       </c>
-      <c r="B36" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="14" t="s">
+      <c r="B36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1884,10 +1893,10 @@
       <c r="A37" s="5">
         <v>253.84</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="14" t="s">
+      <c r="B37" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1895,10 +1904,10 @@
       <c r="A38" s="5">
         <v>1000</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="14" t="s">
+      <c r="B38" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1906,10 +1915,10 @@
       <c r="A39" s="5">
         <v>355.3</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="B39" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1917,10 +1926,10 @@
       <c r="A40" s="5">
         <v>3000</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="14" t="s">
+      <c r="B40" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="16" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1928,10 +1937,10 @@
       <c r="A41" s="5">
         <v>174</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="14" t="s">
+      <c r="B41" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1939,10 +1948,10 @@
       <c r="A42" s="5">
         <v>33.6</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="16" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1950,10 +1959,10 @@
       <c r="A43" s="5">
         <v>500</v>
       </c>
-      <c r="B43" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2208,25 +2217,25 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
       <c r="C21" s="3"/>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
       <c r="C22" s="3"/>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
       <c r="C23" s="3"/>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -2234,75 +2243,75 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="8">
+      <c r="A25" s="10">
         <v>6683.96</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="8">
+      <c r="A26" s="10">
         <v>1861.8</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="3"/>
     </row>
     <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="8">
+      <c r="A27" s="10">
         <v>0</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="8">
+      <c r="A28" s="10">
         <v>19919.1</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="3"/>
     </row>
     <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="8">
+      <c r="A29" s="10">
         <v>13970.88</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="3"/>
     </row>
     <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="11">
         <f>SUM(成本明细表_6[成本明细])</f>
         <v>36512.81</v>
       </c>
-      <c r="C32" s="10"/>
+      <c r="C32" s="12"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="11">
         <f>SUM(营业额明细表_5[营业额明细])</f>
         <v>42435.74</v>
       </c>
-      <c r="C33" s="11"/>
+      <c r="C33" s="13"/>
     </row>
     <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="11"/>
+      <c r="C34" s="13"/>
     </row>
     <row r="36" customHeight="1" spans="1:1">
       <c r="A36" t="s">
@@ -2332,7 +2341,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -2364,7 +2373,7 @@
     </row>
     <row r="3" customHeight="1" spans="1:3">
       <c r="A3" s="2">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>45</v>
@@ -2572,91 +2581,147 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="3"/>
+      <c r="A22" s="6">
+        <v>362</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:3">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B33" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="8">
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="10">
         <v>0</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="8">
+      <c r="B34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:3">
+      <c r="A35" s="10">
         <v>0</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="8">
+      <c r="B35" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:3">
+      <c r="A36" s="10">
         <v>0</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="8">
+      <c r="B36" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:3">
+      <c r="A37" s="10">
         <v>0</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="6" t="s">
+      <c r="B37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:3">
+      <c r="A40" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B40" s="11">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>41646.22</v>
-      </c>
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="6" t="s">
+        <v>41008.22</v>
+      </c>
+      <c r="C40" s="12"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:3">
+      <c r="A41" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B41" s="11">
         <f>SUM(营业额明细表[营业额明细])</f>
         <v>0</v>
       </c>
-      <c r="C31" s="11"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:1">
-      <c r="A33" t="s">
+      <c r="C41" s="13"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:3">
+      <c r="A42" s="8" t="s">
         <v>79</v>
+      </c>
+      <c r="C42" s="13"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:1">
+      <c r="A43" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20 B21 B2:B19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20 B21 B22 B2:B19">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="78">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -147,6 +147,15 @@
     <t>硅胶防烫套</t>
   </si>
   <si>
+    <t>成本合计</t>
+  </si>
+  <si>
+    <t>营业额合计</t>
+  </si>
+  <si>
+    <t>利润</t>
+  </si>
+  <si>
     <t>成本明细</t>
   </si>
   <si>
@@ -180,18 +189,6 @@
     <t>美团外卖</t>
   </si>
   <si>
-    <t>成本合计</t>
-  </si>
-  <si>
-    <t>营业额合计</t>
-  </si>
-  <si>
-    <t>利润</t>
-  </si>
-  <si>
-    <t>卡内结余</t>
-  </si>
-  <si>
     <t>芋头小笼120斤*12，肉燕120斤*22.5，菜探长进货</t>
   </si>
   <si>
@@ -253,25 +250,20 @@
   </si>
   <si>
     <t>美团</t>
-  </si>
-  <si>
-    <t>毛利润</t>
-  </si>
-  <si>
-    <t>净利润</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -888,9 +880,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -909,16 +906,12 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1108,53 +1101,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="9334500"/>
-          <a:ext cx="9733915" cy="4010025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
   <autoFilter ref="A5:C43"/>
@@ -1168,8 +1114,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A24:C29" totalsRowShown="0">
-  <autoFilter ref="A24:C29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A29:C34" totalsRowShown="0">
+  <autoFilter ref="A29:C34"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细"/>
     <tableColumn id="2" name="分类"/>
@@ -1180,8 +1126,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A1:C20" totalsRowShown="0">
-  <autoFilter ref="A1:C20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
+  <autoFilter ref="A6:C25"/>
   <tableColumns count="3">
     <tableColumn id="1" name="成本明细"/>
     <tableColumn id="2" name="分类"/>
@@ -1192,8 +1138,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A33:C37" totalsRowShown="0">
-  <autoFilter ref="A33:C37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A31:C35" totalsRowShown="0">
+  <autoFilter ref="A31:C35"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1204,8 +1150,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A1:C22" totalsRowShown="0">
-  <autoFilter ref="A1:C22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C27" totalsRowShown="0">
+  <autoFilter ref="A6:C27"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1505,464 +1451,464 @@
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="8" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="14" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12">
+      <c r="C1" s="13">
         <v>100000</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="14">
         <f>SUM(成本明细[金额(元)])</f>
         <v>99761.38</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="14">
         <f>C1-C2</f>
         <v>238.619999999981</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:3">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>10000</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:3">
-      <c r="A7" s="2">
+      <c r="A7" s="5">
         <v>26000</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:3">
-      <c r="A8" s="2">
+      <c r="A8" s="5">
         <v>6000</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:3">
-      <c r="A9" s="2">
+      <c r="A9" s="5">
         <v>3000</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="2">
+      <c r="A10" s="5">
         <v>2100</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:3">
-      <c r="A11" s="2">
+      <c r="A11" s="5">
         <v>340</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:3">
-      <c r="A12" s="2">
+      <c r="A12" s="5">
         <v>200</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:3">
-      <c r="A13" s="2">
+      <c r="A13" s="5">
         <v>11000</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:3">
-      <c r="A14" s="2">
+      <c r="A14" s="5">
         <v>5000</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:3">
-      <c r="A15" s="2">
+      <c r="A15" s="5">
         <v>755</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:3">
-      <c r="A16" s="2">
+      <c r="A16" s="5">
         <v>190</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:3">
-      <c r="A17" s="2">
+      <c r="A17" s="5">
         <v>405.9</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:3">
-      <c r="A18" s="2">
+      <c r="A18" s="5">
         <v>228</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:3">
-      <c r="A19" s="2">
+      <c r="A19" s="5">
         <v>639.5</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:3">
-      <c r="A20" s="2">
+      <c r="A20" s="5">
         <v>1259.1</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:3">
-      <c r="A21" s="2">
+      <c r="A21" s="5">
         <v>1000</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:3">
-      <c r="A22" s="2">
+      <c r="A22" s="5">
         <v>13260</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:3">
-      <c r="A23" s="2">
+      <c r="A23" s="5">
         <v>47.97</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:3">
-      <c r="A24" s="2">
+      <c r="A24" s="5">
         <v>276.1</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:3">
-      <c r="A25" s="2">
+      <c r="A25" s="5">
         <v>6000</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:3">
-      <c r="A26" s="2">
+      <c r="A26" s="5">
         <v>640</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:3">
-      <c r="A27" s="2">
+      <c r="A27" s="5">
         <v>500</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:3">
-      <c r="A28" s="2">
+      <c r="A28" s="5">
         <v>600</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:3">
-      <c r="A29" s="2">
+      <c r="A29" s="5">
         <v>938</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="15" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:3">
-      <c r="A30" s="2">
+      <c r="A30" s="5">
         <v>1000</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:3">
-      <c r="A31" s="2">
+      <c r="A31" s="5">
         <v>60.5</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:3">
-      <c r="A32" s="2">
+      <c r="A32" s="5">
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="15" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:3">
-      <c r="A33" s="2">
+      <c r="A33" s="5">
         <v>42.16</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="15" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:3">
-      <c r="A34" s="2">
+      <c r="A34" s="5">
         <v>1000</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:3">
-      <c r="A35" s="5">
+      <c r="A35" s="8">
         <v>500</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:3">
-      <c r="A36" s="5">
+      <c r="A36" s="8">
         <v>1300</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="B36" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:3">
-      <c r="A37" s="5">
+      <c r="A37" s="8">
         <v>253.84</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="16" t="s">
+      <c r="B37" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:3">
-      <c r="A38" s="5">
+      <c r="A38" s="8">
         <v>1000</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="16" t="s">
+      <c r="B38" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="17" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:3">
-      <c r="A39" s="5">
+      <c r="A39" s="8">
         <v>355.3</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="B39" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:3">
-      <c r="A40" s="5">
+      <c r="A40" s="8">
         <v>3000</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="16" t="s">
+      <c r="B40" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:3">
-      <c r="A41" s="5">
+      <c r="A41" s="8">
         <v>174</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="B41" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:3">
-      <c r="A42" s="5">
+      <c r="A42" s="8">
         <v>33.6</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:3">
-      <c r="A43" s="5">
+      <c r="A43" s="8">
         <v>500</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="16" t="s">
+      <c r="B43" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="17" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1988,7 +1934,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -1996,334 +1942,374 @@
     <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:3">
+    <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="3">
+        <f>SUM(成本明细表_6[成本明细])</f>
+        <v>36512.81</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="3">
+        <f>SUM(营业额明细表_5[营业额明细])</f>
+        <v>42435.74</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3">
+        <f>B2-B1</f>
+        <v>5922.93</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="2">
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="5">
         <v>4333</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:3">
-      <c r="A3" s="2">
+      <c r="C7" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="5">
         <v>7500</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:3">
-      <c r="A4" s="2">
+      <c r="B8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:3">
+      <c r="A9" s="5">
         <v>1000</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="2">
+    <row r="10" customHeight="1" spans="1:3">
+      <c r="A10" s="5">
         <v>13260</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="2">
+    <row r="11" customHeight="1" spans="1:3">
+      <c r="A11" s="5">
         <v>600</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C11" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="2">
+    <row r="12" customHeight="1" spans="1:3">
+      <c r="A12" s="5">
         <v>938</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="2">
-        <v>60.5</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:3">
-      <c r="A10" s="2">
-        <v>162.41</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:3">
-      <c r="A11" s="2">
-        <v>42.16</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:3">
-      <c r="A12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:3">
       <c r="A13" s="5">
-        <v>1300</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>47</v>
+        <v>1000</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
       <c r="A14" s="5">
-        <v>253.84</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="4" t="s">
+        <v>60.5</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
       <c r="A15" s="5">
-        <v>1000</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>26</v>
+        <v>162.41</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
       <c r="A16" s="5">
-        <v>355.3</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>36</v>
+        <v>42.16</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
       <c r="A17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="8">
+        <v>1300</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="8">
+        <v>253.84</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="8">
+        <v>1000</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="8">
+        <v>355.3</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="8">
         <v>3000</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="5">
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="8">
         <v>174</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="5">
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="8">
         <v>33.6</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B24" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C24" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="5">
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="8">
         <v>500</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="9" t="s">
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C29" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="10">
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="12">
         <v>6683.96</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="10">
+      <c r="B30" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:3">
+      <c r="A31" s="12">
         <v>1861.8</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="10">
+      <c r="B31" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="12">
         <v>0</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="10">
+      <c r="B32" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="12">
         <v>19919.1</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="10">
+      <c r="B33" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="6"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="12">
         <v>13970.88</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="11">
-        <f>SUM(成本明细表_6[成本明细])</f>
-        <v>36512.81</v>
-      </c>
-      <c r="C32" s="12"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="11">
-        <f>SUM(营业额明细表_5[营业额明细])</f>
-        <v>42435.74</v>
-      </c>
-      <c r="C33" s="13"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="8" t="s">
+      <c r="B34" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="13"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:1">
-      <c r="A36" t="s">
-        <v>57</v>
-      </c>
+      <c r="C34" s="6"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="13"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="14"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:3">
+      <c r="A39" s="2"/>
+      <c r="C39" s="14"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="6"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:3">
+      <c r="A44" s="12"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="6"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:3">
+      <c r="A45" s="12"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="6"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:3">
+      <c r="A46" s="12"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:3">
+      <c r="A47" s="12"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="6"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:3">
+      <c r="A48" s="12"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B24">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B20">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2341,7 +2327,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -2349,389 +2335,363 @@
     <col min="3" max="3" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:3">
+    <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="3">
+        <f>SUM(成本明细表[成本明细])</f>
+        <v>41008.22</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="3">
+        <f>SUM(营业额明细表[营业额明细])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="4">
+        <f>B2-B1</f>
+        <v>-41008.22</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="2">
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="5">
         <v>4333</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:3">
-      <c r="A3" s="2">
+      <c r="C7" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="5">
         <v>17000</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:3">
-      <c r="A4" s="2">
+      <c r="B8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:3">
+      <c r="A9" s="5">
         <v>4140</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:3">
+      <c r="A10" s="5">
+        <v>7866</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="2">
-        <v>7866</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="11" customHeight="1" spans="1:3">
+      <c r="A11" s="5">
+        <v>28.64</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="2">
-        <v>28.64</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    <row r="12" customHeight="1" spans="1:3">
+      <c r="A12" s="5">
+        <v>44.48</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:3">
+      <c r="A13" s="5">
+        <v>3000</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:3">
+      <c r="A14" s="5">
+        <v>23</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="2">
-        <v>44.48</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="2">
-        <v>3000</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="2">
-        <v>23</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4" t="s">
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="5">
+        <v>468</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
-      <c r="A10" s="2">
-        <v>468</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="5">
+        <v>385</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:3">
-      <c r="A11" s="2">
-        <v>385</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="4" t="s">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A17" s="5">
+        <v>295</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A12" s="2">
-        <v>295</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A18" s="5">
+        <v>718</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A13" s="2">
-        <v>718</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4" t="s">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A19" s="5">
+        <v>57.6</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A14" s="2">
-        <v>57.6</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="2">
-        <v>302.5</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="2">
-        <v>1000</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="5">
-        <v>225</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="5">
-        <v>350</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="5">
-        <v>112</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
       <c r="A20" s="5">
-        <v>198</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>72</v>
+        <v>302.5</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
       <c r="A21" s="5">
+        <v>1000</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="8">
+        <v>225</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="8">
+        <v>350</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="8">
+        <v>112</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="8">
+        <v>198</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="8">
         <v>100</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C26" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="9">
+        <v>362</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="6">
-        <v>362</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="7" t="s">
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:3">
+      <c r="A31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="12">
+        <v>0</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="3"/>
+      <c r="C32" s="6"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="A33" s="12">
+        <v>0</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="6"/>
     </row>
     <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="10">
+      <c r="A34" s="12">
         <v>0</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="3"/>
+      <c r="B34" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="6"/>
     </row>
     <row r="35" customHeight="1" spans="1:3">
-      <c r="A35" s="10">
+      <c r="A35" s="12">
         <v>0</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:3">
-      <c r="A36" s="10">
-        <v>0</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="B35" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:3">
-      <c r="A37" s="10">
-        <v>0</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="3"/>
+      <c r="C35" s="6"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="13"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:3">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="14"/>
     </row>
     <row r="40" customHeight="1" spans="1:3">
-      <c r="A40" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="11">
-        <f>SUM(成本明细表[成本明细])</f>
-        <v>41008.22</v>
-      </c>
-      <c r="C40" s="12"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:3">
-      <c r="A41" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="11">
-        <f>SUM(营业额明细表[营业额明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C41" s="13"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:3">
-      <c r="A42" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" s="13"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:1">
-      <c r="A43" t="s">
-        <v>80</v>
-      </c>
+      <c r="A40" s="2"/>
+      <c r="C40" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20 B21 B22 B2:B19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25 B26 B27 B7:B24">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
   <tableParts count="2">
+    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
+    <workbookView windowWidth="28000" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -257,13 +257,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -289,7 +289,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,6 +303,21 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -310,25 +325,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +348,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -350,8 +363,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -366,22 +387,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -395,27 +401,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -424,9 +409,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -441,25 +441,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,7 +585,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,145 +615,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,6 +632,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -660,6 +678,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -670,26 +703,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -711,184 +724,171 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -897,19 +897,13 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -985,7 +979,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -1021,7 +1015,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -1058,7 +1052,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1453,14 +1447,14 @@
   <cols>
     <col min="1" max="1" width="23.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="15" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13">
+      <c r="C1" s="11">
         <v>100000</v>
       </c>
     </row>
@@ -1468,7 +1462,7 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <f>SUM(成本明细[金额(元)])</f>
         <v>99761.38</v>
       </c>
@@ -1477,7 +1471,7 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="12">
         <f>C1-C2</f>
         <v>238.619999999981</v>
       </c>
@@ -1487,7 +1481,7 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1666,7 +1660,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1710,7 +1704,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1721,7 +1715,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1732,7 +1726,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1743,7 +1737,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1754,7 +1748,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1765,7 +1759,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1776,7 +1770,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="13" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1787,7 +1781,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1798,7 +1792,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1809,7 +1803,7 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1817,10 +1811,10 @@
       <c r="A35" s="8">
         <v>500</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1828,10 +1822,10 @@
       <c r="A36" s="8">
         <v>1300</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="17" t="s">
+      <c r="B36" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1839,10 +1833,10 @@
       <c r="A37" s="8">
         <v>253.84</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="17" t="s">
+      <c r="B37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1850,10 +1844,10 @@
       <c r="A38" s="8">
         <v>1000</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="17" t="s">
+      <c r="B38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1861,10 +1855,10 @@
       <c r="A39" s="8">
         <v>355.3</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="17" t="s">
+      <c r="B39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1872,10 +1866,10 @@
       <c r="A40" s="8">
         <v>3000</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="17" t="s">
+      <c r="B40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1883,10 +1877,10 @@
       <c r="A41" s="8">
         <v>174</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="17" t="s">
+      <c r="B41" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1894,10 +1888,10 @@
       <c r="A42" s="8">
         <v>33.6</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="15" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1905,10 +1899,10 @@
       <c r="A43" s="8">
         <v>500</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="17" t="s">
+      <c r="B43" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1948,7 +1942,7 @@
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表_6[成本明细])</f>
-        <v>36512.81</v>
+        <v>37512.81</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:2">
@@ -1966,7 +1960,7 @@
       </c>
       <c r="B3" s="3">
         <f>B2-B1</f>
-        <v>5922.93</v>
+        <v>4922.92999999999</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
@@ -1993,7 +1987,7 @@
     </row>
     <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="5">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>48</v>
@@ -2191,24 +2185,24 @@
     </row>
     <row r="26" customHeight="1" spans="1:3">
       <c r="A26" s="2"/>
-      <c r="B26" s="11"/>
+      <c r="B26" s="9"/>
       <c r="C26" s="6"/>
     </row>
     <row r="27" customHeight="1" spans="1:3">
       <c r="A27" s="2"/>
-      <c r="B27" s="11"/>
+      <c r="B27" s="9"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" customHeight="1" spans="1:3">
       <c r="A28" s="2"/>
-      <c r="B28" s="11"/>
+      <c r="B28" s="9"/>
       <c r="C28" s="6"/>
     </row>
     <row r="29" customHeight="1" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -2216,46 +2210,46 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="12">
+      <c r="A30" s="10">
         <v>6683.96</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C30" s="6"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="12">
+      <c r="A31" s="10">
         <v>1861.8</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="6"/>
     </row>
     <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="12">
+      <c r="A32" s="10">
         <v>0</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C32" s="6"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="12">
+      <c r="A33" s="10">
         <v>19919.1</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C33" s="6"/>
     </row>
     <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="12">
+      <c r="A34" s="10">
         <v>13970.88</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C34" s="6"/>
@@ -2263,45 +2257,45 @@
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="13"/>
+      <c r="C37" s="11"/>
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="14"/>
+      <c r="C38" s="12"/>
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="2"/>
-      <c r="C39" s="14"/>
+      <c r="C39" s="12"/>
     </row>
     <row r="43" customHeight="1" spans="1:3">
       <c r="A43" s="2"/>
-      <c r="B43" s="11"/>
+      <c r="B43" s="9"/>
       <c r="C43" s="6"/>
     </row>
     <row r="44" customHeight="1" spans="1:3">
-      <c r="A44" s="12"/>
-      <c r="B44" s="11"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="9"/>
       <c r="C44" s="6"/>
     </row>
     <row r="45" customHeight="1" spans="1:3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="11"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="9"/>
       <c r="C45" s="6"/>
     </row>
     <row r="46" customHeight="1" spans="1:3">
-      <c r="A46" s="12"/>
-      <c r="B46" s="11"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="9"/>
       <c r="C46" s="6"/>
     </row>
     <row r="47" customHeight="1" spans="1:3">
-      <c r="A47" s="12"/>
-      <c r="B47" s="11"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="9"/>
       <c r="C47" s="6"/>
     </row>
     <row r="48" customHeight="1" spans="1:3">
-      <c r="A48" s="12"/>
-      <c r="B48" s="11"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="9"/>
       <c r="C48" s="6"/>
     </row>
   </sheetData>
@@ -2594,36 +2588,36 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="9">
+      <c r="A27" s="8">
         <v>362</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="B27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:3">
       <c r="A28" s="2"/>
-      <c r="B28" s="11"/>
+      <c r="B28" s="9"/>
       <c r="C28" s="6"/>
     </row>
     <row r="29" customHeight="1" spans="1:3">
       <c r="A29" s="2"/>
-      <c r="B29" s="11"/>
+      <c r="B29" s="9"/>
       <c r="C29" s="6"/>
     </row>
     <row r="30" customHeight="1" spans="1:3">
       <c r="A30" s="2"/>
-      <c r="B30" s="11"/>
+      <c r="B30" s="9"/>
       <c r="C30" s="6"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
       <c r="A31" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -2631,37 +2625,37 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="12">
+      <c r="A32" s="10">
         <v>0</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C32" s="6"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="12">
+      <c r="A33" s="10">
         <v>0</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C33" s="6"/>
     </row>
     <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="12">
+      <c r="A34" s="10">
         <v>0</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="9" t="s">
         <v>76</v>
       </c>
       <c r="C34" s="6"/>
     </row>
     <row r="35" customHeight="1" spans="1:3">
-      <c r="A35" s="12">
+      <c r="A35" s="10">
         <v>0</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="9" t="s">
         <v>77</v>
       </c>
       <c r="C35" s="6"/>
@@ -2669,16 +2663,16 @@
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="13"/>
+      <c r="C38" s="11"/>
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
-      <c r="C39" s="14"/>
+      <c r="C39" s="12"/>
     </row>
     <row r="40" customHeight="1" spans="1:3">
       <c r="A40" s="2"/>
-      <c r="C40" s="14"/>
+      <c r="C40" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15820" activeTab="1"/>
+    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="80">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>硕美牛肉丸样品20斤，17一斤+22运费</t>
+  </si>
+  <si>
+    <t>京东推广</t>
+  </si>
+  <si>
+    <t>一次性塑料袋和一次性勺子，塑料袋1分钱/个，勺子8分钱/个</t>
   </si>
   <si>
     <t>堂食</t>
@@ -257,12 +263,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -302,14 +308,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
@@ -325,6 +323,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -333,8 +346,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -349,7 +379,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -357,15 +387,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -385,45 +423,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -431,6 +430,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -453,43 +459,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,127 +627,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,11 +650,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,17 +674,43 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -692,185 +730,153 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -880,14 +886,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -900,10 +906,16 @@
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1015,7 +1027,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     </dxf>
     <dxf>
       <font>
@@ -1121,7 +1133,13 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
-  <autoFilter ref="A6:C25"/>
+  <autoFilter ref="A6:C25">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="equal" val="推广"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="3">
     <tableColumn id="1" name="成本明细"/>
     <tableColumn id="2" name="分类"/>
@@ -1132,8 +1150,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A31:C35" totalsRowShown="0">
-  <autoFilter ref="A31:C35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A34:C38" totalsRowShown="0">
+  <autoFilter ref="A34:C38"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1144,8 +1162,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C27" totalsRowShown="0">
-  <autoFilter ref="A6:C27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C29" totalsRowShown="0">
+  <autoFilter ref="A6:C29"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1447,14 +1465,14 @@
   <cols>
     <col min="1" max="1" width="23.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="13">
         <v>100000</v>
       </c>
     </row>
@@ -1462,7 +1480,7 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="14">
         <f>SUM(成本明细[金额(元)])</f>
         <v>99761.38</v>
       </c>
@@ -1471,7 +1489,7 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="14">
         <f>C1-C2</f>
         <v>238.619999999981</v>
       </c>
@@ -1481,7 +1499,7 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1660,7 +1678,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1704,7 +1722,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1715,7 +1733,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1726,7 +1744,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="15" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1737,7 +1755,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="15" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1748,7 +1766,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="15" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1759,7 +1777,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1770,7 +1788,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1781,7 +1799,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="15" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1792,7 +1810,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="15" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1803,7 +1821,7 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1811,10 +1829,10 @@
       <c r="A35" s="8">
         <v>500</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="17" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1822,10 +1840,10 @@
       <c r="A36" s="8">
         <v>1300</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="17" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1833,10 +1851,10 @@
       <c r="A37" s="8">
         <v>253.84</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="17" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1844,10 +1862,10 @@
       <c r="A38" s="8">
         <v>1000</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="15" t="s">
+      <c r="B38" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="17" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1855,10 +1873,10 @@
       <c r="A39" s="8">
         <v>355.3</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="B39" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="17" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1866,10 +1884,10 @@
       <c r="A40" s="8">
         <v>3000</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="15" t="s">
+      <c r="B40" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="17" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1877,10 +1895,10 @@
       <c r="A41" s="8">
         <v>174</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="15" t="s">
+      <c r="B41" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1888,10 +1906,10 @@
       <c r="A42" s="8">
         <v>33.6</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="17" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1899,10 +1917,10 @@
       <c r="A43" s="8">
         <v>500</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="15" t="s">
+      <c r="B43" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="17" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1974,7 +1992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
+    <row r="7" hidden="1" customHeight="1" spans="1:3">
       <c r="A7" s="5">
         <v>4333</v>
       </c>
@@ -1985,7 +2003,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:3">
+    <row r="8" hidden="1" customHeight="1" spans="1:3">
       <c r="A8" s="5">
         <v>8500</v>
       </c>
@@ -1996,7 +2014,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:3">
+    <row r="9" hidden="1" customHeight="1" spans="1:3">
       <c r="A9" s="5">
         <v>1000</v>
       </c>
@@ -2007,7 +2025,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
+    <row r="10" hidden="1" customHeight="1" spans="1:3">
       <c r="A10" s="5">
         <v>13260</v>
       </c>
@@ -2029,7 +2047,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:3">
+    <row r="12" hidden="1" customHeight="1" spans="1:3">
       <c r="A12" s="5">
         <v>938</v>
       </c>
@@ -2040,7 +2058,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:3">
+    <row r="13" hidden="1" customHeight="1" spans="1:3">
       <c r="A13" s="5">
         <v>1000</v>
       </c>
@@ -2051,7 +2069,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:3">
+    <row r="14" hidden="1" customHeight="1" spans="1:3">
       <c r="A14" s="5">
         <v>60.5</v>
       </c>
@@ -2062,7 +2080,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:3">
+    <row r="15" hidden="1" customHeight="1" spans="1:3">
       <c r="A15" s="5">
         <v>162.41</v>
       </c>
@@ -2073,7 +2091,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
+    <row r="16" hidden="1" customHeight="1" spans="1:3">
       <c r="A16" s="5">
         <v>42.16</v>
       </c>
@@ -2084,7 +2102,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:3">
+    <row r="17" hidden="1" customHeight="1" spans="1:3">
       <c r="A17" s="5">
         <v>1000</v>
       </c>
@@ -2095,7 +2113,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:3">
+    <row r="18" hidden="1" customHeight="1" spans="1:3">
       <c r="A18" s="8">
         <v>1300</v>
       </c>
@@ -2106,7 +2124,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:3">
+    <row r="19" hidden="1" customHeight="1" spans="1:3">
       <c r="A19" s="8">
         <v>253.84</v>
       </c>
@@ -2117,7 +2135,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
+    <row r="20" hidden="1" customHeight="1" spans="1:3">
       <c r="A20" s="8">
         <v>1000</v>
       </c>
@@ -2128,7 +2146,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:3">
+    <row r="21" hidden="1" customHeight="1" spans="1:3">
       <c r="A21" s="8">
         <v>355.3</v>
       </c>
@@ -2139,7 +2157,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:3">
+    <row r="22" hidden="1" customHeight="1" spans="1:3">
       <c r="A22" s="8">
         <v>3000</v>
       </c>
@@ -2150,7 +2168,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:3">
+    <row r="23" hidden="1" customHeight="1" spans="1:3">
       <c r="A23" s="8">
         <v>174</v>
       </c>
@@ -2161,7 +2179,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:3">
+    <row r="24" hidden="1" customHeight="1" spans="1:3">
       <c r="A24" s="8">
         <v>33.6</v>
       </c>
@@ -2172,7 +2190,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:3">
+    <row r="25" hidden="1" customHeight="1" spans="1:3">
       <c r="A25" s="8">
         <v>500</v>
       </c>
@@ -2185,24 +2203,24 @@
     </row>
     <row r="26" customHeight="1" spans="1:3">
       <c r="A26" s="2"/>
-      <c r="B26" s="9"/>
+      <c r="B26" s="11"/>
       <c r="C26" s="6"/>
     </row>
     <row r="27" customHeight="1" spans="1:3">
       <c r="A27" s="2"/>
-      <c r="B27" s="9"/>
+      <c r="B27" s="11"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" customHeight="1" spans="1:3">
       <c r="A28" s="2"/>
-      <c r="B28" s="9"/>
+      <c r="B28" s="11"/>
       <c r="C28" s="6"/>
     </row>
     <row r="29" customHeight="1" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -2210,46 +2228,46 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="10">
+      <c r="A30" s="12">
         <v>6683.96</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C30" s="6"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="10">
+      <c r="A31" s="12">
         <v>1861.8</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="11" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="6"/>
     </row>
     <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="10">
+      <c r="A32" s="12">
         <v>0</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C32" s="6"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="10">
+      <c r="A33" s="12">
         <v>19919.1</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="11" t="s">
         <v>55</v>
       </c>
       <c r="C33" s="6"/>
     </row>
     <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="10">
+      <c r="A34" s="12">
         <v>13970.88</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="11" t="s">
         <v>56</v>
       </c>
       <c r="C34" s="6"/>
@@ -2257,45 +2275,45 @@
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="11"/>
+      <c r="C37" s="13"/>
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="12"/>
+      <c r="C38" s="14"/>
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="2"/>
-      <c r="C39" s="12"/>
+      <c r="C39" s="14"/>
     </row>
     <row r="43" customHeight="1" spans="1:3">
       <c r="A43" s="2"/>
-      <c r="B43" s="9"/>
+      <c r="B43" s="11"/>
       <c r="C43" s="6"/>
     </row>
     <row r="44" customHeight="1" spans="1:3">
-      <c r="A44" s="10"/>
-      <c r="B44" s="9"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="11"/>
       <c r="C44" s="6"/>
     </row>
     <row r="45" customHeight="1" spans="1:3">
-      <c r="A45" s="10"/>
-      <c r="B45" s="9"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="11"/>
       <c r="C45" s="6"/>
     </row>
     <row r="46" customHeight="1" spans="1:3">
-      <c r="A46" s="10"/>
-      <c r="B46" s="9"/>
+      <c r="A46" s="12"/>
+      <c r="B46" s="11"/>
       <c r="C46" s="6"/>
     </row>
     <row r="47" customHeight="1" spans="1:3">
-      <c r="A47" s="10"/>
-      <c r="B47" s="9"/>
+      <c r="A47" s="12"/>
+      <c r="B47" s="11"/>
       <c r="C47" s="6"/>
     </row>
     <row r="48" customHeight="1" spans="1:3">
-      <c r="A48" s="10"/>
-      <c r="B48" s="9"/>
+      <c r="A48" s="12"/>
+      <c r="B48" s="11"/>
       <c r="C48" s="6"/>
     </row>
   </sheetData>
@@ -2321,7 +2339,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -2335,7 +2353,7 @@
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>41008.22</v>
+        <v>40836.22</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:2">
@@ -2353,7 +2371,7 @@
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-41008.22</v>
+        <v>-40836.22</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
@@ -2523,7 +2541,7 @@
     </row>
     <row r="21" customHeight="1" spans="1:3">
       <c r="A21" s="5">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>32</v>
@@ -2599,84 +2617,111 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="6"/>
+      <c r="A28" s="9">
+        <v>300</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="6"/>
+      <c r="A29" s="9">
+        <v>128</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="30" customHeight="1" spans="1:3">
       <c r="A30" s="2"/>
-      <c r="B30" s="9"/>
+      <c r="B30" s="11"/>
       <c r="C30" s="6"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="2"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="6"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B34" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C34" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="10">
+    <row r="35" customHeight="1" spans="1:3">
+      <c r="A35" s="12">
         <v>0</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="10">
+      <c r="B35" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="6"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:3">
+      <c r="A36" s="12">
         <v>0</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="6"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="10">
+      <c r="B36" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="6"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:3">
+      <c r="A37" s="12">
         <v>0</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="6"/>
-    </row>
-    <row r="35" customHeight="1" spans="1:3">
-      <c r="A35" s="10">
+      <c r="B37" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="6"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:3">
+      <c r="A38" s="12">
         <v>0</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" s="6"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="11"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="12"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:3">
-      <c r="A40" s="2"/>
-      <c r="C40" s="12"/>
+      <c r="B38" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="6"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:3">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="13"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:3">
+      <c r="A43" s="2"/>
+      <c r="C43" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25 B26 B27 B7:B24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25 B26 B27 B28 B29 B7:B24">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -240,7 +240,7 @@
     <t>硕美牛肉丸样品20斤，17一斤+22运费</t>
   </si>
   <si>
-    <t>京东推广</t>
+    <t>京东外卖推广</t>
   </si>
   <si>
     <t>一次性塑料袋和一次性勺子，塑料袋1分钱/个，勺子8分钱/个</t>
@@ -264,12 +264,12 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
     <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -308,10 +308,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -331,42 +332,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -378,8 +347,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -387,15 +365,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -410,6 +387,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -417,15 +401,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -437,6 +413,30 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -453,181 +453,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -650,17 +650,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -684,21 +678,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -730,153 +709,174 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -886,7 +886,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -904,12 +904,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1465,14 +1459,14 @@
   <cols>
     <col min="1" max="1" width="23.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="15" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13">
+      <c r="C1" s="11">
         <v>100000</v>
       </c>
     </row>
@@ -1480,7 +1474,7 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <f>SUM(成本明细[金额(元)])</f>
         <v>99761.38</v>
       </c>
@@ -1489,7 +1483,7 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="12">
         <f>C1-C2</f>
         <v>238.619999999981</v>
       </c>
@@ -1499,7 +1493,7 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1678,7 +1672,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1722,7 +1716,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1733,7 +1727,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1744,7 +1738,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1755,7 +1749,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1766,7 +1760,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1777,7 +1771,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1788,7 +1782,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="13" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1799,7 +1793,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1810,7 +1804,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1821,7 +1815,7 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1829,10 +1823,10 @@
       <c r="A35" s="8">
         <v>500</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1840,10 +1834,10 @@
       <c r="A36" s="8">
         <v>1300</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="17" t="s">
+      <c r="B36" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1851,10 +1845,10 @@
       <c r="A37" s="8">
         <v>253.84</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="17" t="s">
+      <c r="B37" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1862,10 +1856,10 @@
       <c r="A38" s="8">
         <v>1000</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="17" t="s">
+      <c r="B38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1873,10 +1867,10 @@
       <c r="A39" s="8">
         <v>355.3</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="17" t="s">
+      <c r="B39" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1884,10 +1878,10 @@
       <c r="A40" s="8">
         <v>3000</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="17" t="s">
+      <c r="B40" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1895,10 +1889,10 @@
       <c r="A41" s="8">
         <v>174</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="17" t="s">
+      <c r="B41" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1906,10 +1900,10 @@
       <c r="A42" s="8">
         <v>33.6</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="15" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1917,10 +1911,10 @@
       <c r="A43" s="8">
         <v>500</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="17" t="s">
+      <c r="B43" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2203,24 +2197,24 @@
     </row>
     <row r="26" customHeight="1" spans="1:3">
       <c r="A26" s="2"/>
-      <c r="B26" s="11"/>
+      <c r="B26" s="9"/>
       <c r="C26" s="6"/>
     </row>
     <row r="27" customHeight="1" spans="1:3">
       <c r="A27" s="2"/>
-      <c r="B27" s="11"/>
+      <c r="B27" s="9"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" customHeight="1" spans="1:3">
       <c r="A28" s="2"/>
-      <c r="B28" s="11"/>
+      <c r="B28" s="9"/>
       <c r="C28" s="6"/>
     </row>
     <row r="29" customHeight="1" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -2228,46 +2222,46 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="12">
+      <c r="A30" s="10">
         <v>6683.96</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C30" s="6"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="12">
+      <c r="A31" s="10">
         <v>1861.8</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="6"/>
     </row>
     <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="12">
+      <c r="A32" s="10">
         <v>0</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C32" s="6"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="12">
+      <c r="A33" s="10">
         <v>19919.1</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C33" s="6"/>
     </row>
     <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="12">
+      <c r="A34" s="10">
         <v>13970.88</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C34" s="6"/>
@@ -2275,45 +2269,45 @@
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="13"/>
+      <c r="C37" s="11"/>
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="14"/>
+      <c r="C38" s="12"/>
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="2"/>
-      <c r="C39" s="14"/>
+      <c r="C39" s="12"/>
     </row>
     <row r="43" customHeight="1" spans="1:3">
       <c r="A43" s="2"/>
-      <c r="B43" s="11"/>
+      <c r="B43" s="9"/>
       <c r="C43" s="6"/>
     </row>
     <row r="44" customHeight="1" spans="1:3">
-      <c r="A44" s="12"/>
-      <c r="B44" s="11"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="9"/>
       <c r="C44" s="6"/>
     </row>
     <row r="45" customHeight="1" spans="1:3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="11"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="9"/>
       <c r="C45" s="6"/>
     </row>
     <row r="46" customHeight="1" spans="1:3">
-      <c r="A46" s="12"/>
-      <c r="B46" s="11"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="9"/>
       <c r="C46" s="6"/>
     </row>
     <row r="47" customHeight="1" spans="1:3">
-      <c r="A47" s="12"/>
-      <c r="B47" s="11"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="9"/>
       <c r="C47" s="6"/>
     </row>
     <row r="48" customHeight="1" spans="1:3">
-      <c r="A48" s="12"/>
-      <c r="B48" s="11"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="9"/>
       <c r="C48" s="6"/>
     </row>
   </sheetData>
@@ -2617,52 +2611,52 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="9">
+      <c r="A28" s="8">
         <v>300</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="9">
+      <c r="A29" s="8">
         <v>128</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="10" t="s">
+      <c r="B29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:3">
       <c r="A30" s="2"/>
-      <c r="B30" s="11"/>
+      <c r="B30" s="9"/>
       <c r="C30" s="6"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
       <c r="A31" s="2"/>
-      <c r="B31" s="11"/>
+      <c r="B31" s="9"/>
       <c r="C31" s="6"/>
     </row>
     <row r="32" customHeight="1" spans="1:3">
       <c r="A32" s="2"/>
-      <c r="B32" s="11"/>
+      <c r="B32" s="9"/>
       <c r="C32" s="6"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
       <c r="A33" s="2"/>
-      <c r="B33" s="11"/>
+      <c r="B33" s="9"/>
       <c r="C33" s="6"/>
     </row>
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C34" s="6" t="s">
@@ -2670,37 +2664,37 @@
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:3">
-      <c r="A35" s="12">
+      <c r="A35" s="10">
         <v>0</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="9" t="s">
         <v>76</v>
       </c>
       <c r="C35" s="6"/>
     </row>
     <row r="36" customHeight="1" spans="1:3">
-      <c r="A36" s="12">
+      <c r="A36" s="10">
         <v>0</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="9" t="s">
         <v>77</v>
       </c>
       <c r="C36" s="6"/>
     </row>
     <row r="37" customHeight="1" spans="1:3">
-      <c r="A37" s="12">
+      <c r="A37" s="10">
         <v>0</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="9" t="s">
         <v>78</v>
       </c>
       <c r="C37" s="6"/>
     </row>
     <row r="38" customHeight="1" spans="1:3">
-      <c r="A38" s="12">
+      <c r="A38" s="10">
         <v>0</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="9" t="s">
         <v>79</v>
       </c>
       <c r="C38" s="6"/>
@@ -2708,16 +2702,16 @@
     <row r="41" customHeight="1" spans="1:3">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
-      <c r="C41" s="13"/>
+      <c r="C41" s="11"/>
     </row>
     <row r="42" customHeight="1" spans="1:3">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
-      <c r="C42" s="14"/>
+      <c r="C42" s="12"/>
     </row>
     <row r="43" customHeight="1" spans="1:3">
       <c r="A43" s="2"/>
-      <c r="C43" s="14"/>
+      <c r="C43" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,22 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAAFF72-B650-4930-B39D-B1ED666FF0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="2026-02流水 " sheetId="3" r:id="rId2"/>
     <sheet name="2026-03流水" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="83">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -216,62 +235,71 @@
     <t>外卖盒子临时补货</t>
   </si>
   <si>
+    <t>美团外卖推广</t>
+  </si>
+  <si>
+    <t>750圆打包盒600个，0.375/个</t>
+  </si>
+  <si>
+    <t>一次性餐具(筷子+勺子)，70元/500个，0.14/个</t>
+  </si>
+  <si>
+    <t>一次性筷子</t>
+  </si>
+  <si>
+    <t>福州鱼丸20包/198</t>
+  </si>
+  <si>
+    <t>京东外卖刷单</t>
+  </si>
+  <si>
+    <t>硕美牛肉丸样品20斤，17一斤+22运费</t>
+  </si>
+  <si>
+    <t>京东外卖推广</t>
+  </si>
+  <si>
+    <t>一次性塑料袋和一次性勺子，塑料袋1分钱/个，勺子8分钱/个</t>
+  </si>
+  <si>
+    <t>堂食</t>
+  </si>
+  <si>
+    <t>京东</t>
+  </si>
+  <si>
+    <t>淘宝</t>
+  </si>
+  <si>
+    <t>美团</t>
+  </si>
+  <si>
+    <t>食材</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>250ml可乐24瓶</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>火鸡面拼多多补货5箱共150袋</t>
-  </si>
-  <si>
-    <t>美团外卖推广</t>
-  </si>
-  <si>
-    <t>750圆打包盒600个，0.375/个</t>
-  </si>
-  <si>
-    <t>一次性餐具(筷子+勺子)，70元/500个，0.14/个</t>
-  </si>
-  <si>
-    <t>一次性筷子</t>
-  </si>
-  <si>
-    <t>福州鱼丸20包/198</t>
-  </si>
-  <si>
-    <t>京东外卖刷单</t>
-  </si>
-  <si>
-    <t>硕美牛肉丸样品20斤，17一斤+22运费</t>
-  </si>
-  <si>
-    <t>京东外卖推广</t>
-  </si>
-  <si>
-    <t>一次性塑料袋和一次性勺子，塑料袋1分钱/个，勺子8分钱/个</t>
-  </si>
-  <si>
-    <t>堂食</t>
-  </si>
-  <si>
-    <t>京东</t>
-  </si>
-  <si>
-    <t>淘宝</t>
-  </si>
-  <si>
-    <t>美团</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>300斤肉片2400+100斤牛肉羹1700+运费255.5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,345 +322,29 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -640,261 +352,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -903,13 +373,13 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -921,175 +391,133 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
+      <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1097,71 +525,74 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
-  <autoFilter ref="A5:C43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
+  <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
-    <tableColumn id="2" name="分类" dataDxfId="1"/>
-    <tableColumn id="3" name="说明" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A29:C34" totalsRowShown="0">
-  <autoFilter ref="A29:C34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A29:C34" totalsRowShown="0">
+  <autoFilter ref="A29:C34" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="营业额明细"/>
-    <tableColumn id="2" name="分类"/>
-    <tableColumn id="3" name="说明"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
-  <autoFilter ref="A6:C25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
+  <autoFilter ref="A6:C25" xr:uid="{00000000-0009-0000-0100-000005000000}">
     <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="equal" val="推广"/>
-      </customFilters>
+      <filters>
+        <filter val="推广"/>
+      </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" name="成本明细"/>
-    <tableColumn id="2" name="分类"/>
-    <tableColumn id="3" name="说明"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A34:C38" totalsRowShown="0">
-  <autoFilter ref="A34:C38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A36:C40" totalsRowShown="0">
+  <autoFilter ref="A36:C40" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
-    <tableColumn id="2" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" name="说明" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C29" totalsRowShown="0">
-  <autoFilter ref="A6:C29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A6:C32" totalsRowShown="0">
+  <autoFilter ref="A6:C32" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
-    <tableColumn id="4" name="分类" dataDxfId="7"/>
-    <tableColumn id="1" name="说明" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1446,23 +877,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1470,26 +902,26 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="12">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99761.38</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:3">
+        <v>99761.380000000019</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="12">
         <f>C1-C2</f>
-        <v>238.619999999981</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="5" ht="15" customHeight="1" spans="1:3">
+        <v>238.61999999998079</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1500,7 +932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5">
         <v>10000</v>
       </c>
@@ -1511,7 +943,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
         <v>26000</v>
       </c>
@@ -1522,7 +954,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5">
         <v>6000</v>
       </c>
@@ -1533,7 +965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5">
         <v>3000</v>
       </c>
@@ -1544,7 +976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5">
         <v>2100</v>
       </c>
@@ -1555,7 +987,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5">
         <v>340</v>
       </c>
@@ -1566,7 +998,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
         <v>200</v>
       </c>
@@ -1577,7 +1009,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5">
         <v>11000</v>
       </c>
@@ -1588,7 +1020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5">
         <v>5000</v>
       </c>
@@ -1599,7 +1031,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="5">
         <v>755</v>
       </c>
@@ -1610,7 +1042,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5">
         <v>190</v>
       </c>
@@ -1621,7 +1053,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5">
         <v>405.9</v>
       </c>
@@ -1632,7 +1064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5">
         <v>228</v>
       </c>
@@ -1643,7 +1075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5">
         <v>639.5</v>
       </c>
@@ -1654,9 +1086,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5">
-        <v>1259.1</v>
+        <v>1259.0999999999999</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -1665,7 +1097,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5">
         <v>1000</v>
       </c>
@@ -1676,7 +1108,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5">
         <v>13260</v>
       </c>
@@ -1687,7 +1119,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5">
         <v>47.97</v>
       </c>
@@ -1698,9 +1130,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5">
-        <v>276.1</v>
+        <v>276.10000000000002</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1709,7 +1141,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5">
         <v>6000</v>
       </c>
@@ -1720,7 +1152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5">
         <v>640</v>
       </c>
@@ -1731,7 +1163,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5">
         <v>500</v>
       </c>
@@ -1742,7 +1174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5">
         <v>600</v>
       </c>
@@ -1753,7 +1185,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5">
         <v>938</v>
       </c>
@@ -1764,7 +1196,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:3">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5">
         <v>1000</v>
       </c>
@@ -1775,7 +1207,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:3">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5">
         <v>60.5</v>
       </c>
@@ -1786,7 +1218,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:3">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5">
         <v>162.41</v>
       </c>
@@ -1797,7 +1229,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:3">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5">
         <v>42.16</v>
       </c>
@@ -1808,7 +1240,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:3">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5">
         <v>1000</v>
       </c>
@@ -1819,7 +1251,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:3">
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="8">
         <v>500</v>
       </c>
@@ -1830,7 +1262,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:3">
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8">
         <v>1300</v>
       </c>
@@ -1841,7 +1273,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:3">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8">
         <v>253.84</v>
       </c>
@@ -1852,7 +1284,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:3">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="8">
         <v>1000</v>
       </c>
@@ -1863,7 +1295,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:3">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="8">
         <v>355.3</v>
       </c>
@@ -1874,7 +1306,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:3">
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="8">
         <v>3000</v>
       </c>
@@ -1885,7 +1317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:3">
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="8">
         <v>174</v>
       </c>
@@ -1896,7 +1328,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:3">
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="8">
         <v>33.6</v>
       </c>
@@ -1907,7 +1339,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:3">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="8">
         <v>500</v>
       </c>
@@ -1919,16 +1351,16 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1936,28 +1368,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:2">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表_6[成本明细])</f>
-        <v>37512.81</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:2">
+        <v>37512.810000000005</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -1966,16 +1398,16 @@
         <v>42435.74</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:2">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="3">
         <f>B2-B1</f>
-        <v>4922.92999999999</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:3">
+        <v>4922.929999999993</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
@@ -1986,7 +1418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" hidden="1" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
         <v>4333</v>
       </c>
@@ -1997,7 +1429,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" hidden="1" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5">
         <v>8500</v>
       </c>
@@ -2008,7 +1440,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" hidden="1" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5">
         <v>1000</v>
       </c>
@@ -2019,7 +1451,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" hidden="1" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5">
         <v>13260</v>
       </c>
@@ -2030,7 +1462,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5">
         <v>600</v>
       </c>
@@ -2041,7 +1473,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" hidden="1" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
         <v>938</v>
       </c>
@@ -2052,7 +1484,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" hidden="1" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5">
         <v>1000</v>
       </c>
@@ -2063,7 +1495,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" hidden="1" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5">
         <v>60.5</v>
       </c>
@@ -2074,7 +1506,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" hidden="1" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="5">
         <v>162.41</v>
       </c>
@@ -2085,7 +1517,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" hidden="1" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5">
         <v>42.16</v>
       </c>
@@ -2096,7 +1528,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" hidden="1" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5">
         <v>1000</v>
       </c>
@@ -2107,7 +1539,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" hidden="1" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8">
         <v>1300</v>
       </c>
@@ -2118,7 +1550,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" hidden="1" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8">
         <v>253.84</v>
       </c>
@@ -2129,7 +1561,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" hidden="1" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8">
         <v>1000</v>
       </c>
@@ -2140,7 +1572,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" hidden="1" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8">
         <v>355.3</v>
       </c>
@@ -2151,7 +1583,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" hidden="1" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8">
         <v>3000</v>
       </c>
@@ -2162,7 +1594,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" hidden="1" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8">
         <v>174</v>
       </c>
@@ -2173,7 +1605,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" hidden="1" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>33.6</v>
       </c>
@@ -2184,7 +1616,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" hidden="1" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>500</v>
       </c>
@@ -2195,22 +1627,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2"/>
       <c r="B26" s="9"/>
       <c r="C26" s="6"/>
     </row>
-    <row r="27" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2"/>
       <c r="B27" s="9"/>
       <c r="C27" s="6"/>
     </row>
-    <row r="28" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2"/>
       <c r="B28" s="9"/>
       <c r="C28" s="6"/>
     </row>
-    <row r="29" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
@@ -2221,7 +1653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:3">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10">
         <v>6683.96</v>
       </c>
@@ -2230,7 +1662,7 @@
       </c>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" customHeight="1" spans="1:3">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10">
         <v>1861.8</v>
       </c>
@@ -2239,7 +1671,7 @@
       </c>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" customHeight="1" spans="1:3">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10">
         <v>0</v>
       </c>
@@ -2248,16 +1680,16 @@
       </c>
       <c r="C32" s="6"/>
     </row>
-    <row r="33" customHeight="1" spans="1:3">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10">
-        <v>19919.1</v>
+        <v>19919.099999999999</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C33" s="6"/>
     </row>
-    <row r="34" customHeight="1" spans="1:3">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10">
         <v>13970.88</v>
       </c>
@@ -2266,61 +1698,61 @@
       </c>
       <c r="C34" s="6"/>
     </row>
-    <row r="37" customHeight="1" spans="1:3">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="11"/>
     </row>
-    <row r="38" customHeight="1" spans="1:3">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="12"/>
     </row>
-    <row r="39" customHeight="1" spans="1:3">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2"/>
       <c r="C39" s="12"/>
     </row>
-    <row r="43" customHeight="1" spans="1:3">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2"/>
       <c r="B43" s="9"/>
       <c r="C43" s="6"/>
     </row>
-    <row r="44" customHeight="1" spans="1:3">
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="9"/>
       <c r="C44" s="6"/>
     </row>
-    <row r="45" customHeight="1" spans="1:3">
+    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="9"/>
       <c r="C45" s="6"/>
     </row>
-    <row r="46" customHeight="1" spans="1:3">
+    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="9"/>
       <c r="C46" s="6"/>
     </row>
-    <row r="47" customHeight="1" spans="1:3">
+    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="9"/>
       <c r="C47" s="6"/>
     </row>
-    <row r="48" customHeight="1" spans="1:3">
+    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="9"/>
       <c r="C48" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B24" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B20" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
@@ -2329,28 +1761,28 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:2">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>40836.22</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:2">
+        <v>45522.35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -2359,16 +1791,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:2">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-40836.22</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:3">
+        <v>-45522.35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
@@ -2379,7 +1811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
         <v>4333</v>
       </c>
@@ -2390,7 +1822,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5">
         <v>17000</v>
       </c>
@@ -2401,7 +1833,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5">
         <v>4140</v>
       </c>
@@ -2412,7 +1844,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5">
         <v>7866</v>
       </c>
@@ -2423,7 +1855,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5">
         <v>28.64</v>
       </c>
@@ -2434,7 +1866,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
         <v>44.48</v>
       </c>
@@ -2445,7 +1877,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5">
         <v>3000</v>
       </c>
@@ -2456,7 +1888,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5">
         <v>23</v>
       </c>
@@ -2467,7 +1899,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="5">
         <v>468</v>
       </c>
@@ -2478,7 +1910,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5">
         <v>385</v>
       </c>
@@ -2489,7 +1921,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5">
         <v>295</v>
       </c>
@@ -2500,7 +1932,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5">
         <v>718</v>
       </c>
@@ -2511,7 +1943,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5">
         <v>57.6</v>
       </c>
@@ -2522,18 +1954,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5">
         <v>302.5</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:3">
+      <c r="C20" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5">
         <v>400</v>
       </c>
@@ -2541,10 +1973,10 @@
         <v>32</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8">
         <v>225</v>
       </c>
@@ -2552,10 +1984,10 @@
         <v>25</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8">
         <v>350</v>
       </c>
@@ -2563,10 +1995,10 @@
         <v>25</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>112</v>
       </c>
@@ -2574,10 +2006,10 @@
         <v>25</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>198</v>
       </c>
@@ -2585,10 +2017,10 @@
         <v>25</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>100</v>
       </c>
@@ -2596,10 +2028,10 @@
         <v>32</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8">
         <v>362</v>
       </c>
@@ -2607,10 +2039,10 @@
         <v>25</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8">
         <v>300</v>
       </c>
@@ -2618,10 +2050,10 @@
         <v>32</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8">
         <v>128</v>
       </c>
@@ -2629,99 +2061,127 @@
         <v>25</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="6"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="8">
+        <v>26</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="16">
+        <v>304.63</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="16">
+        <v>4355.5</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="16"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+    </row>
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="2"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="6"/>
+    </row>
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="2"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="6"/>
+    </row>
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B36" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C36" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:3">
-      <c r="A35" s="10">
-        <v>0</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="6"/>
-    </row>
-    <row r="36" customHeight="1" spans="1:3">
-      <c r="A36" s="10">
-        <v>0</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="6"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:3">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10">
         <v>0</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C37" s="6"/>
     </row>
-    <row r="38" customHeight="1" spans="1:3">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10">
         <v>0</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C38" s="6"/>
     </row>
-    <row r="41" customHeight="1" spans="1:3">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="11"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="12"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:3">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="10">
+        <v>0</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="6"/>
+    </row>
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="10">
+        <v>0</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="6"/>
+    </row>
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2"/>
-      <c r="C43" s="12"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="11"/>
+    </row>
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="12"/>
+    </row>
+    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="2"/>
+      <c r="C45" s="12"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25 B26 B27 B28 B29 B7:B24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B33" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAAFF72-B650-4930-B39D-B1ED666FF0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE535C7-1C9D-489D-9D8D-F191983BC3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="81">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -260,18 +260,6 @@
   </si>
   <si>
     <t>一次性塑料袋和一次性勺子，塑料袋1分钱/个，勺子8分钱/个</t>
-  </si>
-  <si>
-    <t>堂食</t>
-  </si>
-  <si>
-    <t>京东</t>
-  </si>
-  <si>
-    <t>淘宝</t>
-  </si>
-  <si>
-    <t>美团</t>
   </si>
   <si>
     <t>食材</t>
@@ -286,7 +274,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>300斤肉片2400+100斤牛肉羹1700+运费255.5</t>
+    <t>弹粉进货，4.5/斤，运费0.5/斤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>300斤肉片2400+100斤牛肉羹1700+运费255.5 = 4355.5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老李9元/斤买走20斤上述肉片</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -296,8 +292,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -356,15 +352,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -373,13 +369,13 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -391,10 +387,19 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -402,6 +407,61 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
+      <alignment horizontal="left"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -436,7 +496,7 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -468,57 +528,6 @@
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -536,9 +545,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
   <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -558,13 +567,7 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
-  <autoFilter ref="A6:C25" xr:uid="{00000000-0009-0000-0100-000005000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="推广"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A6:C25" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
@@ -575,24 +578,24 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A36:C40" totalsRowShown="0">
-  <autoFilter ref="A36:C40" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A37:C42" totalsRowShown="0">
+  <autoFilter ref="A37:C42" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A6:C32" totalsRowShown="0">
-  <autoFilter ref="A6:C32" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A6:C34" totalsRowShown="0">
+  <autoFilter ref="A6:C34" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1377,7 +1380,7 @@
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="23.25" customWidth="1"/>
+    <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1418,7 +1421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
         <v>4333</v>
       </c>
@@ -1429,7 +1432,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5">
         <v>8500</v>
       </c>
@@ -1440,7 +1443,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5">
         <v>1000</v>
       </c>
@@ -1451,7 +1454,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5">
         <v>13260</v>
       </c>
@@ -1473,7 +1476,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
         <v>938</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5">
         <v>1000</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5">
         <v>60.5</v>
       </c>
@@ -1506,7 +1509,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="5">
         <v>162.41</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5">
         <v>42.16</v>
       </c>
@@ -1528,7 +1531,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5">
         <v>1000</v>
       </c>
@@ -1539,7 +1542,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8">
         <v>1300</v>
       </c>
@@ -1550,7 +1553,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8">
         <v>253.84</v>
       </c>
@@ -1561,7 +1564,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8">
         <v>1000</v>
       </c>
@@ -1572,7 +1575,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8">
         <v>355.3</v>
       </c>
@@ -1583,7 +1586,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8">
         <v>3000</v>
       </c>
@@ -1594,7 +1597,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8">
         <v>174</v>
       </c>
@@ -1605,7 +1608,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>33.6</v>
       </c>
@@ -1616,7 +1619,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>500</v>
       </c>
@@ -1745,7 +1748,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B24" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B25" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B20" xr:uid="{00000000-0002-0000-0100-000001000000}">
@@ -1753,9 +1756,10 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1765,7 +1769,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -1779,7 +1783,7 @@
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>45522.35</v>
+        <v>45692.35</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1797,7 +1801,7 @@
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-45522.35</v>
+        <v>-45692.35</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1812,7 +1816,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="5">
+      <c r="A7" s="17">
         <v>4333</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1823,7 +1827,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="5">
+      <c r="A8" s="17">
         <v>17000</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -1834,7 +1838,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="5">
+      <c r="A9" s="17">
         <v>4140</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -1845,7 +1849,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="5">
+      <c r="A10" s="17">
         <v>7866</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -1856,7 +1860,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="5">
+      <c r="A11" s="17">
         <v>28.64</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -1867,7 +1871,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="5">
+      <c r="A12" s="17">
         <v>44.48</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -1878,7 +1882,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="5">
+      <c r="A13" s="17">
         <v>3000</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -1889,7 +1893,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="5">
+      <c r="A14" s="17">
         <v>23</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -1900,7 +1904,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="5">
+      <c r="A15" s="17">
         <v>468</v>
       </c>
       <c r="B15" s="7" t="s">
@@ -1911,7 +1915,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="5">
+      <c r="A16" s="17">
         <v>385</v>
       </c>
       <c r="B16" s="7" t="s">
@@ -1922,7 +1926,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="5">
+      <c r="A17" s="17">
         <v>295</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -1933,7 +1937,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="5">
+      <c r="A18" s="17">
         <v>718</v>
       </c>
       <c r="B18" s="7" t="s">
@@ -1944,7 +1948,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="5">
+      <c r="A19" s="17">
         <v>57.6</v>
       </c>
       <c r="B19" s="7" t="s">
@@ -1955,18 +1959,18 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="5">
+      <c r="A20" s="17">
         <v>302.5</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="17" t="s">
-        <v>81</v>
+      <c r="C20" s="16" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="5">
+      <c r="A21" s="17">
         <v>400</v>
       </c>
       <c r="B21" s="7" t="s">
@@ -1977,7 +1981,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="8">
+      <c r="A22" s="18">
         <v>225</v>
       </c>
       <c r="B22" s="7" t="s">
@@ -1988,7 +1992,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="8">
+      <c r="A23" s="18">
         <v>350</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -1999,7 +2003,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="8">
+      <c r="A24" s="18">
         <v>112</v>
       </c>
       <c r="B24" s="7" t="s">
@@ -2010,7 +2014,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="8">
+      <c r="A25" s="18">
         <v>198</v>
       </c>
       <c r="B25" s="7" t="s">
@@ -2021,7 +2025,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="8">
+      <c r="A26" s="18">
         <v>100</v>
       </c>
       <c r="B26" s="7" t="s">
@@ -2032,7 +2036,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="8">
+      <c r="A27" s="18">
         <v>362</v>
       </c>
       <c r="B27" s="7" t="s">
@@ -2043,7 +2047,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="8">
+      <c r="A28" s="18">
         <v>300</v>
       </c>
       <c r="B28" s="7" t="s">
@@ -2054,7 +2058,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="8">
+      <c r="A29" s="18">
         <v>128</v>
       </c>
       <c r="B29" s="7" t="s">
@@ -2065,47 +2069,59 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="8">
+      <c r="A30" s="18">
         <v>26</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="19">
+        <v>304.63</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="19">
+        <v>4355.5</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="17" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="19">
+        <v>-180</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="16">
-        <v>304.63</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="16">
-        <v>4355.5</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="16"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-    </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="2"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="6"/>
+      <c r="A34" s="19">
+        <v>350</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2"/>
@@ -2113,31 +2129,27 @@
       <c r="C35" s="6"/>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="2"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="6"/>
+    </row>
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B37" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="10">
-        <v>0</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="6"/>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10">
         <v>0</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C38" s="6"/>
     </row>
@@ -2146,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C39" s="6"/>
     </row>
@@ -2155,28 +2167,46 @@
         <v>0</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C40" s="6"/>
     </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="11"/>
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="10">
+        <v>0</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="6"/>
+    </row>
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="20">
+        <v>0</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="16"/>
     </row>
     <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
-      <c r="C44" s="12"/>
+      <c r="C44" s="11"/>
     </row>
     <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="2"/>
+      <c r="B45" s="3"/>
       <c r="C45" s="12"/>
+    </row>
+    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="2"/>
+      <c r="C46" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B33" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B34" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE535C7-1C9D-489D-9D8D-F191983BC3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -418,61 +418,6 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -528,6 +473,61 @@
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -545,9 +545,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
   <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -581,9 +581,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A37:C42" totalsRowShown="0">
   <autoFilter ref="A37:C42" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -593,9 +593,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A6:C34" totalsRowShown="0">
   <autoFilter ref="A6:C34" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="8"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE535C7-1C9D-489D-9D8D-F191983BC3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E2CDEF-82EC-44AB-AB41-9874923267D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="82">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -260,14 +260,6 @@
   </si>
   <si>
     <t>一次性塑料袋和一次性勺子，塑料袋1分钱/个，勺子8分钱/个</t>
-  </si>
-  <si>
-    <t>食材</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>250ml可乐24瓶</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>火鸡面拼多多补货5箱共150袋</t>
@@ -283,6 +275,18 @@
   </si>
   <si>
     <t>老李9元/斤买走20斤上述肉片</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>300圆碗四箱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>450圆碗三箱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>50包火鸡面</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -410,42 +414,6 @@
     <dxf>
       <font>
         <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
@@ -486,6 +454,42 @@
       </font>
       <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
       <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -545,9 +549,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
   <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -578,8 +582,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A37:C42" totalsRowShown="0">
-  <autoFilter ref="A37:C42" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A39:C44" totalsRowShown="0">
+  <autoFilter ref="A39:C44" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="7"/>
@@ -590,12 +594,12 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A6:C34" totalsRowShown="0">
-  <autoFilter ref="A6:C34" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A6:C36" totalsRowShown="0">
+  <autoFilter ref="A6:C36" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1769,7 +1773,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -1783,7 +1787,7 @@
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>45692.35</v>
+        <v>46179.549999999996</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1801,7 +1805,7 @@
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-45692.35</v>
+        <v>-46179.549999999996</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1966,7 +1970,7 @@
         <v>25</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -2069,19 +2073,19 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="18">
-        <v>26</v>
+      <c r="A30" s="19">
+        <v>304.63</v>
       </c>
       <c r="B30" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>75</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="19">
-        <v>304.63</v>
+        <v>4355.5</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>25</v>
@@ -2092,82 +2096,86 @@
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="19">
-        <v>4355.5</v>
+        <v>-180</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="19">
-        <v>-180</v>
+        <v>350</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="19">
-        <v>350</v>
+        <v>224</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="2"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="6"/>
+      <c r="A35" s="19">
+        <v>177</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="2"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="6"/>
+      <c r="A36" s="19">
+        <v>112.2</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="2"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="6"/>
+    </row>
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="2"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="6"/>
+    </row>
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B39" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C39" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="10">
-        <v>0</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="6"/>
-    </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="10">
-        <v>0</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="6"/>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10">
         <v>0</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C40" s="6"/>
     </row>
@@ -2176,45 +2184,63 @@
         <v>0</v>
       </c>
       <c r="B41" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="6"/>
+    </row>
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="10">
+        <v>0</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="6"/>
+    </row>
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="10">
+        <v>0</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="6"/>
-    </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="20">
+      <c r="C43" s="6"/>
+    </row>
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="20">
         <v>0</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B44" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="16"/>
-    </row>
-    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="11"/>
-    </row>
-    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="12"/>
+      <c r="C44" s="16"/>
     </row>
     <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2"/>
-      <c r="C46" s="12"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="11"/>
+    </row>
+    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="12"/>
+    </row>
+    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="2"/>
+      <c r="C48" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B34" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B36" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,41 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\ChanWeiMai\财务与流水\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E2CDEF-82EC-44AB-AB41-9874923267D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="15820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="2026-02流水 " sheetId="3" r:id="rId2"/>
     <sheet name="2026-03流水" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="83">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -208,6 +189,9 @@
     <t>美团外卖</t>
   </si>
   <si>
+    <t>表哥工资预付3500</t>
+  </si>
+  <si>
     <t>芋头小笼120斤*12，肉燕120斤*22.5，菜探长进货</t>
   </si>
   <si>
@@ -235,6 +219,9 @@
     <t>外卖盒子临时补货</t>
   </si>
   <si>
+    <t>火鸡面拼多多补货5箱共150袋</t>
+  </si>
+  <si>
     <t>美团外卖推广</t>
   </si>
   <si>
@@ -262,44 +249,38 @@
     <t>一次性塑料袋和一次性勺子，塑料袋1分钱/个，勺子8分钱/个</t>
   </si>
   <si>
-    <t>火鸡面拼多多补货5箱共150袋</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>300斤肉片2400+100斤牛肉羹1700+运费255.5 = 4355.5</t>
+  </si>
+  <si>
+    <t>老李9元/斤买走20斤上述肉片</t>
   </si>
   <si>
     <t>弹粉进货，4.5/斤，运费0.5/斤</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>300斤肉片2400+100斤牛肉羹1700+运费255.5 = 4355.5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>老李9元/斤买走20斤上述肉片</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>300圆碗四箱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>450圆碗三箱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>50包火鸡面</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,29 +303,351 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -352,9 +655,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -370,167 +915,215 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -538,68 +1131,65 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
-  <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
+  <autoFilter ref="A5:C43"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="3"/>
+    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
+    <tableColumn id="2" name="分类" dataDxfId="1"/>
+    <tableColumn id="3" name="说明" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A29:C34" totalsRowShown="0">
-  <autoFilter ref="A29:C34" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A29:C34" totalsRowShown="0">
+  <autoFilter ref="A29:C34"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明"/>
+    <tableColumn id="1" name="营业额明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
-  <autoFilter ref="A6:C25" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
+  <autoFilter ref="A6:C25"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="说明"/>
+    <tableColumn id="1" name="成本明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A39:C44" totalsRowShown="0">
-  <autoFilter ref="A39:C44" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A39:C44" totalsRowShown="0">
+  <autoFilter ref="A39:C44"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="6"/>
+    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
+    <tableColumn id="2" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" name="说明" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A6:C36" totalsRowShown="0">
-  <autoFilter ref="A6:C36" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C36" totalsRowShown="0">
+  <autoFilter ref="A6:C36"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="0"/>
+    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
+    <tableColumn id="4" name="分类" dataDxfId="7"/>
+    <tableColumn id="1" name="说明" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -884,62 +1474,61 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="23.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="13" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" ht="15" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="15">
         <v>100000</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" ht="15" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="16">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99761.380000000019</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>99761.38</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="16">
         <f>C1-C2</f>
-        <v>238.61999999998079</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>238.619999999981</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1"/>
+    <row r="5" ht="15" customHeight="1" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" ht="15" customHeight="1" spans="1:3">
       <c r="A6" s="5">
         <v>10000</v>
       </c>
@@ -950,7 +1539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" ht="15" customHeight="1" spans="1:3">
       <c r="A7" s="5">
         <v>26000</v>
       </c>
@@ -961,7 +1550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" ht="15" customHeight="1" spans="1:3">
       <c r="A8" s="5">
         <v>6000</v>
       </c>
@@ -972,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" ht="15" customHeight="1" spans="1:3">
       <c r="A9" s="5">
         <v>3000</v>
       </c>
@@ -983,7 +1572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" ht="15" customHeight="1" spans="1:3">
       <c r="A10" s="5">
         <v>2100</v>
       </c>
@@ -994,7 +1583,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" ht="15" customHeight="1" spans="1:3">
       <c r="A11" s="5">
         <v>340</v>
       </c>
@@ -1005,7 +1594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" ht="15" customHeight="1" spans="1:3">
       <c r="A12" s="5">
         <v>200</v>
       </c>
@@ -1016,7 +1605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" ht="15" customHeight="1" spans="1:3">
       <c r="A13" s="5">
         <v>11000</v>
       </c>
@@ -1027,7 +1616,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" ht="15" customHeight="1" spans="1:3">
       <c r="A14" s="5">
         <v>5000</v>
       </c>
@@ -1038,7 +1627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" ht="15" customHeight="1" spans="1:3">
       <c r="A15" s="5">
         <v>755</v>
       </c>
@@ -1049,7 +1638,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" ht="15" customHeight="1" spans="1:3">
       <c r="A16" s="5">
         <v>190</v>
       </c>
@@ -1060,7 +1649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" ht="15" customHeight="1" spans="1:3">
       <c r="A17" s="5">
         <v>405.9</v>
       </c>
@@ -1071,7 +1660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" ht="15" customHeight="1" spans="1:3">
       <c r="A18" s="5">
         <v>228</v>
       </c>
@@ -1082,7 +1671,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" ht="15" customHeight="1" spans="1:3">
       <c r="A19" s="5">
         <v>639.5</v>
       </c>
@@ -1093,9 +1682,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" ht="15" customHeight="1" spans="1:3">
       <c r="A20" s="5">
-        <v>1259.0999999999999</v>
+        <v>1259.1</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -1104,18 +1693,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" ht="15" customHeight="1" spans="1:3">
       <c r="A21" s="5">
         <v>1000</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" ht="15" customHeight="1" spans="1:3">
       <c r="A22" s="5">
         <v>13260</v>
       </c>
@@ -1126,7 +1715,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" ht="15" customHeight="1" spans="1:3">
       <c r="A23" s="5">
         <v>47.97</v>
       </c>
@@ -1137,9 +1726,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" ht="15" customHeight="1" spans="1:3">
       <c r="A24" s="5">
-        <v>276.10000000000002</v>
+        <v>276.1</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1148,226 +1737,226 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" ht="15" customHeight="1" spans="1:3">
       <c r="A25" s="5">
         <v>6000</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="18" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" ht="15" customHeight="1" spans="1:3">
       <c r="A26" s="5">
         <v>640</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" ht="15" customHeight="1" spans="1:3">
       <c r="A27" s="5">
         <v>500</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" ht="15" customHeight="1" spans="1:3">
       <c r="A28" s="5">
         <v>600</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" ht="15" customHeight="1" spans="1:3">
       <c r="A29" s="5">
         <v>938</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" ht="15" customHeight="1" spans="1:3">
       <c r="A30" s="5">
         <v>1000</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" ht="15" customHeight="1" spans="1:3">
       <c r="A31" s="5">
         <v>60.5</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" ht="15" customHeight="1" spans="1:3">
       <c r="A32" s="5">
         <v>162.41</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="18" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" ht="15" customHeight="1" spans="1:3">
       <c r="A33" s="5">
         <v>42.16</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" ht="15" customHeight="1" spans="1:3">
       <c r="A34" s="5">
         <v>1000</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="8">
+    <row r="35" ht="15" customHeight="1" spans="1:3">
+      <c r="A35" s="17">
         <v>500</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="20" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="8">
+    <row r="36" ht="15" customHeight="1" spans="1:3">
+      <c r="A36" s="17">
         <v>1300</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="8">
+    <row r="37" ht="15" customHeight="1" spans="1:3">
+      <c r="A37" s="17">
         <v>253.84</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="8">
+    <row r="38" ht="15" customHeight="1" spans="1:3">
+      <c r="A38" s="17">
         <v>1000</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="15" t="s">
+      <c r="B38" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="8">
+    <row r="39" ht="15" customHeight="1" spans="1:3">
+      <c r="A39" s="17">
         <v>355.3</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="B39" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="8">
+    <row r="40" ht="15" customHeight="1" spans="1:3">
+      <c r="A40" s="17">
         <v>3000</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="15" t="s">
+      <c r="B40" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="8">
+    <row r="41" ht="15" customHeight="1" spans="1:3">
+      <c r="A41" s="17">
         <v>174</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="15" t="s">
+      <c r="B41" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="8">
+    <row r="42" ht="15" customHeight="1" spans="1:3">
+      <c r="A42" s="17">
         <v>33.6</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="20" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="8">
+    <row r="43" ht="15" customHeight="1" spans="1:3">
+      <c r="A43" s="17">
         <v>500</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="15" t="s">
+      <c r="B43" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="20" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1375,28 +1964,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表_6[成本明细])</f>
-        <v>37512.810000000005</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>37512.81</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -1405,16 +1994,16 @@
         <v>42435.74</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="3">
         <f>B2-B1</f>
-        <v>4922.929999999993</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>4922.92999999999</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:3">
       <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
@@ -1425,7 +2014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" customHeight="1" spans="1:3">
       <c r="A7" s="5">
         <v>4333</v>
       </c>
@@ -1436,7 +2025,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="5">
         <v>8500</v>
       </c>
@@ -1447,7 +2036,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" customHeight="1" spans="1:3">
       <c r="A9" s="5">
         <v>1000</v>
       </c>
@@ -1458,7 +2047,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" customHeight="1" spans="1:3">
       <c r="A10" s="5">
         <v>13260</v>
       </c>
@@ -1469,7 +2058,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" customHeight="1" spans="1:3">
       <c r="A11" s="5">
         <v>600</v>
       </c>
@@ -1480,7 +2069,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" customHeight="1" spans="1:3">
       <c r="A12" s="5">
         <v>938</v>
       </c>
@@ -1491,7 +2080,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" customHeight="1" spans="1:3">
       <c r="A13" s="5">
         <v>1000</v>
       </c>
@@ -1502,7 +2091,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" customHeight="1" spans="1:3">
       <c r="A14" s="5">
         <v>60.5</v>
       </c>
@@ -1513,7 +2102,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" customHeight="1" spans="1:3">
       <c r="A15" s="5">
         <v>162.41</v>
       </c>
@@ -1524,7 +2113,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" customHeight="1" spans="1:3">
       <c r="A16" s="5">
         <v>42.16</v>
       </c>
@@ -1535,7 +2124,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" customHeight="1" spans="1:3">
       <c r="A17" s="5">
         <v>1000</v>
       </c>
@@ -1546,251 +2135,251 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="8">
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="17">
         <v>1300</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="B18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="8">
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="17">
         <v>253.84</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="8">
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="17">
         <v>1000</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="8">
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="17">
         <v>355.3</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="8">
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="17">
         <v>3000</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="8">
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="17">
         <v>174</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="7" t="s">
+      <c r="B23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="8">
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="17">
         <v>33.6</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="8">
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="17">
         <v>500</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="B25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" customHeight="1" spans="1:3">
       <c r="A26" s="2"/>
-      <c r="B26" s="9"/>
+      <c r="B26" s="12"/>
       <c r="C26" s="6"/>
     </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" customHeight="1" spans="1:3">
       <c r="A27" s="2"/>
-      <c r="B27" s="9"/>
+      <c r="B27" s="12"/>
       <c r="C27" s="6"/>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" customHeight="1" spans="1:3">
       <c r="A28" s="2"/>
-      <c r="B28" s="9"/>
+      <c r="B28" s="12"/>
       <c r="C28" s="6"/>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" customHeight="1" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="10">
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="13">
         <v>6683.96</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10">
+    <row r="31" customHeight="1" spans="1:3">
+      <c r="A31" s="13">
         <v>1861.8</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="12" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10">
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="13">
         <v>0</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C32" s="6"/>
     </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="10">
-        <v>19919.099999999999</v>
-      </c>
-      <c r="B33" s="9" t="s">
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="13">
+        <v>19919.1</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C33" s="6"/>
     </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="10">
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="13">
         <v>13970.88</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C34" s="6"/>
     </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="11"/>
-    </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C37" s="15"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="12"/>
-    </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C38" s="16"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="2"/>
-      <c r="C39" s="12"/>
-    </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C39" s="16"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:3">
       <c r="A43" s="2"/>
-      <c r="B43" s="9"/>
+      <c r="B43" s="12"/>
       <c r="C43" s="6"/>
     </row>
-    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="10"/>
-      <c r="B44" s="9"/>
+    <row r="44" customHeight="1" spans="1:3">
+      <c r="A44" s="13"/>
+      <c r="B44" s="12"/>
       <c r="C44" s="6"/>
     </row>
-    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="10"/>
-      <c r="B45" s="9"/>
+    <row r="45" customHeight="1" spans="1:3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="12"/>
       <c r="C45" s="6"/>
     </row>
-    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="10"/>
-      <c r="B46" s="9"/>
+    <row r="46" customHeight="1" spans="1:3">
+      <c r="A46" s="13"/>
+      <c r="B46" s="12"/>
       <c r="C46" s="6"/>
     </row>
-    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="10"/>
-      <c r="B47" s="9"/>
+    <row r="47" customHeight="1" spans="1:3">
+      <c r="A47" s="13"/>
+      <c r="B47" s="12"/>
       <c r="C47" s="6"/>
     </row>
-    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="10"/>
-      <c r="B48" s="9"/>
+    <row r="48" customHeight="1" spans="1:3">
+      <c r="A48" s="13"/>
+      <c r="B48" s="12"/>
       <c r="C48" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B25" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B25">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B20" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B20">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <tableParts count="2">
+    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>46179.549999999996</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>32679.55</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -1799,16 +2388,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-46179.549999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>-32679.55</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:3">
       <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
@@ -1819,8 +2408,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="17">
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="7">
         <v>4333</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1830,417 +2419,417 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="17">
-        <v>17000</v>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="7">
+        <v>3500</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="17">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:3">
+      <c r="A9" s="7">
         <v>4140</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="17">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:3">
+      <c r="A10" s="7">
         <v>7866</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="17">
+      <c r="B10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:3">
+      <c r="A11" s="7">
         <v>28.64</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="17">
+      <c r="C11" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:3">
+      <c r="A12" s="7">
         <v>44.48</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="17">
+    <row r="13" customHeight="1" spans="1:3">
+      <c r="A13" s="7">
         <v>3000</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="17">
+    <row r="14" customHeight="1" spans="1:3">
+      <c r="A14" s="7">
         <v>23</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="17">
+      <c r="B14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="7">
         <v>468</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="17">
+      <c r="B15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="7">
         <v>385</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="17">
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A17" s="7">
         <v>295</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="17">
+      <c r="B17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A18" s="7">
         <v>718</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="17">
+      <c r="B18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A19" s="7">
         <v>57.6</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="17">
+      <c r="B19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="7">
         <v>302.5</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="7">
+        <v>400</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="10">
+        <v>225</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="10">
+        <v>350</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="10">
+        <v>112</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="10">
+        <v>198</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="10">
+        <v>100</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="10">
+        <v>362</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="10">
+        <v>300</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="17">
-        <v>400</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="18">
-        <v>225</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="7" t="s">
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="10">
+        <v>128</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="11">
+        <v>304.63</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="18">
+    <row r="31" customHeight="1" spans="1:3">
+      <c r="A31" s="11">
+        <v>4355.5</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:3">
+      <c r="A32" s="11">
+        <v>-180</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="11">
         <v>350</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="18">
-        <v>112</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="18">
-        <v>198</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="18">
-        <v>100</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="18">
-        <v>362</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="18">
-        <v>300</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="18">
-        <v>128</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="19">
-        <v>304.63</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="19">
-        <v>4355.5</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="19">
-        <v>-180</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="19">
-        <v>350</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="19">
+      <c r="B33" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="11">
         <v>224</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="19">
+      <c r="B34" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:3">
+      <c r="A35" s="11">
         <v>177</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="19">
+      <c r="B35" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:3">
+      <c r="A36" s="11">
         <v>112.2</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="2"/>
-      <c r="B37" s="9"/>
+      <c r="B37" s="12"/>
       <c r="C37" s="6"/>
     </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="2"/>
-      <c r="B38" s="9"/>
+      <c r="B38" s="12"/>
       <c r="C38" s="6"/>
     </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="10">
+    <row r="40" customHeight="1" spans="1:3">
+      <c r="A40" s="13">
         <v>0</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C40" s="6"/>
     </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="10">
+    <row r="41" customHeight="1" spans="1:3">
+      <c r="A41" s="13">
         <v>0</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="12" t="s">
         <v>53</v>
       </c>
       <c r="C41" s="6"/>
     </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="10">
+    <row r="42" customHeight="1" spans="1:3">
+      <c r="A42" s="13">
         <v>0</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C42" s="6"/>
     </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="10">
+    <row r="43" customHeight="1" spans="1:3">
+      <c r="A43" s="13">
         <v>0</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C43" s="6"/>
     </row>
-    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="20">
+    <row r="44" customHeight="1" spans="1:3">
+      <c r="A44" s="14">
         <v>0</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C44" s="16"/>
-    </row>
-    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C44" s="9"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:3">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
-      <c r="C46" s="11"/>
-    </row>
-    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C46" s="15"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:3">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
-      <c r="C47" s="12"/>
-    </row>
-    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C47" s="16"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:3">
       <c r="A48" s="2"/>
-      <c r="C48" s="12"/>
+      <c r="C48" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B36" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B36">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <tableParts count="2">
+    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="86">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -265,6 +265,15 @@
   </si>
   <si>
     <t>50包火鸡面</t>
+  </si>
+  <si>
+    <t>老李买走100斤肉片</t>
+  </si>
+  <si>
+    <t>老池垫付的牛肉丸+鱼丸钱</t>
+  </si>
+  <si>
+    <t>硕美8元肉片补货300斤+100运费</t>
   </si>
 </sst>
 </file>
@@ -272,15 +281,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,12 +304,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -330,10 +333,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -342,6 +354,28 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -369,14 +403,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -391,11 +417,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -416,42 +449,12 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -468,19 +471,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -492,157 +597,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,6 +668,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -676,6 +688,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -710,17 +737,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -735,169 +756,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -907,45 +910,45 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1015,7 +1018,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -1051,7 +1054,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1092,7 +1095,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
+      <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1172,8 +1175,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A39:C44" totalsRowShown="0">
-  <autoFilter ref="A39:C44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A45:C50" totalsRowShown="0">
+  <autoFilter ref="A45:C50"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1184,8 +1187,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C36" totalsRowShown="0">
-  <autoFilter ref="A6:C36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C39" totalsRowShown="0">
+  <autoFilter ref="A6:C39"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -2362,7 +2365,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -2376,7 +2379,7 @@
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>32679.55</v>
+        <v>35471.55</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:2">
@@ -2394,7 +2397,7 @@
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-32679.55</v>
+        <v>-35471.55</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
@@ -2558,7 +2561,7 @@
       <c r="B20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2574,7 +2577,7 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>225</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -2585,7 +2588,7 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="10">
+      <c r="A23" s="9">
         <v>350</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -2596,7 +2599,7 @@
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="10">
+      <c r="A24" s="9">
         <v>112</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -2607,7 +2610,7 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="10">
+      <c r="A25" s="9">
         <v>198</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -2618,7 +2621,7 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
-      <c r="A26" s="10">
+      <c r="A26" s="9">
         <v>100</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -2629,7 +2632,7 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
-      <c r="A27" s="10">
+      <c r="A27" s="9">
         <v>362</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -2640,7 +2643,7 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="10">
+      <c r="A28" s="9">
         <v>300</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -2651,7 +2654,7 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
-      <c r="A29" s="10">
+      <c r="A29" s="9">
         <v>128</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -2662,165 +2665,213 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="11">
+      <c r="A30" s="9">
         <v>304.63</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="B30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="11">
+      <c r="A31" s="9">
         <v>4355.5</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="B31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="11">
+      <c r="A32" s="9">
         <v>-180</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="9" t="s">
+      <c r="B32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="11">
+      <c r="A33" s="9">
         <v>350</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="9" t="s">
+      <c r="B33" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="11">
+      <c r="A34" s="9">
         <v>224</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" s="9" t="s">
+      <c r="B34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:3">
-      <c r="A35" s="11">
+      <c r="A35" s="9">
         <v>177</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="9" t="s">
+      <c r="B35" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:3">
-      <c r="A36" s="11">
+      <c r="A36" s="9">
         <v>112.2</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="9" t="s">
+      <c r="B36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="6"/>
+      <c r="A37" s="10">
+        <v>-896</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="38" customHeight="1" spans="1:3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="6"/>
+      <c r="A38" s="10">
+        <v>1188</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="39" customHeight="1" spans="1:3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="10">
+        <v>2500</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:3">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="6"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:3">
+      <c r="A45" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B45" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C45" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:3">
-      <c r="A40" s="13">
+    <row r="46" customHeight="1" spans="1:3">
+      <c r="A46" s="13">
         <v>0</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B46" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="6"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:3">
-      <c r="A41" s="13">
+      <c r="C46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:3">
+      <c r="A47" s="13">
         <v>0</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B47" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="6"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:3">
-      <c r="A42" s="13">
+      <c r="C47" s="6"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:3">
+      <c r="A48" s="13">
         <v>0</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B48" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="6"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:3">
-      <c r="A43" s="13">
+      <c r="C48" s="6"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:3">
+      <c r="A49" s="13">
         <v>0</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B49" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="6"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:3">
-      <c r="A44" s="14">
+      <c r="C49" s="6"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:3">
+      <c r="A50" s="14">
         <v>0</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B50" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C44" s="9"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="15"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:3">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="16"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:3">
-      <c r="A48" s="2"/>
-      <c r="C48" s="16"/>
+      <c r="C50" s="8"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="15"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:3">
+      <c r="A53" s="2"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="16"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:3">
+      <c r="A54" s="2"/>
+      <c r="C54" s="16"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B37 B38 B39 B7:B36 B40:B43">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15820" activeTab="2"/>
+    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="88">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -189,7 +189,7 @@
     <t>美团外卖</t>
   </si>
   <si>
-    <t>表哥工资预付3500</t>
+    <t>员工工资，暂未发</t>
   </si>
   <si>
     <t>芋头小笼120斤*12，肉燕120斤*22.5，菜探长进货</t>
@@ -274,6 +274,12 @@
   </si>
   <si>
     <t>硕美8元肉片补货300斤+100运费</t>
+  </si>
+  <si>
+    <t>淘宝出餐机签约，299支持返现+免佣300</t>
+  </si>
+  <si>
+    <t>老李买走500斤肉片</t>
   </si>
 </sst>
 </file>
@@ -282,11 +288,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -326,8 +332,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -349,14 +370,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -365,41 +378,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -417,6 +400,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
@@ -425,16 +432,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,11 +454,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -471,13 +477,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,7 +597,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,25 +627,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,121 +651,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,6 +670,60 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -692,60 +752,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -759,142 +765,142 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -904,33 +910,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -948,7 +948,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1018,7 +1018,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -1095,7 +1095,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
+      <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1187,8 +1187,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C39" totalsRowShown="0">
-  <autoFilter ref="A6:C39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C41" totalsRowShown="0">
+  <autoFilter ref="A6:C41"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -1490,14 +1490,14 @@
   <cols>
     <col min="1" max="1" width="23.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="37.25" style="18" customWidth="1"/>
+    <col min="3" max="3" width="37.25" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15">
+      <c r="C1" s="13">
         <v>100000</v>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="14">
         <f>SUM(成本明细[金额(元)])</f>
         <v>99761.38</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="14">
         <f>C1-C2</f>
         <v>238.619999999981</v>
       </c>
@@ -1524,7 +1524,7 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1703,7 +1703,7 @@
       <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="16" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="16" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="16" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       <c r="B28" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="16" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="16" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       <c r="B31" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="16" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       <c r="B32" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="16" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="16" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1846,106 +1846,106 @@
       <c r="B34" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:3">
-      <c r="A35" s="17">
+      <c r="A35" s="15">
         <v>500</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:3">
-      <c r="A36" s="17">
+      <c r="A36" s="15">
         <v>1300</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="20" t="s">
+      <c r="B36" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="18" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:3">
-      <c r="A37" s="17">
+      <c r="A37" s="15">
         <v>253.84</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="20" t="s">
+      <c r="B37" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:3">
-      <c r="A38" s="17">
+      <c r="A38" s="15">
         <v>1000</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="20" t="s">
+      <c r="B38" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="18" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:3">
-      <c r="A39" s="17">
+      <c r="A39" s="15">
         <v>355.3</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="20" t="s">
+      <c r="B39" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:3">
-      <c r="A40" s="17">
+      <c r="A40" s="15">
         <v>3000</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="20" t="s">
+      <c r="B40" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="18" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:3">
-      <c r="A41" s="17">
+      <c r="A41" s="15">
         <v>174</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="20" t="s">
+      <c r="B41" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:3">
-      <c r="A42" s="17">
+      <c r="A42" s="15">
         <v>33.6</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:3">
-      <c r="A43" s="17">
+      <c r="A43" s="15">
         <v>500</v>
       </c>
-      <c r="B43" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="20" t="s">
+      <c r="B43" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="17">
+      <c r="A18" s="15">
         <v>1300</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -2150,7 +2150,7 @@
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="17">
+      <c r="A19" s="15">
         <v>253.84</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -2161,7 +2161,7 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="17">
+      <c r="A20" s="15">
         <v>1000</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -2172,7 +2172,7 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="17">
+      <c r="A21" s="15">
         <v>355.3</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -2183,7 +2183,7 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="17">
+      <c r="A22" s="15">
         <v>3000</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -2194,7 +2194,7 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="17">
+      <c r="A23" s="15">
         <v>174</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -2205,7 +2205,7 @@
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:3">
-      <c r="A24" s="17">
+      <c r="A24" s="15">
         <v>33.6</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -2216,7 +2216,7 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
-      <c r="A25" s="17">
+      <c r="A25" s="15">
         <v>500</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -2228,24 +2228,24 @@
     </row>
     <row r="26" customHeight="1" spans="1:3">
       <c r="A26" s="2"/>
-      <c r="B26" s="12"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="6"/>
     </row>
     <row r="27" customHeight="1" spans="1:3">
       <c r="A27" s="2"/>
-      <c r="B27" s="12"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" customHeight="1" spans="1:3">
       <c r="A28" s="2"/>
-      <c r="B28" s="12"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="6"/>
     </row>
     <row r="29" customHeight="1" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C29" s="6" t="s">
@@ -2253,46 +2253,46 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:3">
-      <c r="A30" s="13">
+      <c r="A30" s="11">
         <v>6683.96</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C30" s="6"/>
     </row>
     <row r="31" customHeight="1" spans="1:3">
-      <c r="A31" s="13">
+      <c r="A31" s="11">
         <v>1861.8</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="6"/>
     </row>
     <row r="32" customHeight="1" spans="1:3">
-      <c r="A32" s="13">
+      <c r="A32" s="11">
         <v>0</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C32" s="6"/>
     </row>
     <row r="33" customHeight="1" spans="1:3">
-      <c r="A33" s="13">
+      <c r="A33" s="11">
         <v>19919.1</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="10" t="s">
         <v>55</v>
       </c>
       <c r="C33" s="6"/>
     </row>
     <row r="34" customHeight="1" spans="1:3">
-      <c r="A34" s="13">
+      <c r="A34" s="11">
         <v>13970.88</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>56</v>
       </c>
       <c r="C34" s="6"/>
@@ -2300,45 +2300,45 @@
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="15"/>
+      <c r="C37" s="13"/>
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="16"/>
+      <c r="C38" s="14"/>
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="2"/>
-      <c r="C39" s="16"/>
+      <c r="C39" s="14"/>
     </row>
     <row r="43" customHeight="1" spans="1:3">
       <c r="A43" s="2"/>
-      <c r="B43" s="12"/>
+      <c r="B43" s="10"/>
       <c r="C43" s="6"/>
     </row>
     <row r="44" customHeight="1" spans="1:3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="12"/>
+      <c r="A44" s="11"/>
+      <c r="B44" s="10"/>
       <c r="C44" s="6"/>
     </row>
     <row r="45" customHeight="1" spans="1:3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="12"/>
+      <c r="A45" s="11"/>
+      <c r="B45" s="10"/>
       <c r="C45" s="6"/>
     </row>
     <row r="46" customHeight="1" spans="1:3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="12"/>
+      <c r="A46" s="11"/>
+      <c r="B46" s="10"/>
       <c r="C46" s="6"/>
     </row>
     <row r="47" customHeight="1" spans="1:3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="12"/>
+      <c r="A47" s="11"/>
+      <c r="B47" s="10"/>
       <c r="C47" s="6"/>
     </row>
     <row r="48" customHeight="1" spans="1:3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="12"/>
+      <c r="A48" s="11"/>
+      <c r="B48" s="10"/>
       <c r="C48" s="6"/>
     </row>
   </sheetData>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>35471.55</v>
+        <v>31837.55</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:2">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-35471.55</v>
+        <v>-31837.55</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
@@ -2424,7 +2424,7 @@
     </row>
     <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="7">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>48</v>
@@ -2742,68 +2742,80 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:3">
-      <c r="A37" s="10">
+      <c r="A37" s="9">
         <v>-896</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="11" t="s">
+      <c r="B37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:3">
-      <c r="A38" s="10">
+      <c r="A38" s="9">
         <v>1188</v>
       </c>
-      <c r="B38" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="11" t="s">
+      <c r="B38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:3">
-      <c r="A39" s="10">
+      <c r="A39" s="9">
         <v>2500</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="11" t="s">
+      <c r="B39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:3">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
+      <c r="A40" s="9">
+        <v>299</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="41" customHeight="1" spans="1:3">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
+      <c r="A41" s="9">
+        <v>-433</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="42" customHeight="1" spans="1:3">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
     </row>
     <row r="43" customHeight="1" spans="1:3">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
     </row>
     <row r="44" customHeight="1" spans="1:3">
       <c r="A44" s="2"/>
-      <c r="B44" s="12"/>
+      <c r="B44" s="10"/>
       <c r="C44" s="6"/>
     </row>
     <row r="45" customHeight="1" spans="1:3">
       <c r="A45" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C45" s="6" t="s">
@@ -2811,46 +2823,46 @@
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:3">
-      <c r="A46" s="13">
+      <c r="A46" s="11">
         <v>0</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C46" s="6"/>
     </row>
     <row r="47" customHeight="1" spans="1:3">
-      <c r="A47" s="13">
+      <c r="A47" s="11">
         <v>0</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="10" t="s">
         <v>53</v>
       </c>
       <c r="C47" s="6"/>
     </row>
     <row r="48" customHeight="1" spans="1:3">
-      <c r="A48" s="13">
+      <c r="A48" s="11">
         <v>0</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C48" s="6"/>
     </row>
     <row r="49" customHeight="1" spans="1:3">
-      <c r="A49" s="13">
+      <c r="A49" s="11">
         <v>0</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="10" t="s">
         <v>55</v>
       </c>
       <c r="C49" s="6"/>
     </row>
     <row r="50" customHeight="1" spans="1:3">
-      <c r="A50" s="14">
+      <c r="A50" s="12">
         <v>0</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="10" t="s">
         <v>56</v>
       </c>
       <c r="C50" s="8"/>
@@ -2858,20 +2870,20 @@
     <row r="52" customHeight="1" spans="1:3">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
-      <c r="C52" s="15"/>
+      <c r="C52" s="13"/>
     </row>
     <row r="53" customHeight="1" spans="1:3">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
-      <c r="C53" s="16"/>
+      <c r="C53" s="14"/>
     </row>
     <row r="54" customHeight="1" spans="1:3">
       <c r="A54" s="2"/>
-      <c r="C54" s="16"/>
+      <c r="C54" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B37 B38 B39 B7:B36 B40:B43">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B37 B38 B39 B40 B41 B7:B36 B42:B43">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -276,10 +276,22 @@
     <t>硕美8元肉片补货300斤+100运费</t>
   </si>
   <si>
-    <t>淘宝出餐机签约，299支持返现+免佣300</t>
+    <t>淘宝出餐机签约，299支持返现+免佣300，需要关注</t>
   </si>
   <si>
     <t>老李买走500斤肉片</t>
+  </si>
+  <si>
+    <t>淘宝推广</t>
+  </si>
+  <si>
+    <t>火鸡面10箱</t>
+  </si>
+  <si>
+    <t>1280打包盒</t>
+  </si>
+  <si>
+    <t>电话费300</t>
   </si>
 </sst>
 </file>
@@ -287,13 +299,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -333,10 +345,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -347,8 +359,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -370,38 +391,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -418,7 +409,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -431,16 +436,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,15 +446,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,13 +489,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,163 +651,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,65 +686,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -754,6 +712,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -762,145 +744,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -916,30 +928,30 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -948,7 +960,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1018,7 +1030,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -1054,7 +1066,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+      <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1095,7 +1107,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
+      <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
@@ -1175,8 +1187,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A45:C50" totalsRowShown="0">
-  <autoFilter ref="A45:C50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A50:C55" totalsRowShown="0">
+  <autoFilter ref="A50:C55"/>
   <tableColumns count="3">
     <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
     <tableColumn id="2" name="分类" dataDxfId="4"/>
@@ -1187,8 +1199,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C41" totalsRowShown="0">
-  <autoFilter ref="A6:C41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C45" totalsRowShown="0">
+  <autoFilter ref="A6:C45"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -2365,7 +2377,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
@@ -2379,7 +2391,7 @@
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>31837.55</v>
+        <v>33179.47</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:2">
@@ -2397,7 +2409,7 @@
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-31837.55</v>
+        <v>-33179.47</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
@@ -2797,93 +2809,142 @@
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
+      <c r="A42" s="9">
+        <v>50</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="43" customHeight="1" spans="1:3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
+      <c r="A43" s="9">
+        <v>601.92</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="44" customHeight="1" spans="1:3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="6"/>
+      <c r="A44" s="9">
+        <v>390</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="45" customHeight="1" spans="1:3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="9">
+        <v>300</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:3">
+      <c r="A49" s="2"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="6"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:3">
+      <c r="A50" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B50" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C50" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:3">
-      <c r="A46" s="11">
+    <row r="51" customHeight="1" spans="1:3">
+      <c r="A51" s="11">
         <v>0</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B51" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="6"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:3">
-      <c r="A47" s="11">
+      <c r="C51" s="6"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:3">
+      <c r="A52" s="11">
         <v>0</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B52" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C47" s="6"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:3">
-      <c r="A48" s="11">
+      <c r="C52" s="6"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:3">
+      <c r="A53" s="11">
         <v>0</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B53" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="6"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:3">
-      <c r="A49" s="11">
+      <c r="C53" s="6"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:3">
+      <c r="A54" s="11">
         <v>0</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B54" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="6"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:3">
-      <c r="A50" s="12">
+      <c r="C54" s="6"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:3">
+      <c r="A55" s="12">
         <v>0</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B55" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C50" s="8"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:3">
-      <c r="A52" s="2"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="13"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:3">
-      <c r="A53" s="2"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="14"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:3">
-      <c r="A54" s="2"/>
-      <c r="C54" s="14"/>
+      <c r="C55" s="8"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:3">
+      <c r="A57" s="2"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="13"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="14"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:3">
+      <c r="A59" s="2"/>
+      <c r="C59" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B37 B38 B39 B40 B41 B7:B36 B42:B43">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B37 B38 B39 B40 B41 B42 B43 B44 B45 B48 B7:B36 B46:B47">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="15820" activeTab="2"/>
+    <workbookView windowHeight="15960" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>电话费300</t>
+  </si>
+  <si>
+    <t>火鸡面临时补货</t>
   </si>
 </sst>
 </file>
@@ -299,13 +302,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -345,46 +348,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -399,11 +363,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -416,29 +410,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,6 +419,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -473,6 +453,29 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -489,25 +492,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -519,31 +642,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -555,115 +660,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,22 +693,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -714,22 +702,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -761,6 +734,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -774,145 +762,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1199,8 +1202,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C45" totalsRowShown="0">
-  <autoFilter ref="A6:C45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C46" totalsRowShown="0">
+  <autoFilter ref="A6:C46"/>
   <tableColumns count="3">
     <tableColumn id="2" name="成本明细" dataDxfId="6"/>
     <tableColumn id="4" name="分类" dataDxfId="7"/>
@@ -2391,7 +2394,7 @@
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>33179.47</v>
+        <v>50304.57</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:2">
@@ -2400,7 +2403,7 @@
       </c>
       <c r="B2" s="3">
         <f>SUM(营业额明细表[营业额明细])</f>
-        <v>0</v>
+        <v>32405.16</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:2">
@@ -2409,7 +2412,7 @@
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-33179.47</v>
+        <v>-17899.41</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
@@ -2436,7 +2439,7 @@
     </row>
     <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="7">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>48</v>
@@ -2853,9 +2856,15 @@
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
+      <c r="A46" s="9">
+        <v>125.1</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="47" customHeight="1" spans="1:3">
       <c r="A47" s="9"/>
@@ -2885,7 +2894,7 @@
     </row>
     <row r="51" customHeight="1" spans="1:3">
       <c r="A51" s="11">
-        <v>0</v>
+        <v>3393.36</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>52</v>
@@ -2894,7 +2903,7 @@
     </row>
     <row r="52" customHeight="1" spans="1:3">
       <c r="A52" s="11">
-        <v>0</v>
+        <v>910.97</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>53</v>
@@ -2903,7 +2912,7 @@
     </row>
     <row r="53" customHeight="1" spans="1:3">
       <c r="A53" s="11">
-        <v>0</v>
+        <v>3114.59</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>54</v>
@@ -2912,7 +2921,7 @@
     </row>
     <row r="54" customHeight="1" spans="1:3">
       <c r="A54" s="11">
-        <v>0</v>
+        <v>13860.32</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>55</v>
@@ -2921,7 +2930,7 @@
     </row>
     <row r="55" customHeight="1" spans="1:3">
       <c r="A55" s="12">
-        <v>0</v>
+        <v>11125.92</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>56</v>
@@ -2944,7 +2953,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B37 B38 B39 B40 B41 B42 B43 B44 B45 B48 B7:B36 B46:B47">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B7:B36">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7328C240-51EE-49BA-A027-B90281CC132C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15960" activeTab="2"/>
+    <workbookView xWindow="1830" yWindow="1095" windowWidth="35070" windowHeight="19335" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="2026-02流水 " sheetId="3" r:id="rId2"/>
     <sheet name="2026-03流水" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="97">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -295,22 +301,34 @@
   </si>
   <si>
     <t>火鸡面临时补货</t>
+  </si>
+  <si>
+    <t>福州鱼丸20包/198</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>750圆碗600个</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>小米空调</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000圆碗800个/308元</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="180" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,344 +352,28 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -679,261 +381,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -951,10 +411,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -963,185 +423,143 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
-      <font>
         <name val="宋体"/>
+        <charset val="134"/>
         <scheme val="none"/>
-        <charset val="134"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <name val="宋体"/>
+        <charset val="134"/>
         <scheme val="none"/>
-        <charset val="134"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <name val="宋体"/>
-        <scheme val="none"/>
-        <charset val="134"/>
         <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="180" formatCode="#,##0.00_ "/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1149,65 +567,68 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
-  <autoFilter ref="A5:C43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
+  <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
-    <tableColumn id="2" name="分类" dataDxfId="1"/>
-    <tableColumn id="3" name="说明" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A29:C34" totalsRowShown="0">
-  <autoFilter ref="A29:C34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A29:C34" totalsRowShown="0">
+  <autoFilter ref="A29:C34" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="营业额明细"/>
-    <tableColumn id="2" name="分类"/>
-    <tableColumn id="3" name="说明"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
-  <autoFilter ref="A6:C25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
+  <autoFilter ref="A6:C25" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="成本明细"/>
-    <tableColumn id="2" name="分类"/>
-    <tableColumn id="3" name="说明"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A50:C55" totalsRowShown="0">
-  <autoFilter ref="A50:C55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A53:C58" totalsRowShown="0">
+  <autoFilter ref="A53:C58" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
-    <tableColumn id="2" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" name="说明" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C46" totalsRowShown="0">
-  <autoFilter ref="A6:C46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A6:C50" totalsRowShown="0">
+  <autoFilter ref="A6:C50" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="2" name="成本明细" dataDxfId="6"/>
-    <tableColumn id="4" name="分类" dataDxfId="7"/>
-    <tableColumn id="1" name="说明" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="分类" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1492,23 +913,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="37.25" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1516,26 +938,26 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="14">
         <f>SUM(成本明细[金额(元)])</f>
-        <v>99761.38</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:3">
+        <v>99761.380000000019</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="14">
         <f>C1-C2</f>
-        <v>238.619999999981</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1"/>
-    <row r="5" ht="15" customHeight="1" spans="1:3">
+        <v>238.61999999998079</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1546,7 +968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5">
         <v>10000</v>
       </c>
@@ -1557,7 +979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
         <v>26000</v>
       </c>
@@ -1568,7 +990,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5">
         <v>6000</v>
       </c>
@@ -1579,7 +1001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5">
         <v>3000</v>
       </c>
@@ -1590,7 +1012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5">
         <v>2100</v>
       </c>
@@ -1601,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5">
         <v>340</v>
       </c>
@@ -1612,7 +1034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
         <v>200</v>
       </c>
@@ -1623,7 +1045,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5">
         <v>11000</v>
       </c>
@@ -1634,7 +1056,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5">
         <v>5000</v>
       </c>
@@ -1645,7 +1067,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="5">
         <v>755</v>
       </c>
@@ -1656,7 +1078,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5">
         <v>190</v>
       </c>
@@ -1667,7 +1089,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5">
         <v>405.9</v>
       </c>
@@ -1678,7 +1100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5">
         <v>228</v>
       </c>
@@ -1689,7 +1111,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5">
         <v>639.5</v>
       </c>
@@ -1700,9 +1122,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5">
-        <v>1259.1</v>
+        <v>1259.0999999999999</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
@@ -1711,7 +1133,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5">
         <v>1000</v>
       </c>
@@ -1722,7 +1144,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5">
         <v>13260</v>
       </c>
@@ -1733,7 +1155,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5">
         <v>47.97</v>
       </c>
@@ -1744,9 +1166,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5">
-        <v>276.1</v>
+        <v>276.10000000000002</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1755,7 +1177,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5">
         <v>6000</v>
       </c>
@@ -1766,7 +1188,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5">
         <v>640</v>
       </c>
@@ -1777,7 +1199,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5">
         <v>500</v>
       </c>
@@ -1788,7 +1210,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5">
         <v>600</v>
       </c>
@@ -1799,7 +1221,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5">
         <v>938</v>
       </c>
@@ -1810,7 +1232,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:3">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5">
         <v>1000</v>
       </c>
@@ -1821,7 +1243,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:3">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5">
         <v>60.5</v>
       </c>
@@ -1832,7 +1254,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:3">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5">
         <v>162.41</v>
       </c>
@@ -1843,7 +1265,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:3">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5">
         <v>42.16</v>
       </c>
@@ -1854,7 +1276,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:3">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5">
         <v>1000</v>
       </c>
@@ -1865,7 +1287,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:3">
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="15">
         <v>500</v>
       </c>
@@ -1876,7 +1298,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:3">
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="15">
         <v>1300</v>
       </c>
@@ -1887,7 +1309,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:3">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="15">
         <v>253.84</v>
       </c>
@@ -1898,7 +1320,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:3">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="15">
         <v>1000</v>
       </c>
@@ -1909,7 +1331,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:3">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="15">
         <v>355.3</v>
       </c>
@@ -1920,7 +1342,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:3">
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="15">
         <v>3000</v>
       </c>
@@ -1931,7 +1353,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:3">
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="15">
         <v>174</v>
       </c>
@@ -1942,7 +1364,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:3">
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="15">
         <v>33.6</v>
       </c>
@@ -1953,7 +1375,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:3">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="15">
         <v>500</v>
       </c>
@@ -1965,16 +1387,16 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"房租，装修，其他，设备，食材，推广，水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B43 B6:B42 F5:F14" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1982,28 +1404,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:2">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表_6[成本明细])</f>
-        <v>37512.81</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:2">
+        <v>37512.810000000005</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -2012,16 +1434,16 @@
         <v>42435.74</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:2">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="3">
         <f>B2-B1</f>
-        <v>4922.92999999999</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:3">
+        <v>4922.929999999993</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
@@ -2032,7 +1454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
         <v>4333</v>
       </c>
@@ -2043,7 +1465,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5">
         <v>8500</v>
       </c>
@@ -2054,7 +1476,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5">
         <v>1000</v>
       </c>
@@ -2065,7 +1487,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5">
         <v>13260</v>
       </c>
@@ -2076,7 +1498,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5">
         <v>600</v>
       </c>
@@ -2087,7 +1509,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
         <v>938</v>
       </c>
@@ -2098,7 +1520,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5">
         <v>1000</v>
       </c>
@@ -2109,7 +1531,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5">
         <v>60.5</v>
       </c>
@@ -2120,7 +1542,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="5">
         <v>162.41</v>
       </c>
@@ -2131,7 +1553,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5">
         <v>42.16</v>
       </c>
@@ -2142,7 +1564,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5">
         <v>1000</v>
       </c>
@@ -2153,7 +1575,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="15">
         <v>1300</v>
       </c>
@@ -2164,7 +1586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="15">
         <v>253.84</v>
       </c>
@@ -2175,7 +1597,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="15">
         <v>1000</v>
       </c>
@@ -2186,7 +1608,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="15">
         <v>355.3</v>
       </c>
@@ -2197,7 +1619,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="15">
         <v>3000</v>
       </c>
@@ -2208,7 +1630,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="15">
         <v>174</v>
       </c>
@@ -2219,7 +1641,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="15">
         <v>33.6</v>
       </c>
@@ -2230,7 +1652,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="15">
         <v>500</v>
       </c>
@@ -2241,22 +1663,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2"/>
       <c r="B26" s="10"/>
       <c r="C26" s="6"/>
     </row>
-    <row r="27" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2"/>
       <c r="B27" s="10"/>
       <c r="C27" s="6"/>
     </row>
-    <row r="28" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2"/>
       <c r="B28" s="10"/>
       <c r="C28" s="6"/>
     </row>
-    <row r="29" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
@@ -2267,7 +1689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:3">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="11">
         <v>6683.96</v>
       </c>
@@ -2276,7 +1698,7 @@
       </c>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" customHeight="1" spans="1:3">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="11">
         <v>1861.8</v>
       </c>
@@ -2285,7 +1707,7 @@
       </c>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" customHeight="1" spans="1:3">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="11">
         <v>0</v>
       </c>
@@ -2294,16 +1716,16 @@
       </c>
       <c r="C32" s="6"/>
     </row>
-    <row r="33" customHeight="1" spans="1:3">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="11">
-        <v>19919.1</v>
+        <v>19919.099999999999</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>55</v>
       </c>
       <c r="C33" s="6"/>
     </row>
-    <row r="34" customHeight="1" spans="1:3">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="11">
         <v>13970.88</v>
       </c>
@@ -2312,62 +1734,62 @@
       </c>
       <c r="C34" s="6"/>
     </row>
-    <row r="37" customHeight="1" spans="1:3">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="13"/>
     </row>
-    <row r="38" customHeight="1" spans="1:3">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="14"/>
     </row>
-    <row r="39" customHeight="1" spans="1:3">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2"/>
       <c r="C39" s="14"/>
     </row>
-    <row r="43" customHeight="1" spans="1:3">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2"/>
       <c r="B43" s="10"/>
       <c r="C43" s="6"/>
     </row>
-    <row r="44" customHeight="1" spans="1:3">
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="11"/>
       <c r="B44" s="10"/>
       <c r="C44" s="6"/>
     </row>
-    <row r="45" customHeight="1" spans="1:3">
+    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="11"/>
       <c r="B45" s="10"/>
       <c r="C45" s="6"/>
     </row>
-    <row r="46" customHeight="1" spans="1:3">
+    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="11"/>
       <c r="B46" s="10"/>
       <c r="C46" s="6"/>
     </row>
-    <row r="47" customHeight="1" spans="1:3">
+    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="11"/>
       <c r="B47" s="10"/>
       <c r="C47" s="6"/>
     </row>
-    <row r="48" customHeight="1" spans="1:3">
+    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="11"/>
       <c r="B48" s="10"/>
       <c r="C48" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B25" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"房租,装修,其他,设备,食材,推广,水电"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B20" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
@@ -2376,46 +1798,46 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C62"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
     <col min="3" max="3" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:2">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="3">
         <f>SUM(成本明细表[成本明细])</f>
-        <v>50304.57</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:2">
+        <v>52467.219999999994</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B2" s="3">
         <f>SUM(营业额明细表[营业额明细])</f>
-        <v>32405.16</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:2">
+        <v>32405.159999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="4">
         <f>B2-B1</f>
-        <v>-17899.41</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:3">
+        <v>-20062.059999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
@@ -2426,7 +1848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7">
         <v>4333</v>
       </c>
@@ -2437,7 +1859,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7">
         <v>17000</v>
       </c>
@@ -2448,7 +1870,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7">
         <v>4140</v>
       </c>
@@ -2459,7 +1881,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7">
         <v>7866</v>
       </c>
@@ -2470,7 +1892,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7">
         <v>28.64</v>
       </c>
@@ -2481,7 +1903,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7">
         <v>44.48</v>
       </c>
@@ -2492,7 +1914,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7">
         <v>3000</v>
       </c>
@@ -2503,7 +1925,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7">
         <v>23</v>
       </c>
@@ -2514,7 +1936,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7">
         <v>468</v>
       </c>
@@ -2525,7 +1947,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7">
         <v>385</v>
       </c>
@@ -2536,7 +1958,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="17" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7">
         <v>295</v>
       </c>
@@ -2547,7 +1969,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="18" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7">
         <v>718</v>
       </c>
@@ -2558,7 +1980,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:3">
+    <row r="19" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7">
         <v>57.6</v>
       </c>
@@ -2569,7 +1991,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:3">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7">
         <v>302.5</v>
       </c>
@@ -2580,7 +2002,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:3">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7">
         <v>400</v>
       </c>
@@ -2591,7 +2013,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:3">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="9">
         <v>225</v>
       </c>
@@ -2602,7 +2024,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:3">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="9">
         <v>350</v>
       </c>
@@ -2613,7 +2035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:3">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="9">
         <v>112</v>
       </c>
@@ -2624,7 +2046,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:3">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="9">
         <v>198</v>
       </c>
@@ -2635,7 +2057,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:3">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="9">
         <v>100</v>
       </c>
@@ -2646,7 +2068,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:3">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="9">
         <v>362</v>
       </c>
@@ -2657,7 +2079,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:3">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="9">
         <v>300</v>
       </c>
@@ -2668,7 +2090,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:3">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="9">
         <v>128</v>
       </c>
@@ -2679,7 +2101,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:3">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="9">
         <v>304.63</v>
       </c>
@@ -2690,7 +2112,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:3">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="9">
         <v>4355.5</v>
       </c>
@@ -2701,7 +2123,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:3">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="9">
         <v>-180</v>
       </c>
@@ -2712,7 +2134,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:3">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="9">
         <v>350</v>
       </c>
@@ -2723,7 +2145,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:3">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="9">
         <v>224</v>
       </c>
@@ -2734,7 +2156,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:3">
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="9">
         <v>177</v>
       </c>
@@ -2745,7 +2167,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:3">
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="9">
         <v>112.2</v>
       </c>
@@ -2756,7 +2178,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:3">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="9">
         <v>-896</v>
       </c>
@@ -2767,7 +2189,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:3">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="9">
         <v>1188</v>
       </c>
@@ -2778,7 +2200,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:3">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="9">
         <v>2500</v>
       </c>
@@ -2789,7 +2211,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:3">
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="9">
         <v>299</v>
       </c>
@@ -2800,7 +2222,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:3">
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="9">
         <v>-433</v>
       </c>
@@ -2811,7 +2233,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:3">
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="9">
         <v>50</v>
       </c>
@@ -2822,9 +2244,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:3">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="9">
-        <v>601.92</v>
+        <v>601.91999999999996</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>25</v>
@@ -2833,7 +2255,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:3">
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="9">
         <v>390</v>
       </c>
@@ -2844,7 +2266,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:3">
+    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="9">
         <v>300</v>
       </c>
@@ -2855,7 +2277,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:3">
+    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="9">
         <v>125.1</v>
       </c>
@@ -2866,100 +2288,139 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-    </row>
-    <row r="49" customHeight="1" spans="1:3">
-      <c r="A49" s="2"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="6"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:3">
-      <c r="A50" s="2" t="s">
+    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="19">
+        <v>170</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="19">
+        <v>1486.65</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="19">
+        <v>198</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="19">
+        <v>308</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="19"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+    </row>
+    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="2"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="6"/>
+    </row>
+    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B53" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C53" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:3">
-      <c r="A51" s="11">
+    <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="11">
         <v>3393.36</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B54" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C51" s="6"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:3">
-      <c r="A52" s="11">
+      <c r="C54" s="6"/>
+    </row>
+    <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="11">
         <v>910.97</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B55" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C52" s="6"/>
-    </row>
-    <row r="53" customHeight="1" spans="1:3">
-      <c r="A53" s="11">
+      <c r="C55" s="6"/>
+    </row>
+    <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="11">
         <v>3114.59</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B56" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="6"/>
-    </row>
-    <row r="54" customHeight="1" spans="1:3">
-      <c r="A54" s="11">
+      <c r="C56" s="6"/>
+    </row>
+    <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="11">
         <v>13860.32</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B57" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="6"/>
-    </row>
-    <row r="55" customHeight="1" spans="1:3">
-      <c r="A55" s="12">
+      <c r="C57" s="6"/>
+    </row>
+    <row r="58" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="12">
         <v>11125.92</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B58" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="8"/>
-    </row>
-    <row r="57" customHeight="1" spans="1:3">
-      <c r="A57" s="2"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="13"/>
-    </row>
-    <row r="58" customHeight="1" spans="1:3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="14"/>
-    </row>
-    <row r="59" customHeight="1" spans="1:3">
-      <c r="A59" s="2"/>
-      <c r="C59" s="14"/>
+      <c r="C58" s="8"/>
+    </row>
+    <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="2"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="13"/>
+    </row>
+    <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="2"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="14"/>
+    </row>
+    <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="2"/>
+      <c r="C62" s="14"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B7:B36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:B51" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7328C240-51EE-49BA-A027-B90281CC132C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1830" yWindow="1095" windowWidth="35070" windowHeight="19335" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="15820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
     <sheet name="2026-02流水 " sheetId="3" r:id="rId2"/>
     <sheet name="2026-03流水" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="97">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -303,32 +297,32 @@
     <t>火鸡面临时补货</t>
   </si>
   <si>
-    <t>福州鱼丸20包/198</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>750圆碗600个</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>小米空调</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>1000圆碗800个/308元</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>硕美进货，肉片500斤4000，小笼包100斤1100，肉燕100斤1800，鸡翅100个300，鸭爪100个130，运费230</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="180" formatCode="#,##0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,26 +348,348 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -381,9 +697,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -391,30 +949,36 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -423,143 +987,185 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="180" formatCode="#,##0.00_ "/>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -567,68 +1173,65 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
-  <autoFilter ref="A5:C43" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="成本明细" displayName="成本明细" ref="A5:C43" totalsRowShown="0">
+  <autoFilter ref="A5:C43"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="金额(元)" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="分类" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="说明" dataDxfId="6"/>
+    <tableColumn id="1" name="金额(元)" dataDxfId="0"/>
+    <tableColumn id="2" name="分类" dataDxfId="1"/>
+    <tableColumn id="3" name="说明" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="营业额明细表_5" displayName="营业额明细表_5" ref="A29:C34" totalsRowShown="0">
-  <autoFilter ref="A29:C34" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="营业额明细表_5" displayName="营业额明细表_5" ref="A29:C34" totalsRowShown="0">
+  <autoFilter ref="A29:C34"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="营业额明细"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="分类"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="说明"/>
+    <tableColumn id="1" name="营业额明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
-  <autoFilter ref="A6:C25" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="成本明细表_6" displayName="成本明细表_6" ref="A6:C25" totalsRowShown="0">
+  <autoFilter ref="A6:C25"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="成本明细"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="分类"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="说明"/>
+    <tableColumn id="1" name="成本明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="营业额明细表" displayName="营业额明细表" ref="A53:C58" totalsRowShown="0">
-  <autoFilter ref="A53:C58" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="营业额明细表" displayName="营业额明细表" ref="A54:C59" totalsRowShown="0">
+  <autoFilter ref="A54:C59"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="营业额明细" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="分类" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="说明" dataDxfId="3"/>
+    <tableColumn id="1" name="营业额明细" dataDxfId="3"/>
+    <tableColumn id="2" name="分类" dataDxfId="4"/>
+    <tableColumn id="3" name="说明" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="成本明细表" displayName="成本明细表" ref="A6:C50" totalsRowShown="0">
-  <autoFilter ref="A6:C50" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="成本明细表" displayName="成本明细表" ref="A6:C51" totalsRowShown="0">
+  <autoFilter ref="A6:C51"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="成本明细" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" n